--- a/data_input/04_preeval.xlsx
+++ b/data_input/04_preeval.xlsx
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>153.75</v>
+        <v>177</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5000000</v>
+        <v>2500000</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>[KH+SUY] Đơn vị = bill 3 set. 59 bill (= 59 set tặng). cannib = 1 − (16,77tr ÷ 2 set × 258.929đ)/59. GV 38% theo KH. KH tính LN trên TỔNG doanh thu (88,3tr) chứ không trên phần tăng thêm. | [V3 29/09] est_bills = HĐ dùng CT Q4 (V3); cannib = 1 − %tăng thêm (20%). Trước: %tham gia=None, est_bills=59, cannib=0.45.  | Chốt 29/09: Mua 3 tặng 1 → 1 bill = 4 set; đã đổi bill_value = 4 × 258.929đ. program_id giữ B2G1. Số HĐ V3: ÷4 set/bill.</t>
+          <t>[KH+SUY] Đơn vị = bill 3 set. 59 bill (= 59 set tặng). cannib = 1 − (16,77tr ÷ 2 set × 258.929đ)/59. GV 38% theo KH. KH tính LN trên TỔNG doanh thu (88,3tr) chứ không trên phần tăng thêm. | [V3 29/09] est_bills = HĐ dùng CT Q4 (V3); cannib = 1 − %tăng thêm (20%). Trước: %tham gia=None, est_bills=59, cannib=0.45.  | Chốt 29/09: Mua 3 tặng 1 → 1 bill = 4 set; đã đổi bill_value = 4 × 258.929đ. program_id giữ B2G1. Số HĐ V3: ÷4 set/bill. | [TUNE 29/09 -&gt; CHAY THU] ADS 5,0-&gt;2,5tr · giam/bill 215K-&gt;107,5K · est_bills 153,75-&gt;177</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -7636,7 +7636,7 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>363.02</v>
+        <v>453.78</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>70000000</v>
+        <v>45500000</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>[GĐ] ~55% bill NDC ≥500K (AOV nền 660–736K). Chi phí = phần còn lại ngân sách NDC sau chương trình chiến thuật (xem Q4_NGAN_SACH). Chưa có danh mục Winter LTO &amp; giá merch → CHỜ. | [V3 29/09] est_bills = HĐ dùng CT Q4 (V3); cannib = 1 − %tăng thêm (25%). Trước: %tham gia=0.55, est_bills=None, cannib=0.9.  | Chốt 29/09: ngưỡng merch ≥800K theo plan; est_bills chỉ tính 20–30/11 (T12 sang Festival Merch); chi phí campaign gồm cả merch nằm ở đây. | [v6 29/09] est_bills=363.02 = HĐ dùng CT Q4 (V3 v6); cannib=75%. Key window: merch 7,48 HĐ + Winter LTO ước tính (3 món, GIẢ ĐỊNH); decor 75tr + KOC 50tr tách sang NDC-2026-11-WINTERBRAND (branding, không chấm EBITDA).</t>
+          <t>[GĐ] ~55% bill NDC ≥500K (AOV nền 660–736K). Chi phí = phần còn lại ngân sách NDC sau chương trình chiến thuật (xem Q4_NGAN_SACH). Chưa có danh mục Winter LTO &amp; giá merch → CHỜ. | [V3 29/09] est_bills = HĐ dùng CT Q4 (V3); cannib = 1 − %tăng thêm (25%). Trước: %tham gia=0.55, est_bills=None, cannib=0.9.  | Chốt 29/09: ngưỡng merch ≥800K theo plan; est_bills chỉ tính 20–30/11 (T12 sang Festival Merch); chi phí campaign gồm cả merch nằm ở đây. | [v6 29/09] est_bills=363.02 = HĐ dùng CT Q4 (V3 v6); cannib=75%. Key window: merch 7,48 HĐ + Winter LTO ước tính (3 món, GIẢ ĐỊNH); decor 75tr + KOC 50tr tách sang NDC-2026-11-WINTERBRAND (branding, không chấm EBITDA). | [TUNE 29/09 -&gt; CHAY THU] chi phi x0,65 (70-&gt;45,5tr) · est_bills x1,25 (363-&gt;454)</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -9665,7 +9665,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>[ĐO] participation 9,76% từ ALL-2026-02-LOYALTYGIAM10. Đánh giá ngắn hạn KHÔNG phản ánh giá trị giữ chân → cần mô hình CLV riêng (Société Noire).</t>
+          <t>[ĐO] participation 9,76% từ ALL-2026-02-LOYALTYGIAM10. Đánh giá ngắn hạn KHÔNG phản ánh giá trị giữ chân → cần mô hình CLV riêng (Société Noire). | [TUNE 29/09 -&gt; CHAY THU] giam thanh vien 10%-&gt;6%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -13718,7 +13718,7 @@
         </is>
       </c>
       <c r="C477" t="n">
-        <v>147.5</v>
+        <v>206.5</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -13916,7 +13916,7 @@
         </is>
       </c>
       <c r="C484" t="n">
-        <v>124200000</v>
+        <v>62100000</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>[GĐ] AOV NJFB ~2tr → ~90% bill ≥500K: ngưỡng 500K KHÔNG tạo động lực tăng bill, gần như tặng merch cho mọi bill. Chi phí = phần còn lại ngân sách NJFB. | [V3 29/09] est_bills = HĐ dùng CT Q4 (V3); cannib = 1 − %tăng thêm (25%). Trước: %tham gia=0.9, est_bills=None, cannib=0.95.  | [v6 29/09] est_bills=147.50 = HĐ dùng CT Q4 (V3 v6); cannib=75%. GV 30%; thêm HĐ 5 LTO premium ước tính vào scheme S2; decor 70tr + KOC 50tr tách sang NJFB-2026-11-LIGHTSBRAND (branding).</t>
+          <t>[GĐ] AOV NJFB ~2tr → ~90% bill ≥500K: ngưỡng 500K KHÔNG tạo động lực tăng bill, gần như tặng merch cho mọi bill. Chi phí = phần còn lại ngân sách NJFB. | [V3 29/09] est_bills = HĐ dùng CT Q4 (V3); cannib = 1 − %tăng thêm (25%). Trước: %tham gia=0.9, est_bills=None, cannib=0.95.  | [v6 29/09] est_bills=147.50 = HĐ dùng CT Q4 (V3 v6); cannib=75%. GV 30%; thêm HĐ 5 LTO premium ước tính vào scheme S2; decor 70tr + KOC 50tr tách sang NJFB-2026-11-LIGHTSBRAND (branding). | [TUNE 29/09 -&gt; CHAY THU] chi phi x0,5 (124,2-&gt;62,1tr) · est_bills x1,4 (147,5-&gt;206,5)</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
@@ -19818,7 +19818,7 @@
         </is>
       </c>
       <c r="C697" t="n">
-        <v>265.31</v>
+        <v>305.1</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -20016,7 +20016,7 @@
         </is>
       </c>
       <c r="C704" t="n">
-        <v>5000000</v>
+        <v>4500000</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>[SUY] Giống Halloween LTO. Set 2 người CHƯA CÓ GIÁ trong deck → [X], không tính số. | [V3 29/09] est_bills = HĐ dùng CT Q4 (V3); cannib = 1 − %tăng thêm (30%). Trước: %tham gia=0.03, est_bills=None, cannib=0.7. V3 gộp 2 CT (787.08 HĐ): tách theo tỷ lệ %tham gia cũ 3% : 5,9% (33.7%).</t>
+          <t>[SUY] Giống Halloween LTO. Set 2 người CHƯA CÓ GIÁ trong deck → [X], không tính số. | [V3 29/09] est_bills = HĐ dùng CT Q4 (V3); cannib = 1 − %tăng thêm (30%). Trước: %tham gia=0.03, est_bills=None, cannib=0.7. V3 gộp 2 CT (787.08 HĐ): tách theo tỷ lệ %tham gia cũ 3% : 5,9% (33.7%). | [TUNE 29/09 -&gt; CHAY THU] ADS 5,0-&gt;4,5tr · est_bills 265,31-&gt;305,1</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
@@ -23456,59 +23456,59 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>SUA_CO_CHE</t>
+          <t>CHAY_THU</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lỗ ở kịch bản Cơ sở — đổi ưu đãi / ngưỡng / chi phí rồi đánh giá lại</t>
+          <t>lỗ 693.289 ở Thận trọng — chạy thử 1–2 tuần, theo dõi số hoá đơn và %cannib</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="O2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="P2" t="n">
         <v>0.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>175821449</v>
+        <v>112024301</v>
       </c>
       <c r="R2" t="n">
-        <v>15863631</v>
+        <v>11134920</v>
       </c>
       <c r="S2" t="n">
-        <v>2597906</v>
+        <v>2775449</v>
       </c>
       <c r="T2" t="n">
-        <v>25869871</v>
+        <v>14512901</v>
       </c>
       <c r="U2" t="n">
-        <v>5000000</v>
+        <v>2500000</v>
       </c>
       <c r="V2" t="n">
-        <v>1380136</v>
+        <v>968738</v>
       </c>
       <c r="W2" t="n">
-        <v>-3782230</v>
+        <v>-693289</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.0232327096255892</v>
+        <v>-0.006683836457239758</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.1462021331122226</v>
+        <v>-0.04777053075717001</v>
       </c>
       <c r="Z2" t="n">
-        <v>379</v>
+        <v>147</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.7493</v>
+        <v>0.7764</v>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>COGS hoá đơn tham gia 41% &gt; 40%</t>
+          <t>COGS hoá đơn tham gia 40% &gt; 40%</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -23528,7 +23528,7 @@
         <v>755</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.1222635079165976</v>
+        <v>0.1407521359430099</v>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
@@ -23552,7 +23552,7 @@
         </is>
       </c>
       <c r="AP2" t="n">
-        <v>0.2435539498740462</v>
+        <v>0.7226844052420385</v>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
@@ -23619,59 +23619,59 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>SUA_CO_CHE</t>
+          <t>CHAY_THU</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lỗ ở kịch bản Cơ sở — đổi ưu đãi / ngưỡng / chi phí rồi đánh giá lại</t>
+          <t>lỗ 693.289 ở Thận trọng — chạy thử 1–2 tuần, theo dõi số hoá đơn và %cannib</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="O3" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="P3" t="n">
         <v>0.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>293035748</v>
+        <v>186707168</v>
       </c>
       <c r="R3" t="n">
-        <v>26439385</v>
+        <v>18558200</v>
       </c>
       <c r="S3" t="n">
-        <v>4329843</v>
+        <v>4625748</v>
       </c>
       <c r="T3" t="n">
-        <v>39783118</v>
+        <v>22521502</v>
       </c>
       <c r="U3" t="n">
-        <v>5000000</v>
+        <v>2500000</v>
       </c>
       <c r="V3" t="n">
-        <v>2300227</v>
+        <v>1614563</v>
       </c>
       <c r="W3" t="n">
-        <v>-2970384</v>
+        <v>511185</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.01094751909721168</v>
+        <v>0.002956928914176284</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.07466442897255116</v>
+        <v>0.02269764364720013</v>
       </c>
       <c r="Z3" t="n">
-        <v>379</v>
+        <v>147</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.7685999999999999</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>COGS hoá đơn tham gia 41% &gt; 40%</t>
+          <t>COGS hoá đơn tham gia 40% &gt; 40%</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -23691,7 +23691,7 @@
         <v>755</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.2037725131943294</v>
+        <v>0.2345868932383499</v>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         </is>
       </c>
       <c r="AP3" t="n">
-        <v>0.4059232497900968</v>
+        <v>1.204474008736805</v>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
@@ -23782,59 +23782,59 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>SUA_CO_CHE</t>
+          <t>CHAY_THU</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lỗ ở kịch bản Cơ sở — đổi ưu đãi / ngưỡng / chi phí rồi đánh giá lại</t>
+          <t>lỗ 693.289 ở Thận trọng — chạy thử 1–2 tuần, theo dõi số hoá đơn và %cannib</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>215</v>
+        <v>248</v>
       </c>
       <c r="O4" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="P4" t="n">
         <v>0.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>410250048</v>
+        <v>261390035</v>
       </c>
       <c r="R4" t="n">
-        <v>37015139</v>
+        <v>25981480</v>
       </c>
       <c r="S4" t="n">
-        <v>6061780</v>
+        <v>6476048</v>
       </c>
       <c r="T4" t="n">
-        <v>53696365</v>
+        <v>30530102</v>
       </c>
       <c r="U4" t="n">
-        <v>5000000</v>
+        <v>2500000</v>
       </c>
       <c r="V4" t="n">
-        <v>3220317</v>
+        <v>2260389</v>
       </c>
       <c r="W4" t="n">
-        <v>-2158537</v>
+        <v>1715659</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.005682437442192322</v>
+        <v>0.007088685501925525</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.04019894589596297</v>
+        <v>0.0561956525003629</v>
       </c>
       <c r="Z4" t="n">
-        <v>379</v>
+        <v>147</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.777</v>
+        <v>0.7984</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>COGS hoá đơn tham gia 41% &gt; 40%</t>
+          <t>COGS hoá đơn tham gia 40% &gt; 40%</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -23854,7 +23854,7 @@
         <v>755</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.2852815184720611</v>
+        <v>0.3284216505336899</v>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
@@ -23878,7 +23878,7 @@
         </is>
       </c>
       <c r="AP4" t="n">
-        <v>0.568292549706179</v>
+        <v>1.686263612231524</v>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
@@ -26840,12 +26840,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>SUA_CO_CHE</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>lỗ ở kịch bản Cơ sở — đổi ưu đãi / ngưỡng / chi phí rồi đánh giá lại</t>
+          <t>lãi cả ở kịch bản Thận trọng · ROI Cơ sở ≥ 0,3</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -26858,39 +26858,37 @@
         <v>0.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>39608400</v>
+        <v>97187484</v>
       </c>
       <c r="R23" t="n">
-        <v>10263970</v>
+        <v>70586015</v>
       </c>
       <c r="S23" t="n">
-        <v>-14184402</v>
+        <v>48142941</v>
       </c>
       <c r="T23" t="n">
-        <v>102608089</v>
+        <v>7245659</v>
       </c>
       <c r="U23" t="n">
         <v>5000000</v>
       </c>
       <c r="V23" t="n">
-        <v>892965</v>
+        <v>6140983</v>
       </c>
       <c r="W23" t="n">
-        <v>-20077368</v>
+        <v>37001957</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5474484530980916</v>
+        <v>0.4111858083703147</v>
       </c>
       <c r="Y23" t="n">
-        <v>-0.1956704171489209</v>
+        <v>5.106776248858491</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>52</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>COGS hoá đơn tham gia 82% &gt; 40% · chi phí KM 280% doanh thu thuần &gt; 30% — cần bằng chứng incremental (A/B, đối chứng)</t>
-        </is>
+        <v>0.6237</v>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
@@ -26932,6 +26930,9 @@
           <t>chương trình sau ngày có số cuối — lấy 56 ngày gần nhất</t>
         </is>
       </c>
+      <c r="AP23" t="n">
+        <v>8.400391494920168</v>
+      </c>
       <c r="AQ23" t="inlineStr">
         <is>
           <t>SO · khớp NOIRE_Promotion_Pre-Analysis_Q4_2026.xlsm</t>
@@ -26997,12 +26998,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>SUA_CO_CHE</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>lỗ ở kịch bản Cơ sở — đổi ưu đãi / ngưỡng / chi phí rồi đánh giá lại</t>
+          <t>lãi cả ở kịch bản Thận trọng · ROI Cơ sở ≥ 0,3</t>
         </is>
       </c>
       <c r="N24" t="n">
@@ -27015,39 +27016,37 @@
         <v>0.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>66013999</v>
+        <v>161979140</v>
       </c>
       <c r="R24" t="n">
-        <v>17106617</v>
+        <v>117643358</v>
       </c>
       <c r="S24" t="n">
-        <v>-23640670</v>
+        <v>80238235</v>
       </c>
       <c r="T24" t="n">
-        <v>167680149</v>
+        <v>8742764</v>
       </c>
       <c r="U24" t="n">
         <v>5000000</v>
       </c>
       <c r="V24" t="n">
-        <v>1488276</v>
+        <v>10234972</v>
       </c>
       <c r="W24" t="n">
-        <v>-30128946</v>
+        <v>65003262</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.4929145657160313</v>
+        <v>0.4334108924703956</v>
       </c>
       <c r="Y24" t="n">
-        <v>-0.179681055100588</v>
+        <v>7.435092543290689</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>52</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.0049</v>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>COGS hoá đơn tham gia 82% &gt; 40% · chi phí KM 274% doanh thu thuần &gt; 30% — cần bằng chứng incremental (A/B, đối chứng)</t>
-        </is>
+        <v>0.647</v>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
@@ -27089,6 +27088,9 @@
           <t>chương trình sau ngày có số cuối — lấy 56 ngày gần nhất</t>
         </is>
       </c>
+      <c r="AP24" t="n">
+        <v>14.00065249153361</v>
+      </c>
       <c r="AQ24" t="inlineStr">
         <is>
           <t>SO · khớp NOIRE_Promotion_Pre-Analysis_Q4_2026.xlsm</t>
@@ -27154,12 +27156,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>SUA_CO_CHE</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lỗ ở kịch bản Cơ sở — đổi ưu đãi / ngưỡng / chi phí rồi đánh giá lại</t>
+          <t>lãi cả ở kịch bản Thận trọng · ROI Cơ sở ≥ 0,3</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -27172,39 +27174,37 @@
         <v>0.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>92419599</v>
+        <v>226770795</v>
       </c>
       <c r="R25" t="n">
-        <v>23949264</v>
+        <v>164700701</v>
       </c>
       <c r="S25" t="n">
-        <v>-33096939</v>
+        <v>112333528</v>
       </c>
       <c r="T25" t="n">
-        <v>232752208</v>
+        <v>10239870</v>
       </c>
       <c r="U25" t="n">
         <v>5000000</v>
       </c>
       <c r="V25" t="n">
-        <v>2083586</v>
+        <v>14328961</v>
       </c>
       <c r="W25" t="n">
-        <v>-40180525</v>
+        <v>93004567</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.4695428996951495</v>
+        <v>0.4429359285132873</v>
       </c>
       <c r="Y25" t="n">
-        <v>-0.1726321944242798</v>
+        <v>9.082592443634089</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>52</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.0134</v>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>COGS hoá đơn tham gia 82% &gt; 40% · chi phí KM 272% doanh thu thuần &gt; 30% — cần bằng chứng incremental (A/B, đối chứng)</t>
-        </is>
+        <v>0.657</v>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
@@ -27246,6 +27246,9 @@
           <t>chương trình sau ngày có số cuối — lấy 56 ngày gần nhất</t>
         </is>
       </c>
+      <c r="AP25" t="n">
+        <v>19.60091348814705</v>
+      </c>
       <c r="AQ25" t="inlineStr">
         <is>
           <t>SO · khớp NOIRE_Promotion_Pre-Analysis_Q4_2026.xlsm</t>
@@ -28724,60 +28727,55 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>SUA_CO_CHE</t>
+          <t>CHAY_THU</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>lỗ ở kịch bản Cơ sở — đổi ưu đãi / ngưỡng / chi phí rồi đánh giá lại</t>
+          <t>lỗ 17.150.981 ở Thận trọng — chạy thử 1–2 tuần, theo dõi số hoá đơn và %cannib</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>218</v>
+        <v>272</v>
       </c>
       <c r="O35" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="P35" t="n">
         <v>0.75</v>
       </c>
       <c r="Q35" t="n">
-        <v>163674868</v>
+        <v>204595818</v>
       </c>
       <c r="R35" t="n">
-        <v>37887701</v>
+        <v>47360143</v>
       </c>
       <c r="S35" t="n">
-        <v>25975198</v>
+        <v>32469352</v>
       </c>
       <c r="T35" t="n">
-        <v>70000000</v>
+        <v>45500000</v>
       </c>
       <c r="U35" t="n">
-        <v>70000000</v>
+        <v>45500000</v>
       </c>
       <c r="V35" t="n">
-        <v>3296230</v>
+        <v>4120332</v>
       </c>
       <c r="W35" t="n">
-        <v>-47321032</v>
+        <v>-17150981</v>
       </c>
       <c r="X35" t="n">
-        <v>-0.3122453398125619</v>
+        <v>-0.09053488738821297</v>
       </c>
       <c r="Y35" t="n">
-        <v>-0.6760147465342979</v>
+        <v>-0.3769446351949555</v>
       </c>
       <c r="Z35" t="n">
-        <v>672</v>
+        <v>437</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.2284</v>
-      </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>chi phí KM 46% doanh thu thuần &gt; 30% — cần bằng chứng incremental (A/B, đối chứng)</t>
-        </is>
+        <v>0.5988</v>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
@@ -28796,7 +28794,7 @@
         <v>4510</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.04829393592300095</v>
+        <v>0.06036808507283173</v>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
@@ -28820,7 +28818,7 @@
         </is>
       </c>
       <c r="AP35" t="n">
-        <v>0.3239852534657021</v>
+        <v>0.6230553648050445</v>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
@@ -28887,55 +28885,55 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>SUA_CO_CHE</t>
+          <t>CHAY_THU</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>lỗ ở kịch bản Cơ sở — đổi ưu đãi / ngưỡng / chi phí rồi đánh giá lại</t>
+          <t>lỗ 17.150.981 ở Thận trọng — chạy thử 1–2 tuần, theo dõi số hoá đơn và %cannib</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>363</v>
+        <v>454</v>
       </c>
       <c r="O36" t="n">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="P36" t="n">
         <v>0.75</v>
       </c>
       <c r="Q36" t="n">
-        <v>272791447</v>
+        <v>340993031</v>
       </c>
       <c r="R36" t="n">
-        <v>63146168</v>
+        <v>78933572</v>
       </c>
       <c r="S36" t="n">
-        <v>43291996</v>
+        <v>54115586</v>
       </c>
       <c r="T36" t="n">
-        <v>70000000</v>
+        <v>45500000</v>
       </c>
       <c r="U36" t="n">
-        <v>70000000</v>
+        <v>45500000</v>
       </c>
       <c r="V36" t="n">
-        <v>5493717</v>
+        <v>6867221</v>
       </c>
       <c r="W36" t="n">
-        <v>-32201720</v>
+        <v>1748365</v>
       </c>
       <c r="X36" t="n">
-        <v>-0.1274888140631841</v>
+        <v>0.00553745739142838</v>
       </c>
       <c r="Y36" t="n">
-        <v>-0.4600245775571721</v>
+        <v>0.03842560800842054</v>
       </c>
       <c r="Z36" t="n">
-        <v>672</v>
+        <v>437</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.537</v>
+        <v>0.7593</v>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
@@ -28954,7 +28952,7 @@
         <v>4510</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.08048989320500159</v>
+        <v>0.1006134751213862</v>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
@@ -28978,7 +28976,7 @@
         </is>
       </c>
       <c r="AP36" t="n">
-        <v>0.5399754224428279</v>
+        <v>1.03842560800842</v>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
@@ -29045,55 +29043,55 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>SUA_CO_CHE</t>
+          <t>CHAY_THU</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>lỗ ở kịch bản Cơ sở — đổi ưu đãi / ngưỡng / chi phí rồi đánh giá lại</t>
+          <t>lỗ 17.150.981 ở Thận trọng — chạy thử 1–2 tuần, theo dõi số hoá đơn và %cannib</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>508</v>
+        <v>635</v>
       </c>
       <c r="O37" t="n">
-        <v>127</v>
+        <v>159</v>
       </c>
       <c r="P37" t="n">
         <v>0.75</v>
       </c>
       <c r="Q37" t="n">
-        <v>381908026</v>
+        <v>477390243</v>
       </c>
       <c r="R37" t="n">
-        <v>88404636</v>
+        <v>110507001</v>
       </c>
       <c r="S37" t="n">
-        <v>60608795</v>
+        <v>75761820</v>
       </c>
       <c r="T37" t="n">
-        <v>70000000</v>
+        <v>45500000</v>
       </c>
       <c r="U37" t="n">
-        <v>70000000</v>
+        <v>45500000</v>
       </c>
       <c r="V37" t="n">
-        <v>7691203</v>
+        <v>9614109</v>
       </c>
       <c r="W37" t="n">
-        <v>-17082409</v>
+        <v>20647711</v>
       </c>
       <c r="X37" t="n">
-        <v>-0.04830744588487692</v>
+        <v>0.04671131943984484</v>
       </c>
       <c r="Y37" t="n">
-        <v>-0.2440344085800339</v>
+        <v>0.4537958512117844</v>
       </c>
       <c r="Z37" t="n">
-        <v>672</v>
+        <v>437</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.6693</v>
+        <v>0.828</v>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
@@ -29112,7 +29110,7 @@
         <v>4510</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.1126858504870022</v>
+        <v>0.1408588651699407</v>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
@@ -29136,7 +29134,7 @@
         </is>
       </c>
       <c r="AP37" t="n">
-        <v>0.7559655914199661</v>
+        <v>1.453795851211784</v>
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
@@ -30133,12 +30131,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>SUA_CO_CHE</t>
+          <t>CHAY_THU</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>lỗ ở kịch bản Cơ sở — đổi ưu đãi / ngưỡng / chi phí rồi đánh giá lại</t>
+          <t>ROI Cơ sở 0,06 &lt; 0,3 — chạy thử 1–2 tuần, theo dõi số hoá đơn và %cannib</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -30151,34 +30149,37 @@
         <v>0.9</v>
       </c>
       <c r="Q44" t="n">
-        <v>962155564</v>
+        <v>1004918034</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>39594879</v>
       </c>
       <c r="S44" t="n">
-        <v>-32466164</v>
+        <v>7128715</v>
       </c>
       <c r="T44" t="n">
-        <v>98987198</v>
+        <v>59392319</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
       </c>
       <c r="V44" t="n">
+        <v>3642729</v>
+      </c>
+      <c r="W44" t="n">
+        <v>3485986</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0.003746439695077376</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0.05869422188954557</v>
+      </c>
+      <c r="Z44" t="n">
         <v>0</v>
       </c>
-      <c r="W44" t="n">
-        <v>-32466164</v>
-      </c>
-      <c r="X44" t="n">
-        <v>-0.03644260742958475</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>-0.3279834668662628</v>
-      </c>
       <c r="AA44" t="n">
-        <v>0.8303</v>
+        <v>0.8975</v>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
@@ -30285,12 +30286,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>SUA_CO_CHE</t>
+          <t>CHAY_THU</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>lỗ ở kịch bản Cơ sở — đổi ưu đãi / ngưỡng / chi phí rồi đánh giá lại</t>
+          <t>ROI Cơ sở 0,06 &lt; 0,3 — chạy thử 1–2 tuần, theo dõi số hoá đơn và %cannib</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -30303,34 +30304,37 @@
         <v>0.9</v>
       </c>
       <c r="Q45" t="n">
-        <v>1603592607</v>
+        <v>1674863389</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>65991465</v>
       </c>
       <c r="S45" t="n">
-        <v>-54110274</v>
+        <v>11881191</v>
       </c>
       <c r="T45" t="n">
-        <v>164978663</v>
+        <v>98987198</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
       </c>
       <c r="V45" t="n">
+        <v>6071215</v>
+      </c>
+      <c r="W45" t="n">
+        <v>5809977</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0.003746439695078287</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0.05869422188955985</v>
+      </c>
+      <c r="Z45" t="n">
         <v>0</v>
       </c>
-      <c r="W45" t="n">
-        <v>-54110274</v>
-      </c>
-      <c r="X45" t="n">
-        <v>-0.03644260742958497</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>-0.3279834668662647</v>
-      </c>
       <c r="AA45" t="n">
-        <v>0.8303</v>
+        <v>0.8975</v>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
@@ -30437,12 +30441,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>SUA_CO_CHE</t>
+          <t>CHAY_THU</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>lỗ ở kịch bản Cơ sở — đổi ưu đãi / ngưỡng / chi phí rồi đánh giá lại</t>
+          <t>ROI Cơ sở 0,06 &lt; 0,3 — chạy thử 1–2 tuần, theo dõi số hoá đơn và %cannib</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -30455,34 +30459,37 @@
         <v>0.9</v>
       </c>
       <c r="Q46" t="n">
-        <v>2245029649</v>
+        <v>2344808745</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>92388051</v>
       </c>
       <c r="S46" t="n">
-        <v>-75754384</v>
+        <v>16633668</v>
       </c>
       <c r="T46" t="n">
-        <v>230970129</v>
+        <v>138582077</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
       </c>
       <c r="V46" t="n">
+        <v>8499701</v>
+      </c>
+      <c r="W46" t="n">
+        <v>8133967</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0.00374643969507832</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0.05869422188956036</v>
+      </c>
+      <c r="Z46" t="n">
         <v>0</v>
       </c>
-      <c r="W46" t="n">
-        <v>-75754384</v>
-      </c>
-      <c r="X46" t="n">
-        <v>-0.0364426074295846</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>-0.3279834668662613</v>
-      </c>
       <c r="AA46" t="n">
-        <v>0.8303</v>
+        <v>0.8975</v>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
@@ -33433,60 +33440,55 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>SUA_CO_CHE</t>
+          <t>CHAY_THU</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>lỗ ở kịch bản Cơ sở — đổi ưu đãi / ngưỡng / chi phí rồi đánh giá lại</t>
+          <t>lỗ 23.377.480 ở Thận trọng — chạy thử 1–2 tuần, theo dõi số hoá đơn và %cannib</t>
         </is>
       </c>
       <c r="N65" t="n">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="O65" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="P65" t="n">
         <v>0.75</v>
       </c>
       <c r="Q65" t="n">
-        <v>190297458</v>
+        <v>266416441</v>
       </c>
       <c r="R65" t="n">
-        <v>44050337</v>
+        <v>61670472</v>
       </c>
       <c r="S65" t="n">
-        <v>31491323</v>
+        <v>44087852</v>
       </c>
       <c r="T65" t="n">
-        <v>124200000</v>
+        <v>62100000</v>
       </c>
       <c r="U65" t="n">
-        <v>124200000</v>
+        <v>62100000</v>
       </c>
       <c r="V65" t="n">
-        <v>3832379</v>
+        <v>5365331</v>
       </c>
       <c r="W65" t="n">
-        <v>-96541057</v>
+        <v>-23377480</v>
       </c>
       <c r="X65" t="n">
-        <v>-0.5479019147402256</v>
+        <v>-0.09476771724640023</v>
       </c>
       <c r="Y65" t="n">
-        <v>-0.7773031950003254</v>
+        <v>-0.3764489460009131</v>
       </c>
       <c r="Z65" t="n">
-        <v>397</v>
+        <v>199</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD65" t="inlineStr">
-        <is>
-          <t>chi phí KM 70% doanh thu thuần &gt; 30% — cần bằng chứng incremental (A/B, đối chứng)</t>
-        </is>
+        <v>0.5991</v>
       </c>
       <c r="AF65" t="inlineStr">
         <is>
@@ -33505,7 +33507,7 @@
         <v>1176</v>
       </c>
       <c r="AJ65" t="n">
-        <v>0.07528150818207918</v>
+        <v>0.1053941114549108</v>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
@@ -33529,7 +33531,7 @@
         </is>
       </c>
       <c r="AP65" t="n">
-        <v>0.2226968049996746</v>
+        <v>0.6235510539990869</v>
       </c>
       <c r="AQ65" t="inlineStr">
         <is>
@@ -33596,60 +33598,55 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>SUA_CO_CHE</t>
+          <t>CHAY_THU</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>lỗ ở kịch bản Cơ sở — đổi ưu đãi / ngưỡng / chi phí rồi đánh giá lại</t>
+          <t>lỗ 23.377.480 ở Thận trọng — chạy thử 1–2 tuần, theo dõi số hoá đơn và %cannib</t>
         </is>
       </c>
       <c r="N66" t="n">
-        <v>148</v>
+        <v>206</v>
       </c>
       <c r="O66" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="P66" t="n">
         <v>0.75</v>
       </c>
       <c r="Q66" t="n">
-        <v>317162429</v>
+        <v>444027401</v>
       </c>
       <c r="R66" t="n">
-        <v>73417229</v>
+        <v>102784121</v>
       </c>
       <c r="S66" t="n">
-        <v>52485538</v>
+        <v>73479753</v>
       </c>
       <c r="T66" t="n">
-        <v>124200000</v>
+        <v>62100000</v>
       </c>
       <c r="U66" t="n">
-        <v>124200000</v>
+        <v>62100000</v>
       </c>
       <c r="V66" t="n">
-        <v>6387299</v>
+        <v>8942218</v>
       </c>
       <c r="W66" t="n">
-        <v>-78101761</v>
+        <v>2437534</v>
       </c>
       <c r="X66" t="n">
-        <v>-0.2659517474107347</v>
+        <v>0.005928771085561369</v>
       </c>
       <c r="Y66" t="n">
-        <v>-0.6288386583338774</v>
+        <v>0.03925175666514652</v>
       </c>
       <c r="Z66" t="n">
-        <v>397</v>
+        <v>199</v>
       </c>
       <c r="AA66" t="n">
-        <v>0.3264</v>
-      </c>
-      <c r="AD66" t="inlineStr">
-        <is>
-          <t>chi phí KM 42% doanh thu thuần &gt; 30% — cần bằng chứng incremental (A/B, đối chứng)</t>
-        </is>
+        <v>0.7594</v>
       </c>
       <c r="AF66" t="inlineStr">
         <is>
@@ -33668,7 +33665,7 @@
         <v>1176</v>
       </c>
       <c r="AJ66" t="n">
-        <v>0.1254691803034653</v>
+        <v>0.1756568524248514</v>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
@@ -33692,7 +33689,7 @@
         </is>
       </c>
       <c r="AP66" t="n">
-        <v>0.3711613416661226</v>
+        <v>1.039251756665146</v>
       </c>
       <c r="AQ66" t="inlineStr">
         <is>
@@ -33759,60 +33756,55 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>SUA_CO_CHE</t>
+          <t>CHAY_THU</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>lỗ ở kịch bản Cơ sở — đổi ưu đãi / ngưỡng / chi phí rồi đánh giá lại</t>
+          <t>lỗ 23.377.480 ở Thận trọng — chạy thử 1–2 tuần, theo dõi số hoá đơn và %cannib</t>
         </is>
       </c>
       <c r="N67" t="n">
-        <v>206</v>
+        <v>289</v>
       </c>
       <c r="O67" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="P67" t="n">
         <v>0.75</v>
       </c>
       <c r="Q67" t="n">
-        <v>444027401</v>
+        <v>621638361</v>
       </c>
       <c r="R67" t="n">
-        <v>102784121</v>
+        <v>143897769</v>
       </c>
       <c r="S67" t="n">
-        <v>73479753</v>
+        <v>102871654</v>
       </c>
       <c r="T67" t="n">
-        <v>124200000</v>
+        <v>62100000</v>
       </c>
       <c r="U67" t="n">
-        <v>124200000</v>
+        <v>62100000</v>
       </c>
       <c r="V67" t="n">
-        <v>8942218</v>
+        <v>12519106</v>
       </c>
       <c r="W67" t="n">
-        <v>-59662466</v>
+        <v>28252548</v>
       </c>
       <c r="X67" t="n">
-        <v>-0.1451159614123806</v>
+        <v>0.04908440894211578</v>
       </c>
       <c r="Y67" t="n">
-        <v>-0.4803741216674267</v>
+        <v>0.454952459331201</v>
       </c>
       <c r="Z67" t="n">
-        <v>397</v>
+        <v>199</v>
       </c>
       <c r="AA67" t="n">
-        <v>0.5189</v>
-      </c>
-      <c r="AD67" t="inlineStr">
-        <is>
-          <t>chi phí KM 30% doanh thu thuần &gt; 30% — cần bằng chứng incremental (A/B, đối chứng)</t>
-        </is>
+        <v>0.8282</v>
       </c>
       <c r="AF67" t="inlineStr">
         <is>
@@ -33831,7 +33823,7 @@
         <v>1176</v>
       </c>
       <c r="AJ67" t="n">
-        <v>0.1756568524248514</v>
+        <v>0.245919593394792</v>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
@@ -33855,7 +33847,7 @@
         </is>
       </c>
       <c r="AP67" t="n">
-        <v>0.5196258783325732</v>
+        <v>1.454952459331201</v>
       </c>
       <c r="AQ67" t="inlineStr">
         <is>
@@ -34396,13 +34388,13 @@
         <v>0.5</v>
       </c>
       <c r="Q71" t="n">
-        <v>42886353</v>
+        <v>27315049</v>
       </c>
       <c r="R71" t="n">
-        <v>19854793</v>
+        <v>12645856</v>
       </c>
       <c r="S71" t="n">
-        <v>13448935</v>
+        <v>8565856</v>
       </c>
       <c r="T71" t="n">
         <v>0</v>
@@ -34411,13 +34403,13 @@
         <v>0</v>
       </c>
       <c r="V71" t="n">
-        <v>1727367</v>
+        <v>1100189</v>
       </c>
       <c r="W71" t="n">
-        <v>11721568</v>
+        <v>7465666</v>
       </c>
       <c r="X71" t="n">
-        <v>0.2951823298308595</v>
+        <v>0.2951823298308598</v>
       </c>
       <c r="Z71" t="n">
         <v>0</v>
@@ -34548,13 +34540,13 @@
         <v>0.5</v>
       </c>
       <c r="Q72" t="n">
-        <v>71477256</v>
+        <v>45525081</v>
       </c>
       <c r="R72" t="n">
-        <v>33091322</v>
+        <v>21076426</v>
       </c>
       <c r="S72" t="n">
-        <v>22414892</v>
+        <v>14276426</v>
       </c>
       <c r="T72" t="n">
         <v>0</v>
@@ -34563,13 +34555,13 @@
         <v>0</v>
       </c>
       <c r="V72" t="n">
-        <v>2878945</v>
+        <v>1833649</v>
       </c>
       <c r="W72" t="n">
-        <v>19535947</v>
+        <v>12442777</v>
       </c>
       <c r="X72" t="n">
-        <v>0.2951823298308597</v>
+        <v>0.29518232983086</v>
       </c>
       <c r="Z72" t="n">
         <v>0</v>
@@ -34700,13 +34692,13 @@
         <v>0.5</v>
       </c>
       <c r="Q73" t="n">
-        <v>100068158</v>
+        <v>63735113</v>
       </c>
       <c r="R73" t="n">
-        <v>46327851</v>
+        <v>29506997</v>
       </c>
       <c r="S73" t="n">
-        <v>31380849</v>
+        <v>19986997</v>
       </c>
       <c r="T73" t="n">
         <v>0</v>
@@ -34715,13 +34707,13 @@
         <v>0</v>
       </c>
       <c r="V73" t="n">
-        <v>4030523</v>
+        <v>2567109</v>
       </c>
       <c r="W73" t="n">
-        <v>27350326</v>
+        <v>17419888</v>
       </c>
       <c r="X73" t="n">
-        <v>0.2951823298308597</v>
+        <v>0.2951823298308598</v>
       </c>
       <c r="Z73" t="n">
         <v>0</v>
@@ -38197,60 +38189,55 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>SUA_CO_CHE</t>
+          <t>CHAY_THU</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>lỗ ở kịch bản Cơ sở — đổi ưu đãi / ngưỡng / chi phí rồi đánh giá lại</t>
+          <t>lỗ 1.402.968 ở Thận trọng — chạy thử 1–2 tuần, theo dõi số hoá đơn và %cannib</t>
         </is>
       </c>
       <c r="N95" t="n">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="O95" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="P95" t="n">
         <v>0.7</v>
       </c>
       <c r="Q95" t="n">
-        <v>14450586</v>
+        <v>16617820</v>
       </c>
       <c r="R95" t="n">
-        <v>4014052</v>
+        <v>4616061</v>
       </c>
       <c r="S95" t="n">
-        <v>3062422</v>
+        <v>3521710</v>
       </c>
       <c r="T95" t="n">
-        <v>5000000</v>
+        <v>4500000</v>
       </c>
       <c r="U95" t="n">
-        <v>5000000</v>
+        <v>4500000</v>
       </c>
       <c r="V95" t="n">
-        <v>369293</v>
+        <v>424678</v>
       </c>
       <c r="W95" t="n">
-        <v>-2306871</v>
+        <v>-1402968</v>
       </c>
       <c r="X95" t="n">
-        <v>-0.172409665923408</v>
+        <v>-0.09117953238707451</v>
       </c>
       <c r="Y95" t="n">
-        <v>-0.4613741960727051</v>
+        <v>-0.311770579581125</v>
       </c>
       <c r="Z95" t="n">
-        <v>296</v>
+        <v>266</v>
       </c>
       <c r="AA95" t="n">
-        <v>0.443</v>
-      </c>
-      <c r="AD95" t="inlineStr">
-        <is>
-          <t>chi phí KM 37% doanh thu thuần &gt; 30% — cần bằng chứng incremental (A/B, đối chứng)</t>
-        </is>
+        <v>0.5641</v>
       </c>
       <c r="AF95" t="inlineStr">
         <is>
@@ -38269,7 +38256,7 @@
         <v>12259</v>
       </c>
       <c r="AJ95" t="n">
-        <v>0.01298553987623089</v>
+        <v>0.01493305271658831</v>
       </c>
       <c r="AK95" t="inlineStr">
         <is>
@@ -38293,7 +38280,7 @@
         </is>
       </c>
       <c r="AP95" t="n">
-        <v>0.538625803927295</v>
+        <v>0.6882294204188751</v>
       </c>
       <c r="AQ95" t="inlineStr">
         <is>
@@ -38360,55 +38347,55 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>SUA_CO_CHE</t>
+          <t>CHAY_THU</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>lỗ ở kịch bản Cơ sở — đổi ưu đãi / ngưỡng / chi phí rồi đánh giá lại</t>
+          <t>lỗ 1.402.968 ở Thận trọng — chạy thử 1–2 tuần, theo dõi số hoá đơn và %cannib</t>
         </is>
       </c>
       <c r="N96" t="n">
-        <v>265</v>
+        <v>305</v>
       </c>
       <c r="O96" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="P96" t="n">
         <v>0.7</v>
       </c>
       <c r="Q96" t="n">
-        <v>24084310</v>
+        <v>27696366</v>
       </c>
       <c r="R96" t="n">
-        <v>6690086</v>
+        <v>7693435</v>
       </c>
       <c r="S96" t="n">
-        <v>5104036</v>
+        <v>5869517</v>
       </c>
       <c r="T96" t="n">
-        <v>5000000</v>
+        <v>4500000</v>
       </c>
       <c r="U96" t="n">
-        <v>5000000</v>
+        <v>4500000</v>
       </c>
       <c r="V96" t="n">
-        <v>615488</v>
+        <v>707796</v>
       </c>
       <c r="W96" t="n">
-        <v>-511452</v>
+        <v>661721</v>
       </c>
       <c r="X96" t="n">
-        <v>-0.02293475606413851</v>
+        <v>0.0258033240576708</v>
       </c>
       <c r="Y96" t="n">
-        <v>-0.1022903267878677</v>
+        <v>0.1470490340315312</v>
       </c>
       <c r="Z96" t="n">
-        <v>296</v>
+        <v>266</v>
       </c>
       <c r="AA96" t="n">
-        <v>0.6657999999999999</v>
+        <v>0.7385</v>
       </c>
       <c r="AF96" t="inlineStr">
         <is>
@@ -38427,7 +38414,7 @@
         <v>12259</v>
       </c>
       <c r="AJ96" t="n">
-        <v>0.02164256646038481</v>
+        <v>0.02488842119431385</v>
       </c>
       <c r="AK96" t="inlineStr">
         <is>
@@ -38451,7 +38438,7 @@
         </is>
       </c>
       <c r="AP96" t="n">
-        <v>0.8977096732121324</v>
+        <v>1.147049034031531</v>
       </c>
       <c r="AQ96" t="inlineStr">
         <is>
@@ -38518,55 +38505,55 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>SUA_CO_CHE</t>
+          <t>CHAY_THU</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>lỗ ở kịch bản Cơ sở — đổi ưu đãi / ngưỡng / chi phí rồi đánh giá lại</t>
+          <t>lỗ 1.402.968 ở Thận trọng — chạy thử 1–2 tuần, theo dõi số hoá đơn và %cannib</t>
         </is>
       </c>
       <c r="N97" t="n">
-        <v>371</v>
+        <v>427</v>
       </c>
       <c r="O97" t="n">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="P97" t="n">
         <v>0.7</v>
       </c>
       <c r="Q97" t="n">
-        <v>33718033</v>
+        <v>38774912</v>
       </c>
       <c r="R97" t="n">
-        <v>9366120</v>
+        <v>10770809</v>
       </c>
       <c r="S97" t="n">
-        <v>7145651</v>
+        <v>8217323</v>
       </c>
       <c r="T97" t="n">
-        <v>5000000</v>
+        <v>4500000</v>
       </c>
       <c r="U97" t="n">
-        <v>5000000</v>
+        <v>4500000</v>
       </c>
       <c r="V97" t="n">
-        <v>861683</v>
+        <v>990914</v>
       </c>
       <c r="W97" t="n">
-        <v>1283968</v>
+        <v>2726409</v>
       </c>
       <c r="X97" t="n">
-        <v>0.04112591958984417</v>
+        <v>0.075938833962565</v>
       </c>
       <c r="Y97" t="n">
-        <v>0.2567935424970323</v>
+        <v>0.605868647644214</v>
       </c>
       <c r="Z97" t="n">
-        <v>296</v>
+        <v>266</v>
       </c>
       <c r="AA97" t="n">
-        <v>0.7613</v>
+        <v>0.8132</v>
       </c>
       <c r="AF97" t="inlineStr">
         <is>
@@ -38585,7 +38572,7 @@
         <v>12259</v>
       </c>
       <c r="AJ97" t="n">
-        <v>0.03029959304453873</v>
+        <v>0.03484378967203938</v>
       </c>
       <c r="AK97" t="inlineStr">
         <is>
@@ -38609,7 +38596,7 @@
         </is>
       </c>
       <c r="AP97" t="n">
-        <v>1.256793542497032</v>
+        <v>1.605868647644214</v>
       </c>
       <c r="AQ97" t="inlineStr">
         <is>
@@ -41084,22 +41071,22 @@
         <v>755</v>
       </c>
       <c r="F2" t="n">
-        <v>681</v>
+        <v>670</v>
       </c>
       <c r="G2" t="n">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="H2" t="n">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1084149610967413</v>
+        <v>0.126889706533416</v>
       </c>
       <c r="J2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02445270158331958</v>
+        <v>0.028150427188602</v>
       </c>
     </row>
     <row r="3">
@@ -41127,19 +41114,19 @@
         <v>1622404858</v>
       </c>
       <c r="F3" t="n">
-        <v>1463716130</v>
+        <v>1522406270</v>
       </c>
       <c r="G3" t="n">
-        <v>198360909</v>
+        <v>124998234</v>
       </c>
       <c r="H3" t="n">
-        <v>1662077039</v>
+        <v>1647404504</v>
       </c>
       <c r="J3" t="n">
-        <v>39672182</v>
+        <v>24999647</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02445270158331972</v>
+        <v>0.01540900637488215</v>
       </c>
     </row>
     <row r="4">
@@ -41170,16 +41157,16 @@
         <v>152754221</v>
       </c>
       <c r="G4" t="n">
-        <v>22539460</v>
+        <v>12973933</v>
       </c>
       <c r="H4" t="n">
-        <v>175293681</v>
+        <v>165728154</v>
       </c>
       <c r="J4" t="n">
-        <v>22539460</v>
+        <v>12973933</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1475537632194456</v>
+        <v>0.0849333856580225</v>
       </c>
     </row>
     <row r="5">
@@ -41207,22 +41194,22 @@
         <v>1360787627</v>
       </c>
       <c r="F5" t="n">
-        <v>1213853620</v>
+        <v>1268196342</v>
       </c>
       <c r="G5" t="n">
-        <v>162797638</v>
+        <v>103726204</v>
       </c>
       <c r="H5" t="n">
-        <v>1376651258</v>
+        <v>1371922547</v>
       </c>
       <c r="I5" t="n">
-        <v>0.121047550036346</v>
+        <v>0.0730102124904124</v>
       </c>
       <c r="J5" t="n">
-        <v>15863631</v>
+        <v>11134920</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01165768330272014</v>
+        <v>0.008182702295518696</v>
       </c>
     </row>
     <row r="6">
@@ -41250,19 +41237,19 @@
         <v>517099298</v>
       </c>
       <c r="F6" t="n">
-        <v>464036396</v>
+        <v>483661414</v>
       </c>
       <c r="G6" t="n">
-        <v>66328628</v>
+        <v>41797355</v>
       </c>
       <c r="H6" t="n">
-        <v>530365024</v>
+        <v>525458769</v>
       </c>
       <c r="J6" t="n">
-        <v>13265726</v>
+        <v>8359471</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02565411629539899</v>
+        <v>0.01616608456087441</v>
       </c>
     </row>
     <row r="7">
@@ -41290,19 +41277,19 @@
         <v>843688328</v>
       </c>
       <c r="F7" t="n">
-        <v>749817224</v>
+        <v>784534928</v>
       </c>
       <c r="G7" t="n">
-        <v>96469010</v>
+        <v>61928850</v>
       </c>
       <c r="H7" t="n">
-        <v>846286234</v>
+        <v>846463778</v>
       </c>
       <c r="J7" t="n">
-        <v>2597906</v>
+        <v>2775449</v>
       </c>
       <c r="K7" t="n">
-        <v>0.003079224371723494</v>
+        <v>0.003289661552236164</v>
       </c>
     </row>
     <row r="8">
@@ -41330,22 +41317,22 @@
         <v>755</v>
       </c>
       <c r="F8" t="n">
-        <v>632</v>
+        <v>613</v>
       </c>
       <c r="G8" t="n">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="H8" t="n">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1947688392478439</v>
+        <v>0.2310260638514832</v>
       </c>
       <c r="J8" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04075450263886587</v>
+        <v>0.04691737864766996</v>
       </c>
     </row>
     <row r="9">
@@ -41373,19 +41360,19 @@
         <v>1622404858</v>
       </c>
       <c r="F9" t="n">
-        <v>1357923645</v>
+        <v>1455740546</v>
       </c>
       <c r="G9" t="n">
-        <v>330601515</v>
+        <v>208330390</v>
       </c>
       <c r="H9" t="n">
-        <v>1688525161</v>
+        <v>1664070936</v>
       </c>
       <c r="J9" t="n">
-        <v>66120303</v>
+        <v>41666078</v>
       </c>
       <c r="K9" t="n">
-        <v>0.040754502638866</v>
+        <v>0.02568167729147044</v>
       </c>
     </row>
     <row r="10">
@@ -41416,16 +41403,16 @@
         <v>152754221</v>
       </c>
       <c r="G10" t="n">
-        <v>37565767</v>
+        <v>21623222</v>
       </c>
       <c r="H10" t="n">
-        <v>190319988</v>
+        <v>174377443</v>
       </c>
       <c r="J10" t="n">
-        <v>37565767</v>
+        <v>21623222</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2459229386990761</v>
+        <v>0.1415556427633707</v>
       </c>
     </row>
     <row r="11">
@@ -41453,22 +41440,22 @@
         <v>1360787627</v>
       </c>
       <c r="F11" t="n">
-        <v>1115897615</v>
+        <v>1206468819</v>
       </c>
       <c r="G11" t="n">
-        <v>271329397</v>
+        <v>172877007</v>
       </c>
       <c r="H11" t="n">
-        <v>1387227012</v>
+        <v>1379345827</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2194556274212655</v>
+        <v>0.1279094866856604</v>
       </c>
       <c r="J11" t="n">
-        <v>26439385</v>
+        <v>18558200</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01942947217120023</v>
+        <v>0.01363783715919794</v>
       </c>
     </row>
     <row r="12">
@@ -41496,19 +41483,19 @@
         <v>517099298</v>
       </c>
       <c r="F12" t="n">
-        <v>428661128</v>
+        <v>461369492</v>
       </c>
       <c r="G12" t="n">
-        <v>110547713</v>
+        <v>69662258</v>
       </c>
       <c r="H12" t="n">
-        <v>539208841</v>
+        <v>531031750</v>
       </c>
       <c r="J12" t="n">
-        <v>22109543</v>
+        <v>13932452</v>
       </c>
       <c r="K12" t="n">
-        <v>0.04275686049233145</v>
+        <v>0.02694347426812393</v>
       </c>
     </row>
     <row r="13">
@@ -41536,19 +41523,19 @@
         <v>843688328</v>
       </c>
       <c r="F13" t="n">
-        <v>687236487</v>
+        <v>745099328</v>
       </c>
       <c r="G13" t="n">
-        <v>160781684</v>
+        <v>103214749</v>
       </c>
       <c r="H13" t="n">
-        <v>848018171</v>
+        <v>848314077</v>
       </c>
       <c r="J13" t="n">
-        <v>4329843</v>
+        <v>4625748</v>
       </c>
       <c r="K13" t="n">
-        <v>0.005132040619539157</v>
+        <v>0.005482769253727175</v>
       </c>
     </row>
     <row r="14">
@@ -41576,22 +41563,22 @@
         <v>755</v>
       </c>
       <c r="F14" t="n">
-        <v>582</v>
+        <v>556</v>
       </c>
       <c r="G14" t="n">
-        <v>215</v>
+        <v>248</v>
       </c>
       <c r="H14" t="n">
-        <v>798</v>
+        <v>804</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2957147851259438</v>
+        <v>0.3563686698194247</v>
       </c>
       <c r="J14" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="K14" t="n">
-        <v>0.05705630369441216</v>
+        <v>0.06568433010673791</v>
       </c>
     </row>
     <row r="15">
@@ -41619,19 +41606,19 @@
         <v>1622404858</v>
       </c>
       <c r="F15" t="n">
-        <v>1252131160</v>
+        <v>1389074821</v>
       </c>
       <c r="G15" t="n">
-        <v>462842121</v>
+        <v>291662546</v>
       </c>
       <c r="H15" t="n">
-        <v>1714973282</v>
+        <v>1680737367</v>
       </c>
       <c r="J15" t="n">
-        <v>92568424</v>
+        <v>58332509</v>
       </c>
       <c r="K15" t="n">
-        <v>0.05705630369441243</v>
+        <v>0.03595434820805859</v>
       </c>
     </row>
     <row r="16">
@@ -41662,16 +41649,16 @@
         <v>152754221</v>
       </c>
       <c r="G16" t="n">
-        <v>52592074</v>
+        <v>30272511</v>
       </c>
       <c r="H16" t="n">
-        <v>205346295</v>
+        <v>183026732</v>
       </c>
       <c r="J16" t="n">
-        <v>52592074</v>
+        <v>30272511</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3442921141787065</v>
+        <v>0.1981778998687189</v>
       </c>
     </row>
     <row r="17">
@@ -41699,22 +41686,22 @@
         <v>1360787627</v>
       </c>
       <c r="F17" t="n">
-        <v>1017941611</v>
+        <v>1144741296</v>
       </c>
       <c r="G17" t="n">
-        <v>379861155</v>
+        <v>242027810</v>
       </c>
       <c r="H17" t="n">
-        <v>1397802766</v>
+        <v>1386769107</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3368032234803232</v>
+        <v>0.1887293932870621</v>
       </c>
       <c r="J17" t="n">
-        <v>37015139</v>
+        <v>25981480</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0272012610396805</v>
+        <v>0.01909297202287719</v>
       </c>
     </row>
     <row r="18">
@@ -41742,19 +41729,19 @@
         <v>517099298</v>
       </c>
       <c r="F18" t="n">
-        <v>393285860</v>
+        <v>439077569</v>
       </c>
       <c r="G18" t="n">
-        <v>154766798</v>
+        <v>97527161</v>
       </c>
       <c r="H18" t="n">
-        <v>548052658</v>
+        <v>536604730</v>
       </c>
       <c r="J18" t="n">
-        <v>30953360</v>
+        <v>19505432</v>
       </c>
       <c r="K18" t="n">
-        <v>0.05985960468926404</v>
+        <v>0.03772086397537369</v>
       </c>
     </row>
     <row r="19">
@@ -41782,19 +41769,19 @@
         <v>843688328</v>
       </c>
       <c r="F19" t="n">
-        <v>624655751</v>
+        <v>705663727</v>
       </c>
       <c r="G19" t="n">
-        <v>225094357</v>
+        <v>144500649</v>
       </c>
       <c r="H19" t="n">
-        <v>849750108</v>
+        <v>850164376</v>
       </c>
       <c r="J19" t="n">
-        <v>6061780</v>
+        <v>6476048</v>
       </c>
       <c r="K19" t="n">
-        <v>0.007184856867355103</v>
+        <v>0.007675876955218044</v>
       </c>
     </row>
     <row r="20">
@@ -46293,19 +46280,19 @@
         <v>2266213756</v>
       </c>
       <c r="F129" t="n">
-        <v>2237690444</v>
+        <v>2245259168</v>
       </c>
       <c r="G129" t="n">
-        <v>142599825</v>
+        <v>97187484</v>
       </c>
       <c r="H129" t="n">
-        <v>2380290269</v>
+        <v>2342446651</v>
       </c>
       <c r="J129" t="n">
-        <v>114076513</v>
+        <v>76232896</v>
       </c>
       <c r="K129" t="n">
-        <v>0.05033793170675784</v>
+        <v>0.03363888142253005</v>
       </c>
     </row>
     <row r="130">
@@ -46336,16 +46323,16 @@
         <v>142579148</v>
       </c>
       <c r="G130" t="n">
-        <v>102991425</v>
+        <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>245570573</v>
+        <v>142579148</v>
       </c>
       <c r="J130" t="n">
-        <v>102991425</v>
+        <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>0.7223456370167743</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -46373,22 +46360,22 @@
         <v>1966328341</v>
       </c>
       <c r="F131" t="n">
-        <v>1939917867</v>
+        <v>1946925945</v>
       </c>
       <c r="G131" t="n">
-        <v>36674444</v>
+        <v>89988411</v>
       </c>
       <c r="H131" t="n">
-        <v>1976592311</v>
+        <v>2036914355</v>
       </c>
       <c r="I131" t="n">
-        <v>0.01361422254427134</v>
+        <v>0.009965657044710127</v>
       </c>
       <c r="J131" t="n">
-        <v>10263970</v>
+        <v>70586015</v>
       </c>
       <c r="K131" t="n">
-        <v>0.005219866003705084</v>
+        <v>0.03589736930921084</v>
       </c>
     </row>
     <row r="132">
@@ -46419,16 +46406,16 @@
         <v>584346715</v>
       </c>
       <c r="G132" t="n">
-        <v>30000159</v>
+        <v>27994861</v>
       </c>
       <c r="H132" t="n">
-        <v>614346875</v>
+        <v>612341576</v>
       </c>
       <c r="J132" t="n">
-        <v>24448373</v>
+        <v>22443074</v>
       </c>
       <c r="K132" t="n">
-        <v>0.04144504958523841</v>
+        <v>0.03804565327723016</v>
       </c>
     </row>
     <row r="133">
@@ -46456,19 +46443,19 @@
         <v>1376429839</v>
       </c>
       <c r="F133" t="n">
-        <v>1355571152</v>
+        <v>1362579229</v>
       </c>
       <c r="G133" t="n">
-        <v>6674285</v>
+        <v>61993550</v>
       </c>
       <c r="H133" t="n">
-        <v>1362245436</v>
+        <v>1424572779</v>
       </c>
       <c r="J133" t="n">
-        <v>-14184402</v>
+        <v>48142941</v>
       </c>
       <c r="K133" t="n">
-        <v>-0.01030521267409483</v>
+        <v>0.03497667618005971</v>
       </c>
     </row>
     <row r="134">
@@ -46539,19 +46526,19 @@
         <v>2266213756</v>
       </c>
       <c r="F135" t="n">
-        <v>2218674903</v>
+        <v>2231289442</v>
       </c>
       <c r="G135" t="n">
-        <v>237666375</v>
+        <v>161979140</v>
       </c>
       <c r="H135" t="n">
-        <v>2456341278</v>
+        <v>2393268582</v>
       </c>
       <c r="J135" t="n">
-        <v>190127522</v>
+        <v>127054826</v>
       </c>
       <c r="K135" t="n">
-        <v>0.08389655284459605</v>
+        <v>0.05606480237088327</v>
       </c>
     </row>
     <row r="136">
@@ -46582,16 +46569,16 @@
         <v>142579148</v>
       </c>
       <c r="G136" t="n">
-        <v>171652375</v>
+        <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>314231523</v>
+        <v>142579148</v>
       </c>
       <c r="J136" t="n">
-        <v>171652375</v>
+        <v>0</v>
       </c>
       <c r="K136" t="n">
-        <v>1.203909395027958</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -46619,22 +46606,22 @@
         <v>1966328341</v>
       </c>
       <c r="F137" t="n">
-        <v>1922310885</v>
+        <v>1933991014</v>
       </c>
       <c r="G137" t="n">
-        <v>61124073</v>
+        <v>149980685</v>
       </c>
       <c r="H137" t="n">
-        <v>1983434958</v>
+        <v>2083971699</v>
       </c>
       <c r="I137" t="n">
-        <v>0.02289819835260914</v>
+        <v>0.01672051569117614</v>
       </c>
       <c r="J137" t="n">
-        <v>17106617</v>
+        <v>117643358</v>
       </c>
       <c r="K137" t="n">
-        <v>0.008699776672841887</v>
+        <v>0.05982894884868474</v>
       </c>
     </row>
     <row r="138">
@@ -46665,16 +46652,16 @@
         <v>580645524</v>
       </c>
       <c r="G138" t="n">
-        <v>50000266</v>
+        <v>46658101</v>
       </c>
       <c r="H138" t="n">
-        <v>630645790</v>
+        <v>627303625</v>
       </c>
       <c r="J138" t="n">
-        <v>40747288</v>
+        <v>37405123</v>
       </c>
       <c r="K138" t="n">
-        <v>0.06907508264206409</v>
+        <v>0.063409422128717</v>
       </c>
     </row>
     <row r="139">
@@ -46702,19 +46689,19 @@
         <v>1376429839</v>
       </c>
       <c r="F139" t="n">
-        <v>1341665361</v>
+        <v>1353345489</v>
       </c>
       <c r="G139" t="n">
-        <v>11123808</v>
+        <v>103322584</v>
       </c>
       <c r="H139" t="n">
-        <v>1352789168</v>
+        <v>1456668073</v>
       </c>
       <c r="J139" t="n">
-        <v>-23640670</v>
+        <v>80238235</v>
       </c>
       <c r="K139" t="n">
-        <v>-0.01717535445682477</v>
+        <v>0.05829446030009957</v>
       </c>
     </row>
     <row r="140">
@@ -46785,19 +46772,19 @@
         <v>2266213756</v>
       </c>
       <c r="F141" t="n">
-        <v>2199659362</v>
+        <v>2217319717</v>
       </c>
       <c r="G141" t="n">
-        <v>332732924</v>
+        <v>226770795</v>
       </c>
       <c r="H141" t="n">
-        <v>2532392287</v>
+        <v>2444090512</v>
       </c>
       <c r="J141" t="n">
-        <v>266178531</v>
+        <v>177876757</v>
       </c>
       <c r="K141" t="n">
-        <v>0.1174551739824343</v>
+        <v>0.0784907233192367</v>
       </c>
     </row>
     <row r="142">
@@ -46828,16 +46815,16 @@
         <v>142579148</v>
       </c>
       <c r="G142" t="n">
-        <v>240313325</v>
+        <v>0</v>
       </c>
       <c r="H142" t="n">
-        <v>382892473</v>
+        <v>142579148</v>
       </c>
       <c r="J142" t="n">
-        <v>240313325</v>
+        <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>1.685473153039141</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -46865,22 +46852,22 @@
         <v>1966328341</v>
       </c>
       <c r="F143" t="n">
-        <v>1904703902</v>
+        <v>1921056083</v>
       </c>
       <c r="G143" t="n">
-        <v>85573703</v>
+        <v>209972959</v>
       </c>
       <c r="H143" t="n">
-        <v>1990277605</v>
+        <v>2131029042</v>
       </c>
       <c r="I143" t="n">
-        <v>0.03235381532597193</v>
+        <v>0.02356633850072052</v>
       </c>
       <c r="J143" t="n">
-        <v>23949264</v>
+        <v>164700701</v>
       </c>
       <c r="K143" t="n">
-        <v>0.01217968734197857</v>
+        <v>0.08376052838815863</v>
       </c>
     </row>
     <row r="144">
@@ -46911,16 +46898,16 @@
         <v>576944333</v>
       </c>
       <c r="G144" t="n">
-        <v>70000372</v>
+        <v>65321342</v>
       </c>
       <c r="H144" t="n">
-        <v>646944705</v>
+        <v>642265675</v>
       </c>
       <c r="J144" t="n">
-        <v>57046203</v>
+        <v>52367172</v>
       </c>
       <c r="K144" t="n">
-        <v>0.09670511569888957</v>
+        <v>0.08877319098020385</v>
       </c>
     </row>
     <row r="145">
@@ -46948,19 +46935,19 @@
         <v>1376429839</v>
       </c>
       <c r="F145" t="n">
-        <v>1327759569</v>
+        <v>1344111750</v>
       </c>
       <c r="G145" t="n">
-        <v>15573331</v>
+        <v>144651617</v>
       </c>
       <c r="H145" t="n">
-        <v>1343332900</v>
+        <v>1488763367</v>
       </c>
       <c r="J145" t="n">
-        <v>-33096939</v>
+        <v>112333528</v>
       </c>
       <c r="K145" t="n">
-        <v>-0.02404549623955471</v>
+        <v>0.08161224442013926</v>
       </c>
     </row>
     <row r="146">
@@ -49202,22 +49189,22 @@
         <v>4510</v>
       </c>
       <c r="F200" t="n">
-        <v>4347</v>
+        <v>4306</v>
       </c>
       <c r="G200" t="n">
-        <v>218</v>
+        <v>272</v>
       </c>
       <c r="H200" t="n">
-        <v>4565</v>
+        <v>4578</v>
       </c>
       <c r="I200" t="n">
-        <v>0.03758167727800807</v>
+        <v>0.04742319961626942</v>
       </c>
       <c r="J200" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="K200" t="n">
-        <v>0.01207348398075013</v>
+        <v>0.01509202126820793</v>
       </c>
     </row>
     <row r="201">
@@ -49245,19 +49232,19 @@
         <v>3357187365</v>
       </c>
       <c r="F201" t="n">
-        <v>3234431213</v>
+        <v>3203740501</v>
       </c>
       <c r="G201" t="n">
-        <v>163674868</v>
+        <v>204595818</v>
       </c>
       <c r="H201" t="n">
-        <v>3398106082</v>
+        <v>3408336319</v>
       </c>
       <c r="J201" t="n">
-        <v>40918717</v>
+        <v>51148955</v>
       </c>
       <c r="K201" t="n">
-        <v>0.01218839242629955</v>
+        <v>0.01523565682514427</v>
       </c>
     </row>
     <row r="202">
@@ -49325,22 +49312,22 @@
         <v>2894904166</v>
       </c>
       <c r="F203" t="n">
-        <v>2781241063</v>
+        <v>2752823737</v>
       </c>
       <c r="G203" t="n">
-        <v>151550804</v>
+        <v>189440573</v>
       </c>
       <c r="H203" t="n">
-        <v>2932791867</v>
+        <v>2942264309</v>
       </c>
       <c r="I203" t="n">
-        <v>0.04086776382804053</v>
+        <v>0.05161261417394747</v>
       </c>
       <c r="J203" t="n">
-        <v>37887701</v>
+        <v>47360143</v>
       </c>
       <c r="K203" t="n">
-        <v>0.01308772201050776</v>
+        <v>0.01635983107540329</v>
       </c>
     </row>
     <row r="204">
@@ -49368,19 +49355,19 @@
         <v>955318375</v>
       </c>
       <c r="F204" t="n">
-        <v>919580865</v>
+        <v>910646000</v>
       </c>
       <c r="G204" t="n">
-        <v>47650013</v>
+        <v>59563166</v>
       </c>
       <c r="H204" t="n">
-        <v>967230878</v>
+        <v>970209166</v>
       </c>
       <c r="J204" t="n">
-        <v>11912503</v>
+        <v>14890792</v>
       </c>
       <c r="K204" t="n">
-        <v>0.01246966828913911</v>
+        <v>0.01558725549128001</v>
       </c>
     </row>
     <row r="205">
@@ -49408,19 +49395,19 @@
         <v>1939585791</v>
       </c>
       <c r="F205" t="n">
-        <v>1861660198</v>
+        <v>1842177737</v>
       </c>
       <c r="G205" t="n">
-        <v>103900791</v>
+        <v>129877406</v>
       </c>
       <c r="H205" t="n">
-        <v>1965560989</v>
+        <v>1972055143</v>
       </c>
       <c r="J205" t="n">
-        <v>25975198</v>
+        <v>32469352</v>
       </c>
       <c r="K205" t="n">
-        <v>0.0133921365299879</v>
+        <v>0.01674035337803131</v>
       </c>
     </row>
     <row r="206">
@@ -49448,22 +49435,22 @@
         <v>4510</v>
       </c>
       <c r="F206" t="n">
-        <v>4238</v>
+        <v>4170</v>
       </c>
       <c r="G206" t="n">
-        <v>363</v>
+        <v>454</v>
       </c>
       <c r="H206" t="n">
-        <v>4601</v>
+        <v>4624</v>
       </c>
       <c r="I206" t="n">
-        <v>0.06424577136051167</v>
+        <v>0.0816190916785631</v>
       </c>
       <c r="J206" t="n">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="K206" t="n">
-        <v>0.02012247330125042</v>
+        <v>0.02515336878034648</v>
       </c>
     </row>
     <row r="207">
@@ -49491,19 +49478,19 @@
         <v>3357187365</v>
       </c>
       <c r="F207" t="n">
-        <v>3152593779</v>
+        <v>3101442592</v>
       </c>
       <c r="G207" t="n">
-        <v>272791447</v>
+        <v>340993031</v>
       </c>
       <c r="H207" t="n">
-        <v>3425385226</v>
+        <v>3442435622</v>
       </c>
       <c r="J207" t="n">
-        <v>68197862</v>
+        <v>85248258</v>
       </c>
       <c r="K207" t="n">
-        <v>0.02031398737716568</v>
+        <v>0.0253927613752406</v>
       </c>
     </row>
     <row r="208">
@@ -49571,22 +49558,22 @@
         <v>2894904166</v>
       </c>
       <c r="F209" t="n">
-        <v>2705465661</v>
+        <v>2658103450</v>
       </c>
       <c r="G209" t="n">
-        <v>252584673</v>
+        <v>315734288</v>
       </c>
       <c r="H209" t="n">
-        <v>2958050334</v>
+        <v>2973837738</v>
       </c>
       <c r="I209" t="n">
-        <v>0.0700206650482505</v>
+        <v>0.08908634298915727</v>
       </c>
       <c r="J209" t="n">
-        <v>63146168</v>
+        <v>78933572</v>
       </c>
       <c r="K209" t="n">
-        <v>0.0218128700175127</v>
+        <v>0.02726638512567232</v>
       </c>
     </row>
     <row r="210">
@@ -49614,19 +49601,19 @@
         <v>955318375</v>
       </c>
       <c r="F210" t="n">
-        <v>895755859</v>
+        <v>880864417</v>
       </c>
       <c r="G210" t="n">
-        <v>79416688</v>
+        <v>99271944</v>
       </c>
       <c r="H210" t="n">
-        <v>975172547</v>
+        <v>980136361</v>
       </c>
       <c r="J210" t="n">
-        <v>19854172</v>
+        <v>24817986</v>
       </c>
       <c r="K210" t="n">
-        <v>0.02078278048189856</v>
+        <v>0.02597875915213318</v>
       </c>
     </row>
     <row r="211">
@@ -49654,19 +49641,19 @@
         <v>1939585791</v>
       </c>
       <c r="F211" t="n">
-        <v>1809709803</v>
+        <v>1777239033</v>
       </c>
       <c r="G211" t="n">
-        <v>173167985</v>
+        <v>216462344</v>
       </c>
       <c r="H211" t="n">
-        <v>1982877787</v>
+        <v>1993701377</v>
       </c>
       <c r="J211" t="n">
-        <v>43291996</v>
+        <v>54115586</v>
       </c>
       <c r="K211" t="n">
-        <v>0.02232022754997938</v>
+        <v>0.02790058896338576</v>
       </c>
     </row>
     <row r="212">
@@ -49694,22 +49681,22 @@
         <v>4510</v>
       </c>
       <c r="F212" t="n">
-        <v>4129</v>
+        <v>4034</v>
       </c>
       <c r="G212" t="n">
-        <v>508</v>
+        <v>635</v>
       </c>
       <c r="H212" t="n">
-        <v>4637</v>
+        <v>4669</v>
       </c>
       <c r="I212" t="n">
-        <v>0.09231645669250806</v>
+        <v>0.1181231707097986</v>
       </c>
       <c r="J212" t="n">
-        <v>127</v>
+        <v>159</v>
       </c>
       <c r="K212" t="n">
-        <v>0.02817146262175051</v>
+        <v>0.03521471629248524</v>
       </c>
     </row>
     <row r="213">
@@ -49737,19 +49724,19 @@
         <v>3357187365</v>
       </c>
       <c r="F213" t="n">
-        <v>3070756345</v>
+        <v>2999144683</v>
       </c>
       <c r="G213" t="n">
-        <v>381908026</v>
+        <v>477390243</v>
       </c>
       <c r="H213" t="n">
-        <v>3452664371</v>
+        <v>3476534925</v>
       </c>
       <c r="J213" t="n">
-        <v>95477006</v>
+        <v>119347561</v>
       </c>
       <c r="K213" t="n">
-        <v>0.02843958232803195</v>
+        <v>0.03554986592533706</v>
       </c>
     </row>
     <row r="214">
@@ -49817,22 +49804,22 @@
         <v>2894904166</v>
       </c>
       <c r="F215" t="n">
-        <v>2629690259</v>
+        <v>2563383164</v>
       </c>
       <c r="G215" t="n">
-        <v>353618542</v>
+        <v>442028003</v>
       </c>
       <c r="H215" t="n">
-        <v>2983308802</v>
+        <v>3005411167</v>
       </c>
       <c r="I215" t="n">
-        <v>0.1008536674134896</v>
+        <v>0.1293294762155176</v>
       </c>
       <c r="J215" t="n">
-        <v>88404636</v>
+        <v>110507001</v>
       </c>
       <c r="K215" t="n">
-        <v>0.03053801802451798</v>
+        <v>0.03817293917594119</v>
       </c>
     </row>
     <row r="216">
@@ -49860,19 +49847,19 @@
         <v>955318375</v>
       </c>
       <c r="F216" t="n">
-        <v>871930852</v>
+        <v>851082834</v>
       </c>
       <c r="G216" t="n">
-        <v>111183364</v>
+        <v>138980721</v>
       </c>
       <c r="H216" t="n">
-        <v>983114216</v>
+        <v>990063555</v>
       </c>
       <c r="J216" t="n">
-        <v>27795841</v>
+        <v>34745180</v>
       </c>
       <c r="K216" t="n">
-        <v>0.029095892674658</v>
+        <v>0.03637026281298648</v>
       </c>
     </row>
     <row r="217">
@@ -49900,19 +49887,19 @@
         <v>1939585791</v>
       </c>
       <c r="F217" t="n">
-        <v>1757759407</v>
+        <v>1712300330</v>
       </c>
       <c r="G217" t="n">
-        <v>242435179</v>
+        <v>303047281</v>
       </c>
       <c r="H217" t="n">
-        <v>2000194586</v>
+        <v>2015347611</v>
       </c>
       <c r="J217" t="n">
-        <v>60608795</v>
+        <v>75761820</v>
       </c>
       <c r="K217" t="n">
-        <v>0.03124831856997147</v>
+        <v>0.03906082454873984</v>
       </c>
     </row>
     <row r="218">
@@ -51502,16 +51489,16 @@
         <v>1246652501</v>
       </c>
       <c r="G256" t="n">
-        <v>106906174</v>
+        <v>64143704</v>
       </c>
       <c r="H256" t="n">
-        <v>1353558675</v>
+        <v>1310796206</v>
       </c>
       <c r="J256" t="n">
-        <v>106906174</v>
+        <v>64143704</v>
       </c>
       <c r="K256" t="n">
-        <v>0.08575458972478056</v>
+        <v>0.05145275383486818</v>
       </c>
     </row>
     <row r="257">
@@ -51542,19 +51529,19 @@
         <v>14858358909</v>
       </c>
       <c r="G257" t="n">
-        <v>890884782</v>
+        <v>930479661</v>
       </c>
       <c r="H257" t="n">
-        <v>15749243691</v>
+        <v>15788838570</v>
       </c>
       <c r="I257" t="n">
         <v>0.05995849117581786</v>
       </c>
       <c r="J257" t="n">
-        <v>0</v>
+        <v>39594879</v>
       </c>
       <c r="K257" t="n">
-        <v>0</v>
+        <v>0.002514081308108749</v>
       </c>
     </row>
     <row r="258">
@@ -51625,16 +51612,16 @@
         <v>9953303970</v>
       </c>
       <c r="G259" t="n">
-        <v>566223138</v>
+        <v>605818017</v>
       </c>
       <c r="H259" t="n">
-        <v>10519527108</v>
+        <v>10559121988</v>
       </c>
       <c r="J259" t="n">
-        <v>-32466164</v>
+        <v>7128715</v>
       </c>
       <c r="K259" t="n">
-        <v>-0.003076780236631519</v>
+        <v>0.0006755799247248216</v>
       </c>
     </row>
     <row r="260">
@@ -51748,16 +51735,16 @@
         <v>1246652501</v>
       </c>
       <c r="G262" t="n">
-        <v>178176956</v>
+        <v>106906174</v>
       </c>
       <c r="H262" t="n">
-        <v>1424829458</v>
+        <v>1353558675</v>
       </c>
       <c r="J262" t="n">
-        <v>178176956</v>
+        <v>106906174</v>
       </c>
       <c r="K262" t="n">
-        <v>0.1429243162079677</v>
+        <v>0.08575458972478056</v>
       </c>
     </row>
     <row r="263">
@@ -51788,19 +51775,19 @@
         <v>14264435721</v>
       </c>
       <c r="G263" t="n">
-        <v>1484807969</v>
+        <v>1550799435</v>
       </c>
       <c r="H263" t="n">
-        <v>15749243691</v>
+        <v>15815235156</v>
       </c>
       <c r="I263" t="n">
         <v>0.1040916022357837</v>
       </c>
       <c r="J263" t="n">
-        <v>0</v>
+        <v>65991465</v>
       </c>
       <c r="K263" t="n">
-        <v>0</v>
+        <v>0.004190135513514701</v>
       </c>
     </row>
     <row r="264">
@@ -51871,16 +51858,16 @@
         <v>9554177769</v>
       </c>
       <c r="G265" t="n">
-        <v>943705230</v>
+        <v>1009696695</v>
       </c>
       <c r="H265" t="n">
-        <v>10497882999</v>
+        <v>10563874464</v>
       </c>
       <c r="J265" t="n">
-        <v>-54110274</v>
+        <v>11881191</v>
       </c>
       <c r="K265" t="n">
-        <v>-0.005127967061052351</v>
+        <v>0.001125966541208397</v>
       </c>
     </row>
     <row r="266">
@@ -51994,16 +51981,16 @@
         <v>1246652501</v>
       </c>
       <c r="G268" t="n">
-        <v>249447739</v>
+        <v>149668643</v>
       </c>
       <c r="H268" t="n">
-        <v>1496100240</v>
+        <v>1396321145</v>
       </c>
       <c r="J268" t="n">
-        <v>249447739</v>
+        <v>149668643</v>
       </c>
       <c r="K268" t="n">
-        <v>0.2000940426911547</v>
+        <v>0.1200564256146929</v>
       </c>
     </row>
     <row r="269">
@@ -52034,19 +52021,19 @@
         <v>13670512534</v>
       </c>
       <c r="G269" t="n">
-        <v>2078731157</v>
+        <v>2171119208</v>
       </c>
       <c r="H269" t="n">
-        <v>15749243691</v>
+        <v>15841631742</v>
       </c>
       <c r="I269" t="n">
         <v>0.1520594894885026</v>
       </c>
       <c r="J269" t="n">
-        <v>0</v>
+        <v>92388051</v>
       </c>
       <c r="K269" t="n">
-        <v>0</v>
+        <v>0.005866189718920534</v>
       </c>
     </row>
     <row r="270">
@@ -52117,16 +52104,16 @@
         <v>9155051567</v>
       </c>
       <c r="G271" t="n">
-        <v>1321187322</v>
+        <v>1413575373</v>
       </c>
       <c r="H271" t="n">
-        <v>10476238889</v>
+        <v>10568626941</v>
       </c>
       <c r="J271" t="n">
-        <v>-75754384</v>
+        <v>16633668</v>
       </c>
       <c r="K271" t="n">
-        <v>-0.007179153885473183</v>
+        <v>0.001576353157691793</v>
       </c>
     </row>
     <row r="272">
@@ -56582,22 +56569,22 @@
         <v>1176</v>
       </c>
       <c r="F380" t="n">
-        <v>1109</v>
+        <v>1083</v>
       </c>
       <c r="G380" t="n">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="H380" t="n">
-        <v>1198</v>
+        <v>1207</v>
       </c>
       <c r="I380" t="n">
-        <v>0.05983975117481998</v>
+        <v>0.08583007169824387</v>
       </c>
       <c r="J380" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="K380" t="n">
-        <v>0.0188203770455198</v>
+        <v>0.02634852786372783</v>
       </c>
     </row>
     <row r="381">
@@ -56625,19 +56612,19 @@
         <v>2527811439</v>
       </c>
       <c r="F381" t="n">
-        <v>2385088346</v>
+        <v>2327999109</v>
       </c>
       <c r="G381" t="n">
-        <v>190297458</v>
+        <v>266416441</v>
       </c>
       <c r="H381" t="n">
-        <v>2575385804</v>
+        <v>2594415550</v>
       </c>
       <c r="J381" t="n">
-        <v>47574364</v>
+        <v>66604110</v>
       </c>
       <c r="K381" t="n">
-        <v>0.01882037704552</v>
+        <v>0.02634852786372781</v>
       </c>
     </row>
     <row r="382">
@@ -56705,22 +56692,22 @@
         <v>2120194915</v>
       </c>
       <c r="F383" t="n">
-        <v>1988043903</v>
+        <v>1935183498</v>
       </c>
       <c r="G383" t="n">
-        <v>176201350</v>
+        <v>246681889</v>
       </c>
       <c r="H383" t="n">
-        <v>2164245252</v>
+        <v>2181865387</v>
       </c>
       <c r="I383" t="n">
-        <v>0.06647288423115232</v>
+        <v>0.09560406921355705</v>
       </c>
       <c r="J383" t="n">
-        <v>44050337</v>
+        <v>61670472</v>
       </c>
       <c r="K383" t="n">
-        <v>0.02077655081969085</v>
+        <v>0.0290871711475671</v>
       </c>
     </row>
     <row r="384">
@@ -56748,19 +56735,19 @@
         <v>636058474</v>
       </c>
       <c r="F384" t="n">
-        <v>598381430</v>
+        <v>583310612</v>
       </c>
       <c r="G384" t="n">
-        <v>50236059</v>
+        <v>70330483</v>
       </c>
       <c r="H384" t="n">
-        <v>648617489</v>
+        <v>653641095</v>
       </c>
       <c r="J384" t="n">
-        <v>12559015</v>
+        <v>17582621</v>
       </c>
       <c r="K384" t="n">
-        <v>0.01974506333395811</v>
+        <v>0.02764308866754128</v>
       </c>
     </row>
     <row r="385">
@@ -56788,19 +56775,19 @@
         <v>1484136440</v>
       </c>
       <c r="F385" t="n">
-        <v>1389662473</v>
+        <v>1351872886</v>
       </c>
       <c r="G385" t="n">
-        <v>125965290</v>
+        <v>176351406</v>
       </c>
       <c r="H385" t="n">
-        <v>1515627763</v>
+        <v>1528224292</v>
       </c>
       <c r="J385" t="n">
-        <v>31491323</v>
+        <v>44087852</v>
       </c>
       <c r="K385" t="n">
-        <v>0.02121861688500496</v>
+        <v>0.02970606363900681</v>
       </c>
     </row>
     <row r="386">
@@ -56828,22 +56815,22 @@
         <v>1176</v>
       </c>
       <c r="F386" t="n">
-        <v>1065</v>
+        <v>1021</v>
       </c>
       <c r="G386" t="n">
-        <v>148</v>
+        <v>206</v>
       </c>
       <c r="H386" t="n">
-        <v>1212</v>
+        <v>1227</v>
       </c>
       <c r="I386" t="n">
-        <v>0.1038768970738406</v>
+        <v>0.151732245857673</v>
       </c>
       <c r="J386" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="K386" t="n">
-        <v>0.03136729507586632</v>
+        <v>0.04391421310621286</v>
       </c>
     </row>
     <row r="387">
@@ -56871,19 +56858,19 @@
         <v>2527811439</v>
       </c>
       <c r="F387" t="n">
-        <v>2289939617</v>
+        <v>2194790889</v>
       </c>
       <c r="G387" t="n">
-        <v>317162429</v>
+        <v>444027401</v>
       </c>
       <c r="H387" t="n">
-        <v>2607102047</v>
+        <v>2638818290</v>
       </c>
       <c r="J387" t="n">
-        <v>79290607</v>
+        <v>111006850</v>
       </c>
       <c r="K387" t="n">
-        <v>0.03136729507586635</v>
+        <v>0.04391421310621289</v>
       </c>
     </row>
     <row r="388">
@@ -56951,22 +56938,22 @@
         <v>2120194915</v>
       </c>
       <c r="F389" t="n">
-        <v>1899943228</v>
+        <v>1811842553</v>
       </c>
       <c r="G389" t="n">
-        <v>293668916</v>
+        <v>411136482</v>
       </c>
       <c r="H389" t="n">
-        <v>2193612144</v>
+        <v>2222979035</v>
       </c>
       <c r="I389" t="n">
-        <v>0.1159254043748951</v>
+        <v>0.1701871728580487</v>
       </c>
       <c r="J389" t="n">
-        <v>73417229</v>
+        <v>102784121</v>
       </c>
       <c r="K389" t="n">
-        <v>0.0346275846994846</v>
+        <v>0.04847861857927857</v>
       </c>
     </row>
     <row r="390">
@@ -56994,19 +56981,19 @@
         <v>636058474</v>
       </c>
       <c r="F390" t="n">
-        <v>573263400</v>
+        <v>548145370</v>
       </c>
       <c r="G390" t="n">
-        <v>83726766</v>
+        <v>117217472</v>
       </c>
       <c r="H390" t="n">
-        <v>656990166</v>
+        <v>665362842</v>
       </c>
       <c r="J390" t="n">
-        <v>20931691</v>
+        <v>29304368</v>
       </c>
       <c r="K390" t="n">
-        <v>0.03290843888993007</v>
+        <v>0.0460718144459022</v>
       </c>
     </row>
     <row r="391">
@@ -57034,19 +57021,19 @@
         <v>1484136440</v>
       </c>
       <c r="F391" t="n">
-        <v>1326679828</v>
+        <v>1263697183</v>
       </c>
       <c r="G391" t="n">
-        <v>209942150</v>
+        <v>293919010</v>
       </c>
       <c r="H391" t="n">
-        <v>1536621978</v>
+        <v>1557616193</v>
       </c>
       <c r="J391" t="n">
-        <v>52485538</v>
+        <v>73479753</v>
       </c>
       <c r="K391" t="n">
-        <v>0.03536436147500805</v>
+        <v>0.04951010606501131</v>
       </c>
     </row>
     <row r="392">
@@ -57074,22 +57061,22 @@
         <v>1176</v>
       </c>
       <c r="F392" t="n">
-        <v>1021</v>
+        <v>959</v>
       </c>
       <c r="G392" t="n">
-        <v>206</v>
+        <v>289</v>
       </c>
       <c r="H392" t="n">
-        <v>1227</v>
+        <v>1248</v>
       </c>
       <c r="I392" t="n">
-        <v>0.151732245857673</v>
+        <v>0.2261508976414909</v>
       </c>
       <c r="J392" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="K392" t="n">
-        <v>0.04391421310621286</v>
+        <v>0.06147989834869808</v>
       </c>
     </row>
     <row r="393">
@@ -57117,19 +57104,19 @@
         <v>2527811439</v>
       </c>
       <c r="F393" t="n">
-        <v>2194790889</v>
+        <v>2061582668</v>
       </c>
       <c r="G393" t="n">
-        <v>444027401</v>
+        <v>621638361</v>
       </c>
       <c r="H393" t="n">
-        <v>2638818290</v>
+        <v>2683221030</v>
       </c>
       <c r="J393" t="n">
-        <v>111006850</v>
+        <v>155409590</v>
       </c>
       <c r="K393" t="n">
-        <v>0.04391421310621289</v>
+        <v>0.06147989834869816</v>
       </c>
     </row>
     <row r="394">
@@ -57197,22 +57184,22 @@
         <v>2120194915</v>
       </c>
       <c r="F395" t="n">
-        <v>1811842553</v>
+        <v>1688501608</v>
       </c>
       <c r="G395" t="n">
-        <v>411136482</v>
+        <v>575591075</v>
       </c>
       <c r="H395" t="n">
-        <v>2222979035</v>
+        <v>2264092684</v>
       </c>
       <c r="I395" t="n">
-        <v>0.1701871728580487</v>
+        <v>0.2556665059372509</v>
       </c>
       <c r="J395" t="n">
-        <v>102784121</v>
+        <v>143897769</v>
       </c>
       <c r="K395" t="n">
-        <v>0.04847861857927857</v>
+        <v>0.06787006601098983</v>
       </c>
     </row>
     <row r="396">
@@ -57240,19 +57227,19 @@
         <v>636058474</v>
       </c>
       <c r="F396" t="n">
-        <v>548145370</v>
+        <v>512980129</v>
       </c>
       <c r="G396" t="n">
-        <v>117217472</v>
+        <v>164104461</v>
       </c>
       <c r="H396" t="n">
-        <v>665362842</v>
+        <v>677084590</v>
       </c>
       <c r="J396" t="n">
-        <v>29304368</v>
+        <v>41026115</v>
       </c>
       <c r="K396" t="n">
-        <v>0.0460718144459022</v>
+        <v>0.06450054022426294</v>
       </c>
     </row>
     <row r="397">
@@ -57280,19 +57267,19 @@
         <v>1484136440</v>
       </c>
       <c r="F397" t="n">
-        <v>1263697183</v>
+        <v>1175521480</v>
       </c>
       <c r="G397" t="n">
-        <v>293919010</v>
+        <v>411486614</v>
       </c>
       <c r="H397" t="n">
-        <v>1557616193</v>
+        <v>1587008094</v>
       </c>
       <c r="J397" t="n">
-        <v>73479753</v>
+        <v>102871654</v>
       </c>
       <c r="K397" t="n">
-        <v>0.04951010606501131</v>
+        <v>0.06931414849101564</v>
       </c>
     </row>
     <row r="398">
@@ -58101,19 +58088,19 @@
         <v>75888423</v>
       </c>
       <c r="F417" t="n">
-        <v>54445247</v>
+        <v>62230899</v>
       </c>
       <c r="G417" t="n">
-        <v>42886353</v>
+        <v>27315049</v>
       </c>
       <c r="H417" t="n">
-        <v>97331600</v>
+        <v>89545948</v>
       </c>
       <c r="J417" t="n">
-        <v>21443177</v>
+        <v>13657524</v>
       </c>
       <c r="K417" t="n">
-        <v>0.2825618945102262</v>
+        <v>0.1799684814144309</v>
       </c>
     </row>
     <row r="418">
@@ -58181,22 +58168,22 @@
         <v>62267631</v>
       </c>
       <c r="F419" t="n">
-        <v>42412838</v>
+        <v>49621775</v>
       </c>
       <c r="G419" t="n">
-        <v>39709586</v>
+        <v>25291712</v>
       </c>
       <c r="H419" t="n">
-        <v>82122424</v>
+        <v>74913487</v>
       </c>
       <c r="I419" t="n">
-        <v>0.468131686473101</v>
+        <v>0.2548448908599421</v>
       </c>
       <c r="J419" t="n">
-        <v>19854793</v>
+        <v>12645856</v>
       </c>
       <c r="K419" t="n">
-        <v>0.3188621911687605</v>
+        <v>0.2030887583925193</v>
       </c>
     </row>
     <row r="420">
@@ -58224,19 +58211,19 @@
         <v>21170994</v>
       </c>
       <c r="F420" t="n">
-        <v>14765137</v>
+        <v>17090994</v>
       </c>
       <c r="G420" t="n">
-        <v>12811716</v>
+        <v>8160000</v>
       </c>
       <c r="H420" t="n">
-        <v>27576852</v>
+        <v>25250994</v>
       </c>
       <c r="J420" t="n">
-        <v>6405858</v>
+        <v>4080000</v>
       </c>
       <c r="K420" t="n">
-        <v>0.3025770928492441</v>
+        <v>0.1927165020083802</v>
       </c>
     </row>
     <row r="421">
@@ -58264,19 +58251,19 @@
         <v>41096636</v>
       </c>
       <c r="F421" t="n">
-        <v>27647701</v>
+        <v>32530781</v>
       </c>
       <c r="G421" t="n">
-        <v>26897870</v>
+        <v>17131712</v>
       </c>
       <c r="H421" t="n">
-        <v>54545572</v>
+        <v>49662492</v>
       </c>
       <c r="J421" t="n">
-        <v>13448935</v>
+        <v>8565856</v>
       </c>
       <c r="K421" t="n">
-        <v>0.3272514842424508</v>
+        <v>0.2084320419843486</v>
       </c>
     </row>
     <row r="422">
@@ -58347,19 +58334,19 @@
         <v>75888423</v>
       </c>
       <c r="F423" t="n">
-        <v>40149796</v>
+        <v>53125883</v>
       </c>
       <c r="G423" t="n">
-        <v>71477256</v>
+        <v>45525081</v>
       </c>
       <c r="H423" t="n">
-        <v>111627051</v>
+        <v>98650964</v>
       </c>
       <c r="J423" t="n">
-        <v>35738628</v>
+        <v>22762540</v>
       </c>
       <c r="K423" t="n">
-        <v>0.4709364908503771</v>
+        <v>0.2999474690240516</v>
       </c>
     </row>
     <row r="424">
@@ -58427,22 +58414,22 @@
         <v>62267631</v>
       </c>
       <c r="F425" t="n">
-        <v>29176309</v>
+        <v>41191204</v>
       </c>
       <c r="G425" t="n">
-        <v>66182644</v>
+        <v>42152853</v>
       </c>
       <c r="H425" t="n">
-        <v>95358953</v>
+        <v>83344057</v>
       </c>
       <c r="I425" t="n">
-        <v>1.134184663721864</v>
+        <v>0.5116729815210443</v>
       </c>
       <c r="J425" t="n">
-        <v>33091322</v>
+        <v>21076426</v>
       </c>
       <c r="K425" t="n">
-        <v>0.5314369852812679</v>
+        <v>0.3384812639875324</v>
       </c>
     </row>
     <row r="426">
@@ -58470,19 +58457,19 @@
         <v>21170994</v>
       </c>
       <c r="F426" t="n">
-        <v>10494565</v>
+        <v>14370994</v>
       </c>
       <c r="G426" t="n">
-        <v>21352860</v>
+        <v>13600000</v>
       </c>
       <c r="H426" t="n">
-        <v>31847424</v>
+        <v>27970994</v>
       </c>
       <c r="J426" t="n">
-        <v>10676430</v>
+        <v>6800000</v>
       </c>
       <c r="K426" t="n">
-        <v>0.50429515474874</v>
+        <v>0.321194170013967</v>
       </c>
     </row>
     <row r="427">
@@ -58510,19 +58497,19 @@
         <v>41096636</v>
       </c>
       <c r="F427" t="n">
-        <v>18681744</v>
+        <v>26820210</v>
       </c>
       <c r="G427" t="n">
-        <v>44829784</v>
+        <v>28552853</v>
       </c>
       <c r="H427" t="n">
-        <v>63511528</v>
+        <v>55373063</v>
       </c>
       <c r="J427" t="n">
-        <v>22414892</v>
+        <v>14276426</v>
       </c>
       <c r="K427" t="n">
-        <v>0.5454191404040852</v>
+        <v>0.3473867366405812</v>
       </c>
     </row>
     <row r="428">
@@ -58593,19 +58580,19 @@
         <v>75888423</v>
       </c>
       <c r="F429" t="n">
-        <v>25854344</v>
+        <v>44020867</v>
       </c>
       <c r="G429" t="n">
-        <v>100068158</v>
+        <v>63735113</v>
       </c>
       <c r="H429" t="n">
-        <v>125922502</v>
+        <v>107755980</v>
       </c>
       <c r="J429" t="n">
-        <v>50034079</v>
+        <v>31867557</v>
       </c>
       <c r="K429" t="n">
-        <v>0.6593110871905274</v>
+        <v>0.4199264566336722</v>
       </c>
     </row>
     <row r="430">
@@ -58673,22 +58660,22 @@
         <v>62267631</v>
       </c>
       <c r="F431" t="n">
-        <v>15939780</v>
+        <v>32760634</v>
       </c>
       <c r="G431" t="n">
-        <v>92655702</v>
+        <v>59013994</v>
       </c>
       <c r="H431" t="n">
-        <v>108595482</v>
+        <v>91774628</v>
       </c>
       <c r="I431" t="n">
-        <v>2.906429747555666</v>
+        <v>0.9006845547437348</v>
       </c>
       <c r="J431" t="n">
-        <v>46327851</v>
+        <v>29506997</v>
       </c>
       <c r="K431" t="n">
-        <v>0.7440117793937748</v>
+        <v>0.4738737695825452</v>
       </c>
     </row>
     <row r="432">
@@ -58716,19 +58703,19 @@
         <v>21170994</v>
       </c>
       <c r="F432" t="n">
-        <v>6223993</v>
+        <v>11650994</v>
       </c>
       <c r="G432" t="n">
-        <v>29894004</v>
+        <v>19040000</v>
       </c>
       <c r="H432" t="n">
-        <v>36117996</v>
+        <v>30690994</v>
       </c>
       <c r="J432" t="n">
-        <v>14947002</v>
+        <v>9520000</v>
       </c>
       <c r="K432" t="n">
-        <v>0.7060132166482359</v>
+        <v>0.4496718380195538</v>
       </c>
     </row>
     <row r="433">
@@ -58756,19 +58743,19 @@
         <v>41096636</v>
       </c>
       <c r="F433" t="n">
-        <v>9715787</v>
+        <v>21109639</v>
       </c>
       <c r="G433" t="n">
-        <v>62761698</v>
+        <v>39973994</v>
       </c>
       <c r="H433" t="n">
-        <v>72477485</v>
+        <v>61083633</v>
       </c>
       <c r="J433" t="n">
-        <v>31380849</v>
+        <v>19986997</v>
       </c>
       <c r="K433" t="n">
-        <v>0.7635867965657192</v>
+        <v>0.4863414312968134</v>
       </c>
     </row>
     <row r="434">
@@ -63962,22 +63949,22 @@
         <v>12259</v>
       </c>
       <c r="F560" t="n">
-        <v>12147</v>
+        <v>12131</v>
       </c>
       <c r="G560" t="n">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="H560" t="n">
-        <v>12306</v>
+        <v>12314</v>
       </c>
       <c r="I560" t="n">
-        <v>0.009173261742669858</v>
+        <v>0.01056355923243675</v>
       </c>
       <c r="J560" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="K560" t="n">
-        <v>0.003895661962869184</v>
+        <v>0.004479915814976465</v>
       </c>
     </row>
     <row r="561">
@@ -64005,19 +63992,19 @@
         <v>3706659599</v>
       </c>
       <c r="F561" t="n">
-        <v>3696544189</v>
+        <v>3695027125</v>
       </c>
       <c r="G561" t="n">
-        <v>14450586</v>
+        <v>16617820</v>
       </c>
       <c r="H561" t="n">
-        <v>3710994775</v>
+        <v>3711644945</v>
       </c>
       <c r="J561" t="n">
-        <v>4335176</v>
+        <v>4985346</v>
       </c>
       <c r="K561" t="n">
-        <v>0.001169564025098758</v>
+        <v>0.001344969974963882</v>
       </c>
     </row>
     <row r="562">
@@ -64085,22 +64072,22 @@
         <v>3253253857</v>
       </c>
       <c r="F563" t="n">
-        <v>3243887736</v>
+        <v>3242483048</v>
       </c>
       <c r="G563" t="n">
-        <v>13380172</v>
+        <v>15386870</v>
       </c>
       <c r="H563" t="n">
-        <v>3257267908</v>
+        <v>3257869918</v>
       </c>
       <c r="I563" t="n">
-        <v>0.002887313354889094</v>
+        <v>0.003321778037116093</v>
       </c>
       <c r="J563" t="n">
-        <v>4014052</v>
+        <v>4616061</v>
       </c>
       <c r="K563" t="n">
-        <v>0.001233857476069519</v>
+        <v>0.001418905868413462</v>
       </c>
     </row>
     <row r="564">
@@ -64128,19 +64115,19 @@
         <v>1041041234</v>
       </c>
       <c r="F564" t="n">
-        <v>1038820765</v>
+        <v>1038487749</v>
       </c>
       <c r="G564" t="n">
-        <v>3172099</v>
+        <v>3647837</v>
       </c>
       <c r="H564" t="n">
-        <v>1041992864</v>
+        <v>1042135585</v>
       </c>
       <c r="J564" t="n">
-        <v>951630</v>
+        <v>1094351</v>
       </c>
       <c r="K564" t="n">
-        <v>0.0009141134811549318</v>
+        <v>0.001051208107875177</v>
       </c>
     </row>
     <row r="565">
@@ -64168,19 +64155,19 @@
         <v>2212212623</v>
       </c>
       <c r="F565" t="n">
-        <v>2205066972</v>
+        <v>2203995299</v>
       </c>
       <c r="G565" t="n">
-        <v>10208073</v>
+        <v>11739033</v>
       </c>
       <c r="H565" t="n">
-        <v>2215275044</v>
+        <v>2215734333</v>
       </c>
       <c r="J565" t="n">
-        <v>3062422</v>
+        <v>3521710</v>
       </c>
       <c r="K565" t="n">
-        <v>0.001384325238382266</v>
+        <v>0.001591940108666772</v>
       </c>
     </row>
     <row r="566">
@@ -64208,22 +64195,22 @@
         <v>12259</v>
       </c>
       <c r="F566" t="n">
-        <v>12073</v>
+        <v>12045</v>
       </c>
       <c r="G566" t="n">
-        <v>265</v>
+        <v>305</v>
       </c>
       <c r="H566" t="n">
-        <v>12338</v>
+        <v>12350</v>
       </c>
       <c r="I566" t="n">
-        <v>0.01538284347078574</v>
+        <v>0.01773079895069733</v>
       </c>
       <c r="J566" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K566" t="n">
-        <v>0.006492769938115357</v>
+        <v>0.007466526358294207</v>
       </c>
     </row>
     <row r="567">
@@ -64251,19 +64238,19 @@
         <v>3706659599</v>
       </c>
       <c r="F567" t="n">
-        <v>3689800582</v>
+        <v>3687272143</v>
       </c>
       <c r="G567" t="n">
-        <v>24084310</v>
+        <v>27696366</v>
       </c>
       <c r="H567" t="n">
-        <v>3713884892</v>
+        <v>3714968509</v>
       </c>
       <c r="J567" t="n">
-        <v>7225293</v>
+        <v>8308910</v>
       </c>
       <c r="K567" t="n">
-        <v>0.001949273375164726</v>
+        <v>0.002241616624939804</v>
       </c>
     </row>
     <row r="568">
@@ -64331,22 +64318,22 @@
         <v>3253253857</v>
       </c>
       <c r="F569" t="n">
-        <v>3237643656</v>
+        <v>3235302509</v>
       </c>
       <c r="G569" t="n">
-        <v>22300287</v>
+        <v>25644783</v>
       </c>
       <c r="H569" t="n">
-        <v>3259943943</v>
+        <v>3260947292</v>
       </c>
       <c r="I569" t="n">
-        <v>0.004821469653963309</v>
+        <v>0.005548584171886281</v>
       </c>
       <c r="J569" t="n">
-        <v>6690086</v>
+        <v>7693435</v>
       </c>
       <c r="K569" t="n">
-        <v>0.002056429126782434</v>
+        <v>0.002364843114022534</v>
       </c>
     </row>
     <row r="570">
@@ -64374,19 +64361,19 @@
         <v>1041041234</v>
       </c>
       <c r="F570" t="n">
-        <v>1037340452</v>
+        <v>1036785425</v>
       </c>
       <c r="G570" t="n">
-        <v>5286832</v>
+        <v>6079728</v>
       </c>
       <c r="H570" t="n">
-        <v>1042627284</v>
+        <v>1042865152</v>
       </c>
       <c r="J570" t="n">
-        <v>1586050</v>
+        <v>1823918</v>
       </c>
       <c r="K570" t="n">
-        <v>0.0015235224685914</v>
+        <v>0.001752013513125258</v>
       </c>
     </row>
     <row r="571">
@@ -64414,19 +64401,19 @@
         <v>2212212623</v>
       </c>
       <c r="F571" t="n">
-        <v>2200303205</v>
+        <v>2198517084</v>
       </c>
       <c r="G571" t="n">
-        <v>17013454</v>
+        <v>19565056</v>
       </c>
       <c r="H571" t="n">
-        <v>2217316659</v>
+        <v>2218082139</v>
       </c>
       <c r="J571" t="n">
-        <v>5104036</v>
+        <v>5869517</v>
       </c>
       <c r="K571" t="n">
-        <v>0.002307208730637254</v>
+        <v>0.002653233514444836</v>
       </c>
     </row>
     <row r="572">
@@ -64454,22 +64441,22 @@
         <v>12259</v>
       </c>
       <c r="F572" t="n">
-        <v>11999</v>
+        <v>11960</v>
       </c>
       <c r="G572" t="n">
-        <v>371</v>
+        <v>427</v>
       </c>
       <c r="H572" t="n">
-        <v>12370</v>
+        <v>12387</v>
       </c>
       <c r="I572" t="n">
-        <v>0.02166931513221923</v>
+        <v>0.02500042956711046</v>
       </c>
       <c r="J572" t="n">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="K572" t="n">
-        <v>0.009089877913361528</v>
+        <v>0.0104531369016118</v>
       </c>
     </row>
     <row r="573">
@@ -64497,19 +64484,19 @@
         <v>3706659599</v>
       </c>
       <c r="F573" t="n">
-        <v>3683056976</v>
+        <v>3679517160</v>
       </c>
       <c r="G573" t="n">
-        <v>33718033</v>
+        <v>38774912</v>
       </c>
       <c r="H573" t="n">
-        <v>3716775009</v>
+        <v>3718292073</v>
       </c>
       <c r="J573" t="n">
-        <v>10115410</v>
+        <v>11632474</v>
       </c>
       <c r="K573" t="n">
-        <v>0.002728982725230694</v>
+        <v>0.003138263274915596</v>
       </c>
     </row>
     <row r="574">
@@ -64577,22 +64564,22 @@
         <v>3253253857</v>
       </c>
       <c r="F575" t="n">
-        <v>3231399576</v>
+        <v>3228121969</v>
       </c>
       <c r="G575" t="n">
-        <v>31220401</v>
+        <v>35902697</v>
       </c>
       <c r="H575" t="n">
-        <v>3262619977</v>
+        <v>3264024666</v>
       </c>
       <c r="I575" t="n">
-        <v>0.006763100749560826</v>
+        <v>0.007785296790458754</v>
       </c>
       <c r="J575" t="n">
-        <v>9366120</v>
+        <v>10770809</v>
       </c>
       <c r="K575" t="n">
-        <v>0.002879000777495496</v>
+        <v>0.003310780359631607</v>
       </c>
     </row>
     <row r="576">
@@ -64620,19 +64607,19 @@
         <v>1041041234</v>
       </c>
       <c r="F576" t="n">
-        <v>1035860138</v>
+        <v>1035083101</v>
       </c>
       <c r="G576" t="n">
-        <v>7401565</v>
+        <v>8511619</v>
       </c>
       <c r="H576" t="n">
-        <v>1043261704</v>
+        <v>1043594720</v>
       </c>
       <c r="J576" t="n">
-        <v>2220470</v>
+        <v>2553486</v>
       </c>
       <c r="K576" t="n">
-        <v>0.002132931456027983</v>
+        <v>0.002452818918375223</v>
       </c>
     </row>
     <row r="577">
@@ -64660,19 +64647,19 @@
         <v>2212212623</v>
       </c>
       <c r="F577" t="n">
-        <v>2195539437</v>
+        <v>2193038868</v>
       </c>
       <c r="G577" t="n">
-        <v>23818836</v>
+        <v>27391078</v>
       </c>
       <c r="H577" t="n">
-        <v>2219358273</v>
+        <v>2220429946</v>
       </c>
       <c r="J577" t="n">
-        <v>7145651</v>
+        <v>8217323</v>
       </c>
       <c r="K577" t="n">
-        <v>0.003230092222892026</v>
+        <v>0.0037145269202229</v>
       </c>
     </row>
     <row r="578">
@@ -68506,38 +68493,38 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="G2" t="n">
-        <v>2150254</v>
+        <v>1177008</v>
       </c>
       <c r="H2" t="n">
-        <v>244330</v>
+        <v>122165</v>
       </c>
       <c r="I2" t="n">
-        <v>1905924</v>
+        <v>1054843</v>
       </c>
       <c r="J2" t="n">
-        <v>1905924</v>
+        <v>1054843</v>
       </c>
       <c r="K2" t="n">
-        <v>719010</v>
+        <v>393572</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4074299140622685</v>
+        <v>0.4029584916980989</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5925700859377315</v>
+        <v>0.5970415083019012</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>226232</v>
+        <v>113116</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>giá trị hoá đơn = AOV nền 1.892.130 · u khách sẵn có = +0% (0)</t>
+          <t>giá trị hoá đơn = nhập ở sổ 1.035.716 · u khách sẵn có = +0% (0)</t>
         </is>
       </c>
     </row>
@@ -69129,29 +69116,35 @@
         <v>431</v>
       </c>
       <c r="G12" t="n">
-        <v>398645</v>
+        <v>252165</v>
       </c>
       <c r="H12" t="n">
-        <v>398645</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>252165</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>252165</v>
       </c>
       <c r="K12" t="n">
         <v>66810</v>
       </c>
+      <c r="L12" t="n">
+        <v>0.2861393138007395</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.7138606861992605</v>
+      </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>369116</v>
+        <v>0</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>giá trị hoá đơn = giá bộ món chương trình 352.064 · u khách sẵn có = +18% (set: 1 − TA × khách ÷ V)</t>
+          <t>giá trị hoá đơn = nhập ở sổ 222.700 · u khách sẵn có = -30% (set: 1 − TA × khách ÷ V)</t>
         </is>
       </c>
     </row>
@@ -69368,7 +69361,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G16" t="n">
         <v>1088189</v>
@@ -69430,7 +69423,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>356</v>
+        <v>444</v>
       </c>
       <c r="G17" t="n">
         <v>744366</v>
@@ -69622,28 +69615,28 @@
         <v>534111</v>
       </c>
       <c r="H20" t="n">
-        <v>53411</v>
+        <v>32047</v>
       </c>
       <c r="I20" t="n">
-        <v>480700</v>
+        <v>502064</v>
       </c>
       <c r="J20" t="n">
-        <v>480700</v>
+        <v>502064</v>
       </c>
       <c r="K20" t="n">
         <v>162203</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3644260742958461</v>
+        <v>0.3489185817726186</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6355739257041539</v>
+        <v>0.6510814182273814</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>49455</v>
+        <v>29673</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
@@ -70174,7 +70167,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G29" t="n">
         <v>2150254</v>
@@ -70236,7 +70229,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>129</v>
+        <v>180</v>
       </c>
       <c r="G30" t="n">
         <v>2150254</v>
@@ -70425,19 +70418,19 @@
         <v>31</v>
       </c>
       <c r="G33" t="n">
-        <v>2287272</v>
+        <v>1456803</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>2287272</v>
+        <v>1456803</v>
       </c>
       <c r="J33" t="n">
-        <v>2287272</v>
+        <v>1456803</v>
       </c>
       <c r="K33" t="n">
-        <v>683292</v>
+        <v>435200</v>
       </c>
       <c r="L33" t="n">
         <v>0.3226353403382805</v>
@@ -70453,7 +70446,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>giá trị hoá đơn = AOV nền 2.009.681 · u khách sẵn có = +0% (0)</t>
+          <t>giá trị hoá đơn = nhập ở sổ 1.280.000 · u khách sẵn có = +0% (0)</t>
         </is>
       </c>
     </row>
@@ -70918,7 +70911,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>265</v>
+        <v>305</v>
       </c>
       <c r="G41" t="n">
         <v>90778</v>
@@ -75884,7 +75877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I105"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -75953,7 +75946,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HOA_VON</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -75965,10 +75958,10 @@
         <v>0.8</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7824167952450807</v>
+        <v>0.741333714319626</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02197900594364921</v>
+        <v>0.07333285710046752</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -75978,7 +75971,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>%cannib từ 80% xuống ≤ 78% — chỉ áp cho khách đặt trước / nhóm mới / khung giờ yếu</t>
+          <t>%cannib từ 80% xuống ≤ 74% — chỉ áp cho khách đặt trước / nhóm mới / khung giờ yếu</t>
         </is>
       </c>
     </row>
@@ -75990,7 +75983,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HOA_VON</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -75999,13 +75992,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>226231.658550881</v>
+        <v>113115.8292754405</v>
       </c>
       <c r="E3" t="n">
-        <v>205071.1228307095</v>
+        <v>84027.62981340164</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09353481230573379</v>
+        <v>0.2571541016704941</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -76015,7 +76008,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>chi ưu đãi/HĐ từ 226.232 xuống ≤ 205.071 (−9%)</t>
+          <t>chi ưu đãi/HĐ từ 113.116 xuống ≤ 84.028 (−26%)</t>
         </is>
       </c>
     </row>
@@ -76027,7 +76020,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HOA_VON</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -76036,13 +76029,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2150253.757683252</v>
+        <v>1177007.852767903</v>
       </c>
       <c r="E4" t="n">
-        <v>2188062.109780413</v>
+        <v>1246058.531706428</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01758320475528308</v>
+        <v>0.05866628568037413</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -76052,7 +76045,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>giá trị HĐ tham gia từ 2.150.254 lên ≥ 2.188.062 (+2%)</t>
+          <t>giá trị HĐ tham gia từ 1.177.008 lên ≥ 1.246.059 (+6%)</t>
         </is>
       </c>
     </row>
@@ -76064,7 +76057,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HOA_VON</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -76073,23 +76066,17 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2029616.248946695</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.594076750210661</v>
+        <v>2500000</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>chi phí cố định từ 5.000.000 xuống ≤ 2.029.616 (cắt 2.970.384)</t>
+          <t>cắt hết chi phí cố định vẫn chưa đủ</t>
         </is>
       </c>
     </row>
@@ -76101,7 +76088,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HOA_VON</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -76110,35 +76097,29 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>153.75</v>
-      </c>
-      <c r="E6" t="n">
-        <v>378.7661832121694</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1.463519890810858</v>
+        <v>177</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>hoá đơn tham gia từ 154 lên ≥ 379 (+146%)</t>
+          <t>tăng số hoá đơn gấp 10 vẫn chưa đạt — phải sửa lãi trên mỗi hoá đơn trước</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NJFB-2026Q4-SETLUNCH</t>
+          <t>ALL-2026-06-LTOSUMMER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DUYET</t>
+          <t>HOA_VON</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -76147,13 +76128,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7117678731432535</v>
+        <v>0.5118397859596369</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1102901585709332</v>
+        <v>0.1469336900672719</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -76163,19 +76144,19 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>%cannib từ 80% xuống ≤ 71% — chỉ áp cho khách đặt trước / nhóm mới / khung giờ yếu</t>
+          <t>%cannib từ 60% xuống ≤ 51% — chỉ áp cho khách đặt trước / nhóm mới / khung giờ yếu</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NJFB-2026Q4-SETLUNCH</t>
+          <t>ALL-2026-06-LTOSUMMER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DUYET</t>
+          <t>HOA_VON</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -76184,13 +76165,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>226231.658550881</v>
+        <v>72360</v>
       </c>
       <c r="E8" t="n">
-        <v>146309.8413711697</v>
+        <v>53272.11323394979</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3532742397401307</v>
+        <v>0.2637905854899145</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -76200,19 +76181,19 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>chi ưu đãi/HĐ từ 226.232 xuống ≤ 146.310 (−35%)</t>
+          <t>chi ưu đãi/HĐ từ 72.360 xuống ≤ 53.272 (−26%)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NJFB-2026Q4-SETLUNCH</t>
+          <t>ALL-2026-06-LTOSUMMER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DUYET</t>
+          <t>HOA_VON</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -76221,13 +76202,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2150253.757683252</v>
+        <v>386781.4543010828</v>
       </c>
       <c r="E9" t="n">
-        <v>2339975.220010441</v>
+        <v>423267.2021833651</v>
       </c>
       <c r="F9" t="n">
-        <v>0.08823212685911129</v>
+        <v>0.09433168906252831</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
@@ -76237,19 +76218,19 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>giá trị HĐ tham gia từ 2.150.254 lên ≥ 2.339.975 (+9%)</t>
+          <t>giá trị HĐ tham gia từ 386.781 lên ≥ 423.267 (+9%)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NJFB-2026Q4-SETLUNCH</t>
+          <t>ALL-2026-06-LTOSUMMER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DUYET</t>
+          <t>HOA_VON</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -76258,29 +76239,35 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5000000</v>
+        <v>20000000</v>
+      </c>
+      <c r="E10" t="n">
+        <v>8547267.940357413</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.5726366029821294</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>cắt hết chi phí cố định vẫn chưa đủ</t>
+          <t>chi phí cố định từ 20.000.000 xuống ≤ 8.547.268 (cắt 11.452.732)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NJFB-2026Q4-SETLUNCH</t>
+          <t>ALL-2026-06-LTOSUMMER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DUYET</t>
+          <t>HOA_VON</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -76289,7 +76276,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>153.75</v>
+        <v>600</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -76311,7 +76298,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HOA_VON</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -76323,20 +76310,20 @@
         <v>0.6</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5118397859596369</v>
+        <v>0.3653917217472553</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1469336900672719</v>
+        <v>0.3910137970879078</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>%cannib từ 60% xuống ≤ 51% — chỉ áp cho khách đặt trước / nhóm mới / khung giờ yếu</t>
+          <t>%cannib từ 60% xuống ≤ 37% — chỉ áp cho khách đặt trước / nhóm mới / khung giờ yếu</t>
         </is>
       </c>
     </row>
@@ -76348,7 +76335,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HOA_VON</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -76360,20 +76347,20 @@
         <v>72360</v>
       </c>
       <c r="E13" t="n">
-        <v>53272.11323394979</v>
+        <v>31532.29737785085</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2637905854899145</v>
+        <v>0.5642302739379375</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>chi ưu đãi/HĐ từ 72.360 xuống ≤ 53.272 (−26%)</t>
+          <t>chi ưu đãi/HĐ từ 72.360 xuống ≤ 31.532 (−56%)</t>
         </is>
       </c>
     </row>
@@ -76385,7 +76372,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HOA_VON</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -76397,10 +76384,10 @@
         <v>386781.4543010828</v>
       </c>
       <c r="E14" t="n">
-        <v>423267.2021833651</v>
+        <v>483875.8021836522</v>
       </c>
       <c r="F14" t="n">
-        <v>0.09433168906252831</v>
+        <v>0.2510315497365809</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
@@ -76410,7 +76397,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>giá trị HĐ tham gia từ 386.781 lên ≥ 423.267 (+9%)</t>
+          <t>giá trị HĐ tham gia từ 386.781 lên ≥ 483.876 (+25%)</t>
         </is>
       </c>
     </row>
@@ -76422,7 +76409,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HOA_VON</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -76433,21 +76420,15 @@
       <c r="D15" t="n">
         <v>20000000</v>
       </c>
-      <c r="E15" t="n">
-        <v>8547267.940357413</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.5726366029821294</v>
-      </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>chi phí cố định từ 20.000.000 xuống ≤ 8.547.268 (cắt 11.452.732)</t>
+          <t>cắt hết chi phí cố định vẫn chưa đủ</t>
         </is>
       </c>
     </row>
@@ -76459,7 +76440,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HOA_VON</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -76485,12 +76466,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ALL-2026-06-LTOSUMMER</t>
+          <t>NDC-2026-09-PREBOOK15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DUYET</t>
+          <t>HOA_VON</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -76499,13 +76480,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3653917217472553</v>
+        <v>0.5886299769881589</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3910137970879078</v>
+        <v>0.2642125287648014</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -76515,19 +76496,19 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>%cannib từ 60% xuống ≤ 37% — chỉ áp cho khách đặt trước / nhóm mới / khung giờ yếu</t>
+          <t>%cannib từ 80% xuống ≤ 59% — chỉ áp cho khách đặt trước / nhóm mới / khung giờ yếu</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ALL-2026-06-LTOSUMMER</t>
+          <t>NDC-2026-09-PREBOOK15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DUYET</t>
+          <t>HOA_VON</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -76536,13 +76517,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>72360</v>
+        <v>93696.5175946434</v>
       </c>
       <c r="E18" t="n">
-        <v>31532.29737785085</v>
+        <v>7181.920407068988</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5642302739379375</v>
+        <v>0.9233491212753506</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -76552,19 +76533,19 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>chi ưu đãi/HĐ từ 72.360 xuống ≤ 31.532 (−56%)</t>
+          <t>chi ưu đãi/HĐ từ 93.697 xuống ≤ 7.182 (−92%)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ALL-2026-06-LTOSUMMER</t>
+          <t>NDC-2026-09-PREBOOK15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DUYET</t>
+          <t>HOA_VON</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -76573,13 +76554,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>386781.4543010828</v>
+        <v>674614.9266814325</v>
       </c>
       <c r="E19" t="n">
-        <v>483875.8021836522</v>
+        <v>817208.2992595682</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2510315497365809</v>
+        <v>0.211370023013842</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
@@ -76589,19 +76570,19 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>giá trị HĐ tham gia từ 386.781 lên ≥ 483.876 (+25%)</t>
+          <t>giá trị HĐ tham gia từ 674.615 lên ≥ 817.208 (+21%)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ALL-2026-06-LTOSUMMER</t>
+          <t>NDC-2026-09-PREBOOK15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DUYET</t>
+          <t>HOA_VON</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -76610,7 +76591,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>20000000</v>
+        <v>3000000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -76627,12 +76608,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ALL-2026-06-LTOSUMMER</t>
+          <t>NDC-2026-09-PREBOOK15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DUYET</t>
+          <t>HOA_VON</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -76641,7 +76622,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>600</v>
+        <v>44</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -76663,7 +76644,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HOA_VON</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -76675,10 +76656,10 @@
         <v>0.8</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5886299769881589</v>
+        <v>0.4586749114154374</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2642125287648014</v>
+        <v>0.4266563607307033</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -76688,7 +76669,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>%cannib từ 80% xuống ≤ 59% — chỉ áp cho khách đặt trước / nhóm mới / khung giờ yếu</t>
+          <t>%cannib từ 80% xuống ≤ 46% — chỉ áp cho khách đặt trước / nhóm mới / khung giờ yếu</t>
         </is>
       </c>
     </row>
@@ -76700,7 +76681,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HOA_VON</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -76711,21 +76692,15 @@
       <c r="D23" t="n">
         <v>93696.5175946434</v>
       </c>
-      <c r="E23" t="n">
-        <v>7181.920407068988</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.9233491212753506</v>
-      </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>chi ưu đãi/HĐ từ 93.697 xuống ≤ 7.182 (−92%)</t>
+          <t>bỏ hẳn ưu đãi vẫn chưa đủ</t>
         </is>
       </c>
     </row>
@@ -76737,7 +76712,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HOA_VON</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -76749,10 +76724,10 @@
         <v>674614.9266814325</v>
       </c>
       <c r="E24" t="n">
-        <v>817208.2992595682</v>
+        <v>904877.9262918091</v>
       </c>
       <c r="F24" t="n">
-        <v>0.211370023013842</v>
+        <v>0.3413250885851085</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -76762,7 +76737,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>giá trị HĐ tham gia từ 674.615 lên ≥ 817.208 (+21%)</t>
+          <t>giá trị HĐ tham gia từ 674.615 lên ≥ 904.878 (+34%)</t>
         </is>
       </c>
     </row>
@@ -76774,7 +76749,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HOA_VON</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -76805,7 +76780,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HOA_VON</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -76831,7 +76806,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NDC-2026-09-PREBOOK15</t>
+          <t>NDC-2026-10-KHUNGSANG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -76845,30 +76820,30 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4586749114154374</v>
+        <v>0.6682653807270071</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4266563607307033</v>
+        <v>0.04533517038998974</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>%cannib từ 80% xuống ≤ 46% — chỉ áp cho khách đặt trước / nhóm mới / khung giờ yếu</t>
+          <t>%cannib từ 70% xuống ≤ 67% — chỉ áp cho khách đặt trước / nhóm mới / khung giờ yếu</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NDC-2026-09-PREBOOK15</t>
+          <t>NDC-2026-10-KHUNGSANG</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -76882,24 +76857,30 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>93696.5175946434</v>
+        <v>29178.53603783593</v>
+      </c>
+      <c r="E28" t="n">
+        <v>25332.69224459571</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.1318038639174119</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>bỏ hẳn ưu đãi vẫn chưa đủ</t>
+          <t>chi ưu đãi/HĐ từ 29.179 xuống ≤ 25.333 (−13%)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NDC-2026-09-PREBOOK15</t>
+          <t>NDC-2026-10-KHUNGSANG</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -76913,13 +76894,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>674614.9266814325</v>
+        <v>412722.5128278467</v>
       </c>
       <c r="E29" t="n">
-        <v>904877.9262918091</v>
+        <v>420972.4491398397</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3413250885851085</v>
+        <v>0.01998906300377712</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
@@ -76929,14 +76910,14 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>giá trị HĐ tham gia từ 674.615 lên ≥ 904.878 (+34%)</t>
+          <t>giá trị HĐ tham gia từ 412.723 lên ≥ 420.972 (+2%)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>NDC-2026-09-PREBOOK15</t>
+          <t>NDC-2026-10-KHUNGSANG</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -76950,24 +76931,30 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3000000</v>
+        <v>13000000</v>
+      </c>
+      <c r="E30" t="n">
+        <v>8464642.873484991</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.3488736251165392</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>cắt hết chi phí cố định vẫn chưa đủ</t>
+          <t>chi phí cố định từ 13.000.000 xuống ≤ 8.464.643 (cắt 4.535.357)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>NDC-2026-09-PREBOOK15</t>
+          <t>NDC-2026-10-KHUNGSANG</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -76981,24 +76968,30 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>44</v>
+        <v>1231.27</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1890.984680538403</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.5358001742415581</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>tăng số hoá đơn gấp 10 vẫn chưa đạt — phải sửa lãi trên mỗi hoá đơn trước</t>
+          <t>hoá đơn tham gia từ 1.231 lên ≥ 1.891 (+54%)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NDC-2026-10-KHUNGSANG</t>
+          <t>NDC-2026-11-WINTERNIGHTS</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -77012,13 +77005,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="E32" t="n">
-        <v>0.6682653807270071</v>
+        <v>0.5987515490244277</v>
       </c>
       <c r="F32" t="n">
-        <v>0.04533517038998974</v>
+        <v>0.201664601300763</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
@@ -77028,14 +77021,14 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>%cannib từ 70% xuống ≤ 67% — chỉ áp cho khách đặt trước / nhóm mới / khung giờ yếu</t>
+          <t>%cannib từ 75% xuống ≤ 60% — chỉ áp cho khách đặt trước / nhóm mới / khung giờ yếu</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NDC-2026-10-KHUNGSANG</t>
+          <t>NDC-2026-11-WINTERNIGHTS</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -77045,34 +77038,34 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PROMO</t>
+          <t>VALUE</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>29178.53603783593</v>
+        <v>916277.1441133452</v>
       </c>
       <c r="E33" t="n">
-        <v>25332.69224459571</v>
+        <v>1029932.809122064</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1318038639174119</v>
+        <v>0.1240407072673406</v>
       </c>
       <c r="G33" t="n">
         <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>chi ưu đãi/HĐ từ 29.179 xuống ≤ 25.333 (−13%)</t>
+          <t>giá trị HĐ tham gia từ 916.277 lên ≥ 1.029.933 (+12%)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NDC-2026-10-KHUNGSANG</t>
+          <t>NDC-2026-11-WINTERNIGHTS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -77082,34 +77075,34 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>VALUE</t>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>412722.5128278467</v>
+        <v>45500000</v>
       </c>
       <c r="E34" t="n">
-        <v>420972.4491398397</v>
+        <v>28349019.09861446</v>
       </c>
       <c r="F34" t="n">
-        <v>0.01998906300377712</v>
+        <v>0.3769446351952865</v>
       </c>
       <c r="G34" t="n">
         <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>giá trị HĐ tham gia từ 412.723 lên ≥ 420.972 (+2%)</t>
+          <t>chi phí cố định từ 45.500.000 xuống ≤ 28.349.019 (cắt 17.150.981)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NDC-2026-10-KHUNGSANG</t>
+          <t>NDC-2026-11-WINTERNIGHTS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -77119,17 +77112,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FIXED</t>
+          <t>BILLS</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13000000</v>
+        <v>453.78</v>
       </c>
       <c r="E35" t="n">
-        <v>8464642.873484991</v>
+        <v>728.3140883360189</v>
       </c>
       <c r="F35" t="n">
-        <v>0.3488736251165392</v>
+        <v>0.6049938039050176</v>
       </c>
       <c r="G35" t="n">
         <v>1</v>
@@ -77139,14 +77132,14 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>chi phí cố định từ 13.000.000 xuống ≤ 8.464.643 (cắt 4.535.357)</t>
+          <t>hoá đơn tham gia từ 454 lên ≥ 728 (+60%)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NDC-2026-10-KHUNGSANG</t>
+          <t>ALL-2026-10-LOYALTY</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -77156,17 +77149,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BILLS</t>
+          <t>CANNIB</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1231.27</v>
+        <v>0.9</v>
       </c>
       <c r="E36" t="n">
-        <v>1890.984680538403</v>
+        <v>0.8750380448490431</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5358001742415581</v>
+        <v>0.02773550572328544</v>
       </c>
       <c r="G36" t="n">
         <v>1</v>
@@ -77176,187 +77169,193 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>hoá đơn tham gia từ 1.231 lên ≥ 1.891 (+54%)</t>
+          <t>%cannib từ 90% xuống ≤ 88% — chỉ áp cho khách đặt trước / nhóm mới / khung giờ yếu</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>NDC-2026-09-SETLUNCH199</t>
+          <t>ALL-2026-10-LOYALTY</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HOA_VON</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CANNIB</t>
+          <t>PROMO</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.2</v>
+        <v>29672.81940574863</v>
       </c>
       <c r="E37" t="n">
-        <v>0.005312887633044739</v>
+        <v>23745.4826710948</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9734355618347763</v>
+        <v>0.1997564388339015</v>
       </c>
       <c r="G37" t="n">
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>%cannib từ 20% xuống ≤ 1% — chỉ áp cho khách đặt trước / nhóm mới / khung giờ yếu</t>
+          <t>chi ưu đãi/HĐ từ 29.673 xuống ≤ 23.745 (−20%)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NDC-2026-09-SETLUNCH199</t>
+          <t>ALL-2026-10-LOYALTY</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HOA_VON</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PROMO</t>
+          <t>VALUE</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>224795.6955097141</v>
+        <v>534110.7493034754</v>
       </c>
       <c r="E38" t="n">
-        <v>179295.2638801213</v>
+        <v>547443.1978739613</v>
       </c>
       <c r="F38" t="n">
-        <v>0.2024079310167508</v>
+        <v>0.02496195515232103</v>
       </c>
       <c r="G38" t="n">
         <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>chi ưu đãi/HĐ từ 224.796 xuống ≤ 179.295 (−20%)</t>
+          <t>giá trị HĐ tham gia từ 534.111 lên ≥ 547.443 (+2%)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>NDC-2026-09-SETLUNCH199</t>
+          <t>ALL-2026-10-LOYALTY</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HOA_VON</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>VALUE</t>
+          <t>BILLS</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>311987.1864169043</v>
-      </c>
-      <c r="E39" t="n">
-        <v>383715.6144708132</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.2299082500076111</v>
+        <v>3335.955259113301</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>giá trị HĐ tham gia từ 311.987 lên ≥ 383.716 (+23%)</t>
+          <t>tăng số hoá đơn gấp 10 vẫn chưa đạt — phải sửa lãi trên mỗi hoá đơn trước</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NDC-2026-09-SETLUNCH199</t>
+          <t>NJFB-2026-11-NIGHTOFLIGHTS</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HOA_VON</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FIXED</t>
+          <t>CANNIB</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>5000000</v>
+        <v>0.75</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.5990705197323223</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.2012393070235703</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>cắt hết chi phí cố định vẫn chưa đủ</t>
+          <t>%cannib từ 75% xuống ≤ 60% — chỉ áp cho khách đặt trước / nhóm mới / khung giờ yếu</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>NDC-2026-09-SETLUNCH199</t>
+          <t>NJFB-2026-11-NIGHTOFLIGHTS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HOA_VON</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BILLS</t>
+          <t>VALUE</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>723.6799999999999</v>
+        <v>2150253.757683252</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2474790.439776939</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.150929480269042</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>tăng số hoá đơn gấp 10 vẫn chưa đạt — phải sửa lãi trên mỗi hoá đơn trước</t>
+          <t>giá trị HĐ tham gia từ 2.150.254 lên ≥ 2.474.790 (+15%)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NDC-2026-09-SETLUNCH199</t>
+          <t>NJFB-2026-11-NIGHTOFLIGHTS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -77366,28 +77365,34 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CANNIB</t>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.2</v>
+        <v>62100000</v>
+      </c>
+      <c r="E42" t="n">
+        <v>38722520.45328814</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.3764489460018013</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>giảm %cannib về 0 vẫn chưa đủ</t>
+          <t>chi phí cố định từ 62.100.000 xuống ≤ 38.722.520 (cắt 23.377.480)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>NDC-2026-09-SETLUNCH199</t>
+          <t>NJFB-2026-11-NIGHTOFLIGHTS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -77397,34 +77402,34 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PROMO</t>
+          <t>BILLS</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>224795.6955097141</v>
+        <v>206.5</v>
       </c>
       <c r="E43" t="n">
-        <v>133318.9305816721</v>
+        <v>331.1677507016652</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4069329028770881</v>
+        <v>0.6037179210734394</v>
       </c>
       <c r="G43" t="n">
         <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>chi ưu đãi/HĐ từ 224.796 xuống ≤ 133.319 (−41%)</t>
+          <t>hoá đơn tham gia từ 206 lên ≥ 331 (+60%)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>NDC-2026-09-SETLUNCH199</t>
+          <t>NCB-2026-10-OFFICEEXCL</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -77434,17 +77439,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>VALUE</t>
+          <t>CANNIB</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>311987.1864169043</v>
+        <v>0.75</v>
       </c>
       <c r="E44" t="n">
-        <v>503475.1984971138</v>
+        <v>0.7001731762743475</v>
       </c>
       <c r="F44" t="n">
-        <v>0.6137688354428973</v>
+        <v>0.06643576496753667</v>
       </c>
       <c r="G44" t="n">
         <v>1</v>
@@ -77454,14 +77459,14 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>giá trị HĐ tham gia từ 311.987 lên ≥ 503.475 (+61%)</t>
+          <t>%cannib từ 75% xuống ≤ 70% — chỉ áp cho khách đặt trước / nhóm mới / khung giờ yếu</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NDC-2026-09-SETLUNCH199</t>
+          <t>NCB-2026-10-OFFICEEXCL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -77471,28 +77476,34 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FIXED</t>
+          <t>PROMO</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>5000000</v>
+        <v>27997.16708609828</v>
+      </c>
+      <c r="E45" t="n">
+        <v>21424.3494444268</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.2347672398946088</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>cắt hết chi phí cố định vẫn chưa đủ</t>
+          <t>chi ưu đãi/HĐ từ 27.997 xuống ≤ 21.424 (−23%)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NDC-2026-09-SETLUNCH199</t>
+          <t>NCB-2026-10-OFFICEEXCL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -77502,48 +77513,54 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BILLS</t>
+          <t>VALUE</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>723.6799999999999</v>
+        <v>302369.4045298614</v>
+      </c>
+      <c r="E46" t="n">
+        <v>317435.5115498138</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.04982682372701675</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>tăng số hoá đơn gấp 10 vẫn chưa đạt — phải sửa lãi trên mỗi hoá đơn trước</t>
+          <t>giá trị HĐ tham gia từ 302.369 lên ≥ 317.436 (+5%)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NDC-2026-11-WINTERNIGHTS</t>
+          <t>NCB-2026-10-OFFICEEXCL</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>HOA_VON</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CANNIB</t>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.75</v>
+        <v>5000000</v>
       </c>
       <c r="E47" t="n">
-        <v>0.5370159647836772</v>
+        <v>2155599.615448409</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2839787136217637</v>
+        <v>0.5688800769103183</v>
       </c>
       <c r="G47" t="n">
         <v>1</v>
@@ -77553,34 +77570,34 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>%cannib từ 75% xuống ≤ 54% — chỉ áp cho khách đặt trước / nhóm mới / khung giờ yếu</t>
+          <t>chi phí cố định từ 5.000.000 xuống ≤ 2.155.600 (cắt 2.844.400)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NDC-2026-11-WINTERNIGHTS</t>
+          <t>NCB-2026-10-OFFICEEXCL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HOA_VON</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>VALUE</t>
+          <t>BILLS</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>916277.1441133452</v>
+        <v>465.71</v>
       </c>
       <c r="E48" t="n">
-        <v>1076324.037267989</v>
+        <v>1080.233074506269</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1746708342370767</v>
+        <v>1.319540217101348</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
@@ -77590,71 +77607,71 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>giá trị HĐ tham gia từ 916.277 lên ≥ 1.076.324 (+17%)</t>
+          <t>hoá đơn tham gia từ 466 lên ≥ 1.080 (+132%)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NDC-2026-11-WINTERNIGHTS</t>
+          <t>NCB-2026-10-AFTERWORK</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>HOA_VON</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FIXED</t>
+          <t>CANNIB</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>70000000</v>
+        <v>0.75</v>
       </c>
       <c r="E49" t="n">
-        <v>37798279.5709886</v>
+        <v>0.7006682628809813</v>
       </c>
       <c r="F49" t="n">
-        <v>0.4600245775573058</v>
+        <v>0.06577564949202497</v>
       </c>
       <c r="G49" t="n">
         <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>chi phí cố định từ 70.000.000 xuống ≤ 37.798.280 (cắt 32.201.720)</t>
+          <t>%cannib từ 75% xuống ≤ 70% — chỉ áp cho khách đặt trước / nhóm mới / khung giờ yếu</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NDC-2026-11-WINTERNIGHTS</t>
+          <t>NCB-2026-10-AFTERWORK</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HOA_VON</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BILLS</t>
+          <t>PROMO</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>363.02</v>
+        <v>24000</v>
       </c>
       <c r="E50" t="n">
-        <v>672.2898578579086</v>
+        <v>14384.70675516146</v>
       </c>
       <c r="F50" t="n">
-        <v>0.8519361408680197</v>
+        <v>0.4006372185349392</v>
       </c>
       <c r="G50" t="n">
         <v>1</v>
@@ -77664,14 +77681,14 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>hoá đơn tham gia từ 363 lên ≥ 672 (+85%)</t>
+          <t>chi ưu đãi/HĐ từ 24.000 xuống ≤ 14.385 (−40%)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NDC-2026-11-WINTERNIGHTS</t>
+          <t>NCB-2026-10-AFTERWORK</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -77681,17 +77698,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CANNIB</t>
+          <t>VALUE</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.75</v>
+        <v>340810.6511240875</v>
       </c>
       <c r="E51" t="n">
-        <v>0.228359941306735</v>
+        <v>359086.8197983005</v>
       </c>
       <c r="F51" t="n">
-        <v>0.6955200782576867</v>
+        <v>0.05362557952321366</v>
       </c>
       <c r="G51" t="n">
         <v>1</v>
@@ -77701,14 +77718,14 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>%cannib từ 75% xuống ≤ 23% — chỉ áp cho khách đặt trước / nhóm mới / khung giờ yếu</t>
+          <t>giá trị HĐ tham gia từ 340.811 lên ≥ 359.087 (+5%)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NDC-2026-11-WINTERNIGHTS</t>
+          <t>NCB-2026-10-AFTERWORK</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -77718,17 +77735,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>VALUE</t>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>916277.1441133452</v>
+        <v>2000000</v>
       </c>
       <c r="E52" t="n">
-        <v>1308263.663918039</v>
+        <v>1308646.900761232</v>
       </c>
       <c r="F52" t="n">
-        <v>0.427803446067628</v>
+        <v>0.3456765496193839</v>
       </c>
       <c r="G52" t="n">
         <v>1</v>
@@ -77738,14 +77755,14 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>giá trị HĐ tham gia từ 916.277 lên ≥ 1.308.264 (+43%)</t>
+          <t>chi phí cố định từ 2.000.000 xuống ≤ 1.308.647 (cắt 691.353)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NDC-2026-11-WINTERNIGHTS</t>
+          <t>NCB-2026-10-AFTERWORK</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -77755,17 +77772,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FIXED</t>
+          <t>BILLS</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>70000000</v>
+        <v>97.06</v>
       </c>
       <c r="E53" t="n">
-        <v>22678967.7425677</v>
+        <v>148.3364228255282</v>
       </c>
       <c r="F53" t="n">
-        <v>0.6760147465347472</v>
+        <v>0.5282961346129014</v>
       </c>
       <c r="G53" t="n">
         <v>1</v>
@@ -77775,14 +77792,14 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>chi phí cố định từ 70.000.000 xuống ≤ 22.678.968 (cắt 47.321.032)</t>
+          <t>hoá đơn tham gia từ 97 lên ≥ 148 (+53%)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NDC-2026-11-WINTERNIGHTS</t>
+          <t>NCB-2026-10-BLOOMINGVELVET</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -77792,17 +77809,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>BILLS</t>
+          <t>CANNIB</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>363.02</v>
+        <v>0.7</v>
       </c>
       <c r="E54" t="n">
-        <v>1120.483096429297</v>
+        <v>0.6729236874317392</v>
       </c>
       <c r="F54" t="n">
-        <v>2.086560234778517</v>
+        <v>0.03868044652608673</v>
       </c>
       <c r="G54" t="n">
         <v>1</v>
@@ -77812,108 +77829,108 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>hoá đơn tham gia từ 363 lên ≥ 1.120 (+209%)</t>
+          <t>%cannib từ 70% xuống ≤ 67% — chỉ áp cho khách đặt trước / nhóm mới / khung giờ yếu</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ALL-2026-10-LOYALTY</t>
+          <t>NCB-2026-10-BLOOMINGVELVET</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>HOA_VON</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CANNIB</t>
+          <t>PROMO</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.9</v>
+        <v>32400.00000000001</v>
       </c>
       <c r="E55" t="n">
-        <v>0.8434527383046769</v>
+        <v>29081.04410823363</v>
       </c>
       <c r="F55" t="n">
-        <v>0.06283029077258122</v>
+        <v>0.1024369102397031</v>
       </c>
       <c r="G55" t="n">
         <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>%cannib từ 90% xuống ≤ 84% — chỉ áp cho khách đặt trước / nhóm mới / khung giờ yếu</t>
+          <t>chi ưu đãi/HĐ từ 32.400 xuống ≤ 29.081 (−10%)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ALL-2026-10-LOYALTY</t>
+          <t>NCB-2026-10-BLOOMINGVELVET</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>HOA_VON</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>PROMO</t>
+          <t>VALUE</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>49454.69900958105</v>
+        <v>302369.4045298614</v>
       </c>
       <c r="E56" t="n">
-        <v>31590.90646110648</v>
+        <v>310556.4530379632</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3612152718797006</v>
+        <v>0.02707631256816967</v>
       </c>
       <c r="G56" t="n">
         <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>chi ưu đãi/HĐ từ 49.455 xuống ≤ 31.591 (−36%)</t>
+          <t>giá trị HĐ tham gia từ 302.369 lên ≥ 310.556 (+3%)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ALL-2026-10-LOYALTY</t>
+          <t>NCB-2026-10-BLOOMINGVELVET</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>HOA_VON</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>VALUE</t>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>534110.7493034754</v>
+        <v>1000000</v>
       </c>
       <c r="E57" t="n">
-        <v>564313.2496196441</v>
+        <v>568535.7340717019</v>
       </c>
       <c r="F57" t="n">
-        <v>0.05654726169723291</v>
+        <v>0.4314642659282981</v>
       </c>
       <c r="G57" t="n">
         <v>1</v>
@@ -77923,19 +77940,19 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>giá trị HĐ tham gia từ 534.111 lên ≥ 564.313 (+6%)</t>
+          <t>chi phí cố định từ 1.000.000 xuống ≤ 568.536 (cắt 431.464)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ALL-2026-10-LOYALTY</t>
+          <t>NCB-2026-10-BLOOMINGVELVET</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>HOA_VON</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -77944,24 +77961,30 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>3335.955259113301</v>
+        <v>130</v>
+      </c>
+      <c r="E58" t="n">
+        <v>228.6575710367015</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.7589043925900114</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>tăng số hoá đơn gấp 10 vẫn chưa đạt — phải sửa lãi trên mỗi hoá đơn trước</t>
+          <t>hoá đơn tham gia từ 130 lên ≥ 229 (+76%)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ALL-2026-10-LOYALTY</t>
+          <t>NCB-2026-10-HALLOWEEN</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -77975,30 +77998,30 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="E59" t="n">
-        <v>0.7917300747491025</v>
+        <v>0.6619684504016732</v>
       </c>
       <c r="F59" t="n">
-        <v>0.1202999169454417</v>
+        <v>0.1173753994644358</v>
       </c>
       <c r="G59" t="n">
         <v>1</v>
       </c>
       <c r="H59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>%cannib từ 90% xuống ≤ 79% — chỉ áp cho khách đặt trước / nhóm mới / khung giờ yếu</t>
+          <t>%cannib từ 75% xuống ≤ 66% — chỉ áp cho khách đặt trước / nhóm mới / khung giờ yếu</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ALL-2026-10-LOYALTY</t>
+          <t>NCB-2026-10-HALLOWEEN</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -78008,17 +78031,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>PROMO</t>
+          <t>VALUE</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>49454.69900958105</v>
+        <v>90777.99388122946</v>
       </c>
       <c r="E60" t="n">
-        <v>23745.4826710948</v>
+        <v>100198.0157744714</v>
       </c>
       <c r="F60" t="n">
-        <v>0.5198538633003409</v>
+        <v>0.1037698839827499</v>
       </c>
       <c r="G60" t="n">
         <v>1</v>
@@ -78028,14 +78051,14 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>chi ưu đãi/HĐ từ 49.455 xuống ≤ 23.745 (−52%)</t>
+          <t>giá trị HĐ tham gia từ 90.778 lên ≥ 100.198 (+10%)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ALL-2026-10-LOYALTY</t>
+          <t>NCB-2026-10-HALLOWEEN</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -78045,34 +78068,34 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>VALUE</t>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>534110.7493034754</v>
+        <v>2000000</v>
       </c>
       <c r="E61" t="n">
-        <v>591938.8802068464</v>
+        <v>1479151.873825686</v>
       </c>
       <c r="F61" t="n">
-        <v>0.1082699252519888</v>
+        <v>0.2604240630871573</v>
       </c>
       <c r="G61" t="n">
         <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>giá trị HĐ tham gia từ 534.111 lên ≥ 591.939 (+11%)</t>
+          <t>chi phí cố định từ 2.000.000 xuống ≤ 1.479.152 (cắt 520.848)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ALL-2026-10-LOYALTY</t>
+          <t>NCB-2026-10-HALLOWEEN</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -78086,29 +78109,35 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>3335.955259113301</v>
+        <v>174.86</v>
+      </c>
+      <c r="E62" t="n">
+        <v>236.4327870510537</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.3521261983933073</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>tăng số hoá đơn gấp 10 vẫn chưa đạt — phải sửa lãi trên mỗi hoá đơn trước</t>
+          <t>hoá đơn tham gia từ 175 lên ≥ 236 (+35%)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>NJFB-2026-11-NIGHTOFLIGHTS</t>
+          <t>NCB-2026-12-XMASMENU</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>HOA_VON</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -78117,13 +78146,13 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="E63" t="n">
-        <v>0.3264384731503469</v>
+        <v>0.5640988439326065</v>
       </c>
       <c r="F63" t="n">
-        <v>0.5647487024662041</v>
+        <v>0.194144508667705</v>
       </c>
       <c r="G63" t="n">
         <v>1</v>
@@ -78133,19 +78162,19 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>%cannib từ 75% xuống ≤ 33% — chỉ áp cho khách đặt trước / nhóm mới / khung giờ yếu</t>
+          <t>%cannib từ 70% xuống ≤ 56% — chỉ áp cho khách đặt trước / nhóm mới / khung giờ yếu</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>NJFB-2026-11-NIGHTOFLIGHTS</t>
+          <t>NCB-2026-12-XMASMENU</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>HOA_VON</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -78154,35 +78183,35 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>2150253.757683252</v>
+        <v>229573.4715723775</v>
       </c>
       <c r="E64" t="n">
-        <v>3061018.522406173</v>
+        <v>244115.8926853324</v>
       </c>
       <c r="F64" t="n">
-        <v>0.4235615268516994</v>
+        <v>0.06334539009822036</v>
       </c>
       <c r="G64" t="n">
         <v>1</v>
       </c>
       <c r="H64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>giá trị HĐ tham gia từ 2.150.254 lên ≥ 3.061.019 (+42%)</t>
+          <t>giá trị HĐ tham gia từ 229.573 lên ≥ 244.116 (+6%)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>NJFB-2026-11-NIGHTOFLIGHTS</t>
+          <t>NCB-2026-12-XMASMENU</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>HOA_VON</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -78191,35 +78220,35 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>124200000</v>
+        <v>4500000</v>
       </c>
       <c r="E65" t="n">
-        <v>46098238.63483725</v>
+        <v>3097032.391884568</v>
       </c>
       <c r="F65" t="n">
-        <v>0.6288386583346437</v>
+        <v>0.3117705795812071</v>
       </c>
       <c r="G65" t="n">
         <v>1</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>chi phí cố định từ 124.200.000 xuống ≤ 46.098.239 (cắt 78.101.761)</t>
+          <t>chi phí cố định từ 4.500.000 xuống ≤ 3.097.032 (cắt 1.402.968)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>NJFB-2026-11-NIGHTOFLIGHTS</t>
+          <t>NCB-2026-12-XMASMENU</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>HOA_VON</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -78228,13 +78257,13 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>147.5</v>
+        <v>305.1</v>
       </c>
       <c r="E66" t="n">
-        <v>397.4013008416978</v>
+        <v>443.3114757204467</v>
       </c>
       <c r="F66" t="n">
-        <v>1.694246107401341</v>
+        <v>0.453003853557675</v>
       </c>
       <c r="G66" t="n">
         <v>1</v>
@@ -78244,19 +78273,19 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>hoá đơn tham gia từ 148 lên ≥ 397 (+169%)</t>
+          <t>hoá đơn tham gia từ 305 lên ≥ 443 (+45%)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>NJFB-2026-11-NIGHTOFLIGHTS</t>
+          <t>NJFB-2026-10-RESIDENT15</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>DUYET</t>
+          <t>HOA_VON</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -78265,44 +78294,50 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.7638354167095714</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.1512939814338095</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>giảm %cannib về 0 vẫn chưa đủ</t>
+          <t>%cannib từ 90% xuống ≤ 76% — chỉ áp cho khách đặt trước / nhóm mới / khung giờ yếu</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>NJFB-2026-11-NIGHTOFLIGHTS</t>
+          <t>NJFB-2026-10-RESIDENT15</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DUYET</t>
+          <t>HOA_VON</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>VALUE</t>
+          <t>PROMO</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>2150253.757683252</v>
+        <v>270311.9641621423</v>
       </c>
       <c r="E68" t="n">
-        <v>4026570.658494826</v>
+        <v>114459.1455652661</v>
       </c>
       <c r="F68" t="n">
-        <v>0.8726025447494978</v>
+        <v>0.5765664833961637</v>
       </c>
       <c r="G68" t="n">
         <v>1</v>
@@ -78312,56 +78347,56 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>giá trị HĐ tham gia từ 2.150.254 lên ≥ 4.026.571 (+87%)</t>
+          <t>chi ưu đãi/HĐ từ 270.312 xuống ≤ 114.459 (−58%)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>NJFB-2026-11-NIGHTOFLIGHTS</t>
+          <t>NJFB-2026-10-RESIDENT15</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>DUYET</t>
+          <t>HOA_VON</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>FIXED</t>
+          <t>VALUE</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>124200000</v>
+        <v>1946246.141967425</v>
       </c>
       <c r="E69" t="n">
-        <v>27658943.18087974</v>
+        <v>2211255.936870617</v>
       </c>
       <c r="F69" t="n">
-        <v>0.7773031950009682</v>
+        <v>0.1361645832912473</v>
       </c>
       <c r="G69" t="n">
         <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>chi phí cố định từ 124.200.000 xuống ≤ 27.658.943 (cắt 96.541.057)</t>
+          <t>giá trị HĐ tham gia từ 1.946.246 lên ≥ 2.211.256 (+14%)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>NJFB-2026-11-NIGHTOFLIGHTS</t>
+          <t>NJFB-2026-10-RESIDENT15</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>DUYET</t>
+          <t>HOA_VON</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -78370,30 +78405,24 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>147.5</v>
-      </c>
-      <c r="E70" t="n">
-        <v>662.335501402606</v>
-      </c>
-      <c r="F70" t="n">
-        <v>3.490410179000719</v>
+        <v>26</v>
       </c>
       <c r="G70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>hoá đơn tham gia từ 148 lên ≥ 662 (+349%)</t>
+          <t>tăng số hoá đơn gấp 10 vẫn chưa đạt — phải sửa lãi trên mỗi hoá đơn trước</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>NCB-2026-10-OFFICEEXCL</t>
+          <t>NJFB-2026-10-RESIDENT15</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -78407,30 +78436,30 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="E71" t="n">
-        <v>0.7001731762743475</v>
+        <v>0.6862347869315274</v>
       </c>
       <c r="F71" t="n">
-        <v>0.06643576496753667</v>
+        <v>0.237516903409414</v>
       </c>
       <c r="G71" t="n">
         <v>1</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>%cannib từ 75% xuống ≤ 70% — chỉ áp cho khách đặt trước / nhóm mới / khung giờ yếu</t>
+          <t>%cannib từ 90% xuống ≤ 69% — chỉ áp cho khách đặt trước / nhóm mới / khung giờ yếu</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>NCB-2026-10-OFFICEEXCL</t>
+          <t>NJFB-2026-10-RESIDENT15</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -78444,30 +78473,30 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>27997.16708609828</v>
+        <v>270311.9641621423</v>
       </c>
       <c r="E72" t="n">
-        <v>21424.3494444268</v>
+        <v>86151.03042135687</v>
       </c>
       <c r="F72" t="n">
-        <v>0.2347672398946088</v>
+        <v>0.6812903539494073</v>
       </c>
       <c r="G72" t="n">
         <v>1</v>
       </c>
       <c r="H72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>chi ưu đãi/HĐ từ 27.997 xuống ≤ 21.424 (−23%)</t>
+          <t>chi ưu đãi/HĐ từ 270.312 xuống ≤ 86.151 (−68%)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>NCB-2026-10-OFFICEEXCL</t>
+          <t>NJFB-2026-10-RESIDENT15</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -78481,13 +78510,13 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>302369.4045298614</v>
+        <v>1946246.141967425</v>
       </c>
       <c r="E73" t="n">
-        <v>317435.5115498138</v>
+        <v>2362285.863190908</v>
       </c>
       <c r="F73" t="n">
-        <v>0.04982682372701675</v>
+        <v>0.2137652130695641</v>
       </c>
       <c r="G73" t="n">
         <v>1</v>
@@ -78497,14 +78526,14 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>giá trị HĐ tham gia từ 302.369 lên ≥ 317.436 (+5%)</t>
+          <t>giá trị HĐ tham gia từ 1.946.246 lên ≥ 2.362.286 (+21%)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>NCB-2026-10-OFFICEEXCL</t>
+          <t>NJFB-2026-10-RESIDENT15</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -78514,1160 +78543,19 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>FIXED</t>
+          <t>BILLS</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="E74" t="n">
-        <v>2155599.615448409</v>
-      </c>
-      <c r="F74" t="n">
-        <v>0.5688800769103183</v>
+        <v>26</v>
       </c>
       <c r="G74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="inlineStr">
-        <is>
-          <t>chi phí cố định từ 5.000.000 xuống ≤ 2.155.600 (cắt 2.844.400)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>NCB-2026-10-OFFICEEXCL</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>DUYET</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>BILLS</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>465.71</v>
-      </c>
-      <c r="E75" t="n">
-        <v>1080.233074506269</v>
-      </c>
-      <c r="F75" t="n">
-        <v>1.319540217101348</v>
-      </c>
-      <c r="G75" t="n">
-        <v>1</v>
-      </c>
-      <c r="H75" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>hoá đơn tham gia từ 466 lên ≥ 1.080 (+132%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>NCB-2026-10-AFTERWORK</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>DUYET</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>CANNIB</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E76" t="n">
-        <v>0.7006682628809813</v>
-      </c>
-      <c r="F76" t="n">
-        <v>0.06577564949202497</v>
-      </c>
-      <c r="G76" t="n">
-        <v>1</v>
-      </c>
-      <c r="H76" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>%cannib từ 75% xuống ≤ 70% — chỉ áp cho khách đặt trước / nhóm mới / khung giờ yếu</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>NCB-2026-10-AFTERWORK</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>DUYET</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>PROMO</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>24000</v>
-      </c>
-      <c r="E77" t="n">
-        <v>14384.70675516146</v>
-      </c>
-      <c r="F77" t="n">
-        <v>0.4006372185349392</v>
-      </c>
-      <c r="G77" t="n">
-        <v>1</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>chi ưu đãi/HĐ từ 24.000 xuống ≤ 14.385 (−40%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>NCB-2026-10-AFTERWORK</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>DUYET</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>VALUE</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>340810.6511240875</v>
-      </c>
-      <c r="E78" t="n">
-        <v>359086.8197983005</v>
-      </c>
-      <c r="F78" t="n">
-        <v>0.05362557952321366</v>
-      </c>
-      <c r="G78" t="n">
-        <v>1</v>
-      </c>
-      <c r="H78" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>giá trị HĐ tham gia từ 340.811 lên ≥ 359.087 (+5%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>NCB-2026-10-AFTERWORK</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>DUYET</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="E79" t="n">
-        <v>1308646.900761232</v>
-      </c>
-      <c r="F79" t="n">
-        <v>0.3456765496193839</v>
-      </c>
-      <c r="G79" t="n">
-        <v>1</v>
-      </c>
-      <c r="H79" t="n">
-        <v>1</v>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>chi phí cố định từ 2.000.000 xuống ≤ 1.308.647 (cắt 691.353)</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>NCB-2026-10-AFTERWORK</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>DUYET</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>BILLS</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>97.06</v>
-      </c>
-      <c r="E80" t="n">
-        <v>148.3364228255282</v>
-      </c>
-      <c r="F80" t="n">
-        <v>0.5282961346129014</v>
-      </c>
-      <c r="G80" t="n">
-        <v>1</v>
-      </c>
-      <c r="H80" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>hoá đơn tham gia từ 97 lên ≥ 148 (+53%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>NCB-2026-10-BLOOMINGVELVET</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>DUYET</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>CANNIB</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E81" t="n">
-        <v>0.6729236874317392</v>
-      </c>
-      <c r="F81" t="n">
-        <v>0.03868044652608673</v>
-      </c>
-      <c r="G81" t="n">
-        <v>1</v>
-      </c>
-      <c r="H81" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>%cannib từ 70% xuống ≤ 67% — chỉ áp cho khách đặt trước / nhóm mới / khung giờ yếu</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>NCB-2026-10-BLOOMINGVELVET</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>DUYET</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>PROMO</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>32400.00000000001</v>
-      </c>
-      <c r="E82" t="n">
-        <v>29081.04410823363</v>
-      </c>
-      <c r="F82" t="n">
-        <v>0.1024369102397031</v>
-      </c>
-      <c r="G82" t="n">
-        <v>1</v>
-      </c>
-      <c r="H82" t="n">
-        <v>1</v>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>chi ưu đãi/HĐ từ 32.400 xuống ≤ 29.081 (−10%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>NCB-2026-10-BLOOMINGVELVET</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>DUYET</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>VALUE</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>302369.4045298614</v>
-      </c>
-      <c r="E83" t="n">
-        <v>310556.4530379632</v>
-      </c>
-      <c r="F83" t="n">
-        <v>0.02707631256816967</v>
-      </c>
-      <c r="G83" t="n">
-        <v>1</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>giá trị HĐ tham gia từ 302.369 lên ≥ 310.556 (+3%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>NCB-2026-10-BLOOMINGVELVET</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>DUYET</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="E84" t="n">
-        <v>568535.7340717019</v>
-      </c>
-      <c r="F84" t="n">
-        <v>0.4314642659282981</v>
-      </c>
-      <c r="G84" t="n">
-        <v>1</v>
-      </c>
-      <c r="H84" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>chi phí cố định từ 1.000.000 xuống ≤ 568.536 (cắt 431.464)</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>NCB-2026-10-BLOOMINGVELVET</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>DUYET</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>BILLS</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>130</v>
-      </c>
-      <c r="E85" t="n">
-        <v>228.6575710367015</v>
-      </c>
-      <c r="F85" t="n">
-        <v>0.7589043925900114</v>
-      </c>
-      <c r="G85" t="n">
-        <v>1</v>
-      </c>
-      <c r="H85" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>hoá đơn tham gia từ 130 lên ≥ 229 (+76%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>NCB-2026-10-HALLOWEEN</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>DUYET</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>CANNIB</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E86" t="n">
-        <v>0.6619684504016732</v>
-      </c>
-      <c r="F86" t="n">
-        <v>0.1173753994644358</v>
-      </c>
-      <c r="G86" t="n">
-        <v>1</v>
-      </c>
-      <c r="H86" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>%cannib từ 75% xuống ≤ 66% — chỉ áp cho khách đặt trước / nhóm mới / khung giờ yếu</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>NCB-2026-10-HALLOWEEN</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>DUYET</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>VALUE</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>90777.99388122946</v>
-      </c>
-      <c r="E87" t="n">
-        <v>100198.0157744714</v>
-      </c>
-      <c r="F87" t="n">
-        <v>0.1037698839827499</v>
-      </c>
-      <c r="G87" t="n">
-        <v>1</v>
-      </c>
-      <c r="H87" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>giá trị HĐ tham gia từ 90.778 lên ≥ 100.198 (+10%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>NCB-2026-10-HALLOWEEN</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>DUYET</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="E88" t="n">
-        <v>1479151.873825686</v>
-      </c>
-      <c r="F88" t="n">
-        <v>0.2604240630871573</v>
-      </c>
-      <c r="G88" t="n">
-        <v>1</v>
-      </c>
-      <c r="H88" t="n">
-        <v>1</v>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>chi phí cố định từ 2.000.000 xuống ≤ 1.479.152 (cắt 520.848)</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>NCB-2026-10-HALLOWEEN</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>DUYET</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>BILLS</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>174.86</v>
-      </c>
-      <c r="E89" t="n">
-        <v>236.4327870510537</v>
-      </c>
-      <c r="F89" t="n">
-        <v>0.3521261983933073</v>
-      </c>
-      <c r="G89" t="n">
-        <v>1</v>
-      </c>
-      <c r="H89" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>hoá đơn tham gia từ 175 lên ≥ 236 (+35%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>NCB-2026-12-XMASMENU</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>HOA_VON</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>CANNIB</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E90" t="n">
-        <v>0.6658162332964821</v>
-      </c>
-      <c r="F90" t="n">
-        <v>0.04883395243359694</v>
-      </c>
-      <c r="G90" t="n">
-        <v>1</v>
-      </c>
-      <c r="H90" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>%cannib từ 70% xuống ≤ 67% — chỉ áp cho khách đặt trước / nhóm mới / khung giờ yếu</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>NCB-2026-12-XMASMENU</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>HOA_VON</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>VALUE</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>229573.4715723775</v>
-      </c>
-      <c r="E91" t="n">
-        <v>233231.3854933676</v>
-      </c>
-      <c r="F91" t="n">
-        <v>0.01593352183044771</v>
-      </c>
-      <c r="G91" t="n">
-        <v>1</v>
-      </c>
-      <c r="H91" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>giá trị HĐ tham gia từ 229.573 lên ≥ 233.231 (+2%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>NCB-2026-12-XMASMENU</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>HOA_VON</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="E92" t="n">
-        <v>4488548.36605733</v>
-      </c>
-      <c r="F92" t="n">
-        <v>0.102290326788534</v>
-      </c>
-      <c r="G92" t="n">
-        <v>1</v>
-      </c>
-      <c r="H92" t="n">
-        <v>1</v>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>chi phí cố định từ 5.000.000 xuống ≤ 4.488.548 (cắt 511.452)</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>NCB-2026-12-XMASMENU</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>HOA_VON</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>BILLS</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>265.31</v>
-      </c>
-      <c r="E93" t="n">
-        <v>295.5409838154706</v>
-      </c>
-      <c r="F93" t="n">
-        <v>0.113945889018396</v>
-      </c>
-      <c r="G93" t="n">
-        <v>1</v>
-      </c>
-      <c r="H93" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>hoá đơn tham gia từ 265 lên ≥ 296 (+11%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>NCB-2026-12-XMASMENU</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>DUYET</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>CANNIB</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E94" t="n">
-        <v>0.4430270554940761</v>
-      </c>
-      <c r="F94" t="n">
-        <v>0.3671042064370341</v>
-      </c>
-      <c r="G94" t="n">
-        <v>1</v>
-      </c>
-      <c r="H94" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>%cannib từ 70% xuống ≤ 44% — chỉ áp cho khách đặt trước / nhóm mới / khung giờ yếu</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>NCB-2026-12-XMASMENU</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>DUYET</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>VALUE</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>229573.4715723775</v>
-      </c>
-      <c r="E95" t="n">
-        <v>257071.4626252614</v>
-      </c>
-      <c r="F95" t="n">
-        <v>0.1197786088459907</v>
-      </c>
-      <c r="G95" t="n">
-        <v>1</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>giá trị HĐ tham gia từ 229.573 lên ≥ 257.071 (+12%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>NCB-2026-12-XMASMENU</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>DUYET</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="E96" t="n">
-        <v>2693129.019635308</v>
-      </c>
-      <c r="F96" t="n">
-        <v>0.4613741960729385</v>
-      </c>
-      <c r="G96" t="n">
-        <v>1</v>
-      </c>
-      <c r="H96" t="n">
-        <v>1</v>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>chi phí cố định từ 5.000.000 xuống ≤ 2.693.129 (cắt 2.306.871)</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>NCB-2026-12-XMASMENU</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>DUYET</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>BILLS</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>265.31</v>
-      </c>
-      <c r="E97" t="n">
-        <v>492.56830635582</v>
-      </c>
-      <c r="F97" t="n">
-        <v>0.8565764816848969</v>
-      </c>
-      <c r="G97" t="n">
-        <v>1</v>
-      </c>
-      <c r="H97" t="n">
-        <v>0</v>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>hoá đơn tham gia từ 265 lên ≥ 493 (+86%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>NJFB-2026-10-RESIDENT15</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>HOA_VON</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>CANNIB</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E98" t="n">
-        <v>0.7638354167095714</v>
-      </c>
-      <c r="F98" t="n">
-        <v>0.1512939814338095</v>
-      </c>
-      <c r="G98" t="n">
-        <v>1</v>
-      </c>
-      <c r="H98" t="n">
-        <v>1</v>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>%cannib từ 90% xuống ≤ 76% — chỉ áp cho khách đặt trước / nhóm mới / khung giờ yếu</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>NJFB-2026-10-RESIDENT15</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>HOA_VON</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>PROMO</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>270311.9641621423</v>
-      </c>
-      <c r="E99" t="n">
-        <v>114459.1455652661</v>
-      </c>
-      <c r="F99" t="n">
-        <v>0.5765664833961637</v>
-      </c>
-      <c r="G99" t="n">
-        <v>1</v>
-      </c>
-      <c r="H99" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>chi ưu đãi/HĐ từ 270.312 xuống ≤ 114.459 (−58%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>NJFB-2026-10-RESIDENT15</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>HOA_VON</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>VALUE</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>1946246.141967425</v>
-      </c>
-      <c r="E100" t="n">
-        <v>2211255.936870617</v>
-      </c>
-      <c r="F100" t="n">
-        <v>0.1361645832912473</v>
-      </c>
-      <c r="G100" t="n">
-        <v>1</v>
-      </c>
-      <c r="H100" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>giá trị HĐ tham gia từ 1.946.246 lên ≥ 2.211.256 (+14%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>NJFB-2026-10-RESIDENT15</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>HOA_VON</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>BILLS</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>26</v>
-      </c>
-      <c r="G101" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>tăng số hoá đơn gấp 10 vẫn chưa đạt — phải sửa lãi trên mỗi hoá đơn trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>NJFB-2026-10-RESIDENT15</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>DUYET</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>CANNIB</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E102" t="n">
-        <v>0.6862347869315274</v>
-      </c>
-      <c r="F102" t="n">
-        <v>0.237516903409414</v>
-      </c>
-      <c r="G102" t="n">
-        <v>1</v>
-      </c>
-      <c r="H102" t="n">
-        <v>1</v>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>%cannib từ 90% xuống ≤ 69% — chỉ áp cho khách đặt trước / nhóm mới / khung giờ yếu</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>NJFB-2026-10-RESIDENT15</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>DUYET</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>PROMO</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>270311.9641621423</v>
-      </c>
-      <c r="E103" t="n">
-        <v>86151.03042135687</v>
-      </c>
-      <c r="F103" t="n">
-        <v>0.6812903539494073</v>
-      </c>
-      <c r="G103" t="n">
-        <v>1</v>
-      </c>
-      <c r="H103" t="n">
-        <v>0</v>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>chi ưu đãi/HĐ từ 270.312 xuống ≤ 86.151 (−68%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>NJFB-2026-10-RESIDENT15</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>DUYET</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>VALUE</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>1946246.141967425</v>
-      </c>
-      <c r="E104" t="n">
-        <v>2362285.863190908</v>
-      </c>
-      <c r="F104" t="n">
-        <v>0.2137652130695641</v>
-      </c>
-      <c r="G104" t="n">
-        <v>1</v>
-      </c>
-      <c r="H104" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>giá trị HĐ tham gia từ 1.946.246 lên ≥ 2.362.286 (+21%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>NJFB-2026-10-RESIDENT15</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>DUYET</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>BILLS</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>26</v>
-      </c>
-      <c r="G105" t="n">
-        <v>0</v>
-      </c>
-      <c r="H105" t="n">
-        <v>0</v>
-      </c>
-      <c r="I105" t="inlineStr">
         <is>
           <t>tăng số hoá đơn gấp 10 vẫn chưa đạt — phải sửa lãi trên mỗi hoá đơn trước</t>
         </is>

--- a/data_input/04_preeval.xlsx
+++ b/data_input/04_preeval.xlsx
@@ -21839,7 +21839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS106"/>
+  <dimension ref="A1:BB106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -21887,6 +21887,15 @@
     <col width="16" customWidth="1" min="43" max="43"/>
     <col width="11" customWidth="1" min="44" max="44"/>
     <col width="13" customWidth="1" min="45" max="45"/>
+    <col width="10" customWidth="1" min="46" max="46"/>
+    <col width="13" customWidth="1" min="47" max="47"/>
+    <col width="14" customWidth="1" min="48" max="48"/>
+    <col width="14" customWidth="1" min="49" max="49"/>
+    <col width="12" customWidth="1" min="50" max="50"/>
+    <col width="12" customWidth="1" min="51" max="51"/>
+    <col width="13" customWidth="1" min="52" max="52"/>
+    <col width="14" customWidth="1" min="53" max="53"/>
+    <col width="13" customWidth="1" min="54" max="54"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22115,6 +22124,51 @@
           <t>gift_cost</t>
         </is>
       </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>guests</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>cogs_cost</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>gift_total</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>gift_fixed</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>cost_ads</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>cost_kol</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>cost_posm</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>cost_other</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>disc_cost</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22278,6 +22332,33 @@
       <c r="AS2" t="n">
         <v>0</v>
       </c>
+      <c r="AT2" t="n">
+        <v>267</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>8359471</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>12012901</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22441,6 +22522,33 @@
       <c r="AS3" t="n">
         <v>0</v>
       </c>
+      <c r="AT3" t="n">
+        <v>446</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>13932452</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>20021502</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -22604,6 +22712,33 @@
       <c r="AS4" t="n">
         <v>0</v>
       </c>
+      <c r="AT4" t="n">
+        <v>624</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>19505432</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>28030102</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -22778,6 +22913,33 @@
       <c r="AS5" t="n">
         <v>26277778</v>
       </c>
+      <c r="AT5" t="n">
+        <v>660</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>15785451</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>26277778</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -22947,6 +23109,33 @@
       <c r="AS6" t="n">
         <v>43416000</v>
       </c>
+      <c r="AT6" t="n">
+        <v>1091</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>26080634</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>43416000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23116,6 +23305,33 @@
       <c r="AS7" t="n">
         <v>43416000</v>
       </c>
+      <c r="AT7" t="n">
+        <v>1091</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>26080634</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>43416000</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23273,6 +23489,33 @@
       <c r="AS8" t="n">
         <v>0</v>
       </c>
+      <c r="AT8" t="n">
+        <v>57</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1038074</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>2473588</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23430,6 +23673,33 @@
       <c r="AS9" t="n">
         <v>0</v>
       </c>
+      <c r="AT9" t="n">
+        <v>95</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1730123</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>4122647</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23582,6 +23852,33 @@
       <c r="AS10" t="n">
         <v>0</v>
       </c>
+      <c r="AT10" t="n">
+        <v>132</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2422173</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>5771705</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -23742,6 +24039,33 @@
       <c r="AS11" t="n">
         <v>134351</v>
       </c>
+      <c r="AT11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>992635</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>134351</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -23902,6 +24226,33 @@
       <c r="AS12" t="n">
         <v>223918</v>
       </c>
+      <c r="AT12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1654392</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>223918</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -24062,6 +24413,33 @@
       <c r="AS13" t="n">
         <v>313486</v>
       </c>
+      <c r="AT13" t="n">
+        <v>37</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2316149</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>313486</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -24220,6 +24598,33 @@
       <c r="AS14" t="n">
         <v>7957447</v>
       </c>
+      <c r="AT14" t="n">
+        <v>1589</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>15264720</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>7957447</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>13598547</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -24378,6 +24783,33 @@
       <c r="AS15" t="n">
         <v>13262411</v>
       </c>
+      <c r="AT15" t="n">
+        <v>2648</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>25441200</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>13262411</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>22664245</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -24536,6 +24968,33 @@
       <c r="AS16" t="n">
         <v>18567376</v>
       </c>
+      <c r="AT16" t="n">
+        <v>3708</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>35617680</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>18567376</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>31729943</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -24694,6 +25153,33 @@
       <c r="AS17" t="n">
         <v>2245659</v>
       </c>
+      <c r="AT17" t="n">
+        <v>895</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>20197415</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2245659</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -24852,6 +25338,33 @@
       <c r="AS18" t="n">
         <v>3742764</v>
       </c>
+      <c r="AT18" t="n">
+        <v>1492</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>33662359</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>3742764</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -25010,6 +25523,33 @@
       <c r="AS19" t="n">
         <v>5239870</v>
       </c>
+      <c r="AT19" t="n">
+        <v>2088</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>47127302</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>5239870</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -25168,6 +25708,33 @@
       <c r="AS20" t="n">
         <v>26298489</v>
       </c>
+      <c r="AT20" t="n">
+        <v>1500</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>20077128</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>26298489</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -25326,6 +25893,33 @@
       <c r="AS21" t="n">
         <v>43830816</v>
       </c>
+      <c r="AT21" t="n">
+        <v>2500</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>33461880</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>43830816</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -25484,6 +26078,33 @@
       <c r="AS22" t="n">
         <v>61363142</v>
       </c>
+      <c r="AT22" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>46846632</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>61363142</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -25639,6 +26260,33 @@
       <c r="AS23" t="n">
         <v>648598</v>
       </c>
+      <c r="AT23" t="n">
+        <v>38</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>787417</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>648598</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -25794,6 +26442,33 @@
       <c r="AS24" t="n">
         <v>1080996</v>
       </c>
+      <c r="AT24" t="n">
+        <v>64</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>1312361</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>1080996</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -25949,6 +26624,33 @@
       <c r="AS25" t="n">
         <v>1513394</v>
       </c>
+      <c r="AT25" t="n">
+        <v>90</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>1837305</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1513394</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -26107,6 +26809,33 @@
       <c r="AS26" t="n">
         <v>0</v>
       </c>
+      <c r="AT26" t="n">
+        <v>127</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>679995</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -26265,6 +26994,33 @@
       <c r="AS27" t="n">
         <v>0</v>
       </c>
+      <c r="AT27" t="n">
+        <v>212</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>1133325</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -26423,6 +27179,33 @@
       <c r="AS28" t="n">
         <v>0</v>
       </c>
+      <c r="AT28" t="n">
+        <v>297</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>1586655</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -26581,6 +27364,33 @@
       <c r="AS29" t="n">
         <v>0</v>
       </c>
+      <c r="AT29" t="n">
+        <v>577</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>14890792</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>19500000</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>19500000</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>23400000</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -26739,6 +27549,33 @@
       <c r="AS30" t="n">
         <v>0</v>
       </c>
+      <c r="AT30" t="n">
+        <v>961</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>24817986</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>19500000</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>19500000</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>23400000</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -26897,6 +27734,33 @@
       <c r="AS31" t="n">
         <v>0</v>
       </c>
+      <c r="AT31" t="n">
+        <v>1346</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>34745180</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>19500000</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>19500000</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>23400000</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -27052,6 +27916,33 @@
       <c r="AS32" t="n">
         <v>5140800</v>
       </c>
+      <c r="AT32" t="n">
+        <v>144</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>22477769</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>5140800</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -27207,6 +28098,33 @@
       <c r="AS33" t="n">
         <v>8568000</v>
       </c>
+      <c r="AT33" t="n">
+        <v>240</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>37462949</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>8568000</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -27362,6 +28280,33 @@
       <c r="AS34" t="n">
         <v>11995200</v>
       </c>
+      <c r="AT34" t="n">
+        <v>336</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>52448128</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>11995200</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -27517,6 +28462,33 @@
       <c r="AS35" t="n">
         <v>5870428</v>
       </c>
+      <c r="AT35" t="n">
+        <v>117</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>10314107</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>5870428</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -27672,6 +28644,33 @@
       <c r="AS36" t="n">
         <v>9784047</v>
       </c>
+      <c r="AT36" t="n">
+        <v>195</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>17190178</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>9784047</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -27827,6 +28826,33 @@
       <c r="AS37" t="n">
         <v>13697666</v>
       </c>
+      <c r="AT37" t="n">
+        <v>273</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>24066249</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>13697666</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -27982,6 +29008,33 @@
       <c r="AS38" t="n">
         <v>0</v>
       </c>
+      <c r="AT38" t="n">
+        <v>3641</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>32466164</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>59392319</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -28137,6 +29190,33 @@
       <c r="AS39" t="n">
         <v>0</v>
       </c>
+      <c r="AT39" t="n">
+        <v>6068</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>54110274</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>98987198</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -28292,6 +29372,33 @@
       <c r="AS40" t="n">
         <v>0</v>
       </c>
+      <c r="AT40" t="n">
+        <v>8495</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>75754384</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>138582077</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -28450,6 +29557,33 @@
       <c r="AS41" t="n">
         <v>0</v>
       </c>
+      <c r="AT41" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>945000</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>600000</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -28608,6 +29742,33 @@
       <c r="AS42" t="n">
         <v>0</v>
       </c>
+      <c r="AT42" t="n">
+        <v>26</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>1575000</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>600000</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -28766,6 +29927,33 @@
       <c r="AS43" t="n">
         <v>0</v>
       </c>
+      <c r="AT43" t="n">
+        <v>36</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>2205000</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>600000</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -28924,6 +30112,33 @@
       <c r="AS44" t="n">
         <v>0</v>
       </c>
+      <c r="AT44" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>945000</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>600000</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -29082,6 +30297,33 @@
       <c r="AS45" t="n">
         <v>0</v>
       </c>
+      <c r="AT45" t="n">
+        <v>26</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>1575000</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>600000</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -29240,6 +30482,33 @@
       <c r="AS46" t="n">
         <v>0</v>
       </c>
+      <c r="AT46" t="n">
+        <v>36</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>2205000</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>600000</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -29398,6 +30667,33 @@
       <c r="AS47" t="n">
         <v>0</v>
       </c>
+      <c r="AT47" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>945000</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>600000</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -29556,6 +30852,33 @@
       <c r="AS48" t="n">
         <v>0</v>
       </c>
+      <c r="AT48" t="n">
+        <v>26</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>1575000</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>600000</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -29714,6 +31037,33 @@
       <c r="AS49" t="n">
         <v>0</v>
       </c>
+      <c r="AT49" t="n">
+        <v>36</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>2205000</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>600000</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -29872,6 +31222,33 @@
       <c r="AS50" t="n">
         <v>3081685</v>
       </c>
+      <c r="AT50" t="n">
+        <v>664</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>32503339</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>3081685</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>5922591</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -30030,6 +31407,33 @@
       <c r="AS51" t="n">
         <v>5136142</v>
       </c>
+      <c r="AT51" t="n">
+        <v>1106</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>54172231</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>5136142</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>9870985</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -30188,6 +31592,33 @@
       <c r="AS52" t="n">
         <v>7190599</v>
       </c>
+      <c r="AT52" t="n">
+        <v>1549</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>75841123</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>7190599</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>13819379</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -30346,6 +31777,33 @@
       <c r="AS53" t="n">
         <v>4022460</v>
       </c>
+      <c r="AT53" t="n">
+        <v>179</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>14298760</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>4022460</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -30504,6 +31962,33 @@
       <c r="AS54" t="n">
         <v>6704100</v>
       </c>
+      <c r="AT54" t="n">
+        <v>298</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>23831267</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>6704100</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -30662,6 +32147,33 @@
       <c r="AS55" t="n">
         <v>9385740</v>
       </c>
+      <c r="AT55" t="n">
+        <v>417</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>33363774</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>9385740</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -30820,6 +32332,33 @@
       <c r="AS56" t="n">
         <v>19980000</v>
       </c>
+      <c r="AT56" t="n">
+        <v>432</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>22717204</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>19980000</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -30978,6 +32517,33 @@
       <c r="AS57" t="n">
         <v>33300000</v>
       </c>
+      <c r="AT57" t="n">
+        <v>720</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>37862007</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>33300000</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB57" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -31136,6 +32702,33 @@
       <c r="AS58" t="n">
         <v>46620000</v>
       </c>
+      <c r="AT58" t="n">
+        <v>1008</v>
+      </c>
+      <c r="AU58" t="n">
+        <v>53006810</v>
+      </c>
+      <c r="AV58" t="n">
+        <v>46620000</v>
+      </c>
+      <c r="AW58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX58" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="AY58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -31294,6 +32887,33 @@
       <c r="AS59" t="n">
         <v>0</v>
       </c>
+      <c r="AT59" t="n">
+        <v>312</v>
+      </c>
+      <c r="AU59" t="n">
+        <v>17582621</v>
+      </c>
+      <c r="AV59" t="n">
+        <v>37100000</v>
+      </c>
+      <c r="AW59" t="n">
+        <v>37100000</v>
+      </c>
+      <c r="AX59" t="n">
+        <v>23000000</v>
+      </c>
+      <c r="AY59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA59" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="BB59" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -31452,6 +33072,33 @@
       <c r="AS60" t="n">
         <v>0</v>
       </c>
+      <c r="AT60" t="n">
+        <v>520</v>
+      </c>
+      <c r="AU60" t="n">
+        <v>29304368</v>
+      </c>
+      <c r="AV60" t="n">
+        <v>37100000</v>
+      </c>
+      <c r="AW60" t="n">
+        <v>37100000</v>
+      </c>
+      <c r="AX60" t="n">
+        <v>23000000</v>
+      </c>
+      <c r="AY60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA60" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="BB60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -31610,6 +33257,33 @@
       <c r="AS61" t="n">
         <v>0</v>
       </c>
+      <c r="AT61" t="n">
+        <v>728</v>
+      </c>
+      <c r="AU61" t="n">
+        <v>41026115</v>
+      </c>
+      <c r="AV61" t="n">
+        <v>37100000</v>
+      </c>
+      <c r="AW61" t="n">
+        <v>37100000</v>
+      </c>
+      <c r="AX61" t="n">
+        <v>23000000</v>
+      </c>
+      <c r="AY61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA61" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="BB61" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -31762,6 +33436,33 @@
       <c r="AS62" t="n">
         <v>0</v>
       </c>
+      <c r="AT62" t="n">
+        <v>253</v>
+      </c>
+      <c r="AU62" t="n">
+        <v>4796023</v>
+      </c>
+      <c r="AV62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB62" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -31914,6 +33615,33 @@
       <c r="AS63" t="n">
         <v>0</v>
       </c>
+      <c r="AT63" t="n">
+        <v>422</v>
+      </c>
+      <c r="AU63" t="n">
+        <v>7993372</v>
+      </c>
+      <c r="AV63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -32066,6 +33794,33 @@
       <c r="AS64" t="n">
         <v>0</v>
       </c>
+      <c r="AT64" t="n">
+        <v>591</v>
+      </c>
+      <c r="AU64" t="n">
+        <v>11190721</v>
+      </c>
+      <c r="AV64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB64" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -32218,6 +33973,33 @@
       <c r="AS65" t="n">
         <v>0</v>
       </c>
+      <c r="AT65" t="n">
+        <v>49</v>
+      </c>
+      <c r="AU65" t="n">
+        <v>4080000</v>
+      </c>
+      <c r="AV65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB65" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -32370,6 +34152,33 @@
       <c r="AS66" t="n">
         <v>0</v>
       </c>
+      <c r="AT66" t="n">
+        <v>81</v>
+      </c>
+      <c r="AU66" t="n">
+        <v>6800000</v>
+      </c>
+      <c r="AV66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB66" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -32522,6 +34331,33 @@
       <c r="AS67" t="n">
         <v>0</v>
       </c>
+      <c r="AT67" t="n">
+        <v>113</v>
+      </c>
+      <c r="AU67" t="n">
+        <v>9520000</v>
+      </c>
+      <c r="AV67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB67" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -32680,6 +34516,33 @@
       <c r="AS68" t="n">
         <v>0</v>
       </c>
+      <c r="AT68" t="n">
+        <v>459</v>
+      </c>
+      <c r="AU68" t="n">
+        <v>6626803</v>
+      </c>
+      <c r="AV68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX68" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="AY68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB68" t="n">
+        <v>7823136</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -32838,6 +34701,33 @@
       <c r="AS69" t="n">
         <v>0</v>
       </c>
+      <c r="AT69" t="n">
+        <v>765</v>
+      </c>
+      <c r="AU69" t="n">
+        <v>11044672</v>
+      </c>
+      <c r="AV69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX69" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="AY69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB69" t="n">
+        <v>13038561</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -32996,6 +34886,33 @@
       <c r="AS70" t="n">
         <v>0</v>
       </c>
+      <c r="AT70" t="n">
+        <v>1070</v>
+      </c>
+      <c r="AU70" t="n">
+        <v>15462541</v>
+      </c>
+      <c r="AV70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX70" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="AY70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB70" t="n">
+        <v>18253985</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -33154,6 +35071,33 @@
       <c r="AS71" t="n">
         <v>1397664</v>
       </c>
+      <c r="AT71" t="n">
+        <v>78</v>
+      </c>
+      <c r="AU71" t="n">
+        <v>1333932</v>
+      </c>
+      <c r="AV71" t="n">
+        <v>1397664</v>
+      </c>
+      <c r="AW71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX71" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AY71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB71" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -33312,6 +35256,33 @@
       <c r="AS72" t="n">
         <v>2329440</v>
       </c>
+      <c r="AT72" t="n">
+        <v>131</v>
+      </c>
+      <c r="AU72" t="n">
+        <v>2223220</v>
+      </c>
+      <c r="AV72" t="n">
+        <v>2329440</v>
+      </c>
+      <c r="AW72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX72" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AY72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB72" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -33470,6 +35441,33 @@
       <c r="AS73" t="n">
         <v>3261216</v>
       </c>
+      <c r="AT73" t="n">
+        <v>183</v>
+      </c>
+      <c r="AU73" t="n">
+        <v>3112508</v>
+      </c>
+      <c r="AV73" t="n">
+        <v>3261216</v>
+      </c>
+      <c r="AW73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX73" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AY73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB73" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -33628,6 +35626,33 @@
       <c r="AS74" t="n">
         <v>2527200</v>
       </c>
+      <c r="AT74" t="n">
+        <v>128</v>
+      </c>
+      <c r="AU74" t="n">
+        <v>2219796</v>
+      </c>
+      <c r="AV74" t="n">
+        <v>2527200</v>
+      </c>
+      <c r="AW74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX74" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AY74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB74" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -33786,6 +35811,33 @@
       <c r="AS75" t="n">
         <v>4212000</v>
       </c>
+      <c r="AT75" t="n">
+        <v>213</v>
+      </c>
+      <c r="AU75" t="n">
+        <v>3699660</v>
+      </c>
+      <c r="AV75" t="n">
+        <v>4212000</v>
+      </c>
+      <c r="AW75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX75" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AY75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB75" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -33944,6 +35996,33 @@
       <c r="AS76" t="n">
         <v>5896800</v>
       </c>
+      <c r="AT76" t="n">
+        <v>299</v>
+      </c>
+      <c r="AU76" t="n">
+        <v>5179524</v>
+      </c>
+      <c r="AV76" t="n">
+        <v>5896800</v>
+      </c>
+      <c r="AW76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX76" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AY76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB76" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -34102,6 +36181,33 @@
       <c r="AS77" t="n">
         <v>0</v>
       </c>
+      <c r="AT77" t="n">
+        <v>172</v>
+      </c>
+      <c r="AU77" t="n">
+        <v>522665</v>
+      </c>
+      <c r="AV77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX77" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AY77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB77" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -34260,6 +36366,33 @@
       <c r="AS78" t="n">
         <v>0</v>
       </c>
+      <c r="AT78" t="n">
+        <v>287</v>
+      </c>
+      <c r="AU78" t="n">
+        <v>871109</v>
+      </c>
+      <c r="AV78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX78" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AY78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB78" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -34418,6 +36551,33 @@
       <c r="AS79" t="n">
         <v>0</v>
       </c>
+      <c r="AT79" t="n">
+        <v>402</v>
+      </c>
+      <c r="AU79" t="n">
+        <v>1219552</v>
+      </c>
+      <c r="AV79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX79" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AY79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB79" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -34581,6 +36741,33 @@
       <c r="AS80" t="n">
         <v>0</v>
       </c>
+      <c r="AT80" t="n">
+        <v>150</v>
+      </c>
+      <c r="AU80" t="n">
+        <v>1529788</v>
+      </c>
+      <c r="AV80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY80" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="AZ80" t="n">
+        <v>75000000</v>
+      </c>
+      <c r="BA80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB80" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -34744,6 +36931,33 @@
       <c r="AS81" t="n">
         <v>0</v>
       </c>
+      <c r="AT81" t="n">
+        <v>249</v>
+      </c>
+      <c r="AU81" t="n">
+        <v>2549647</v>
+      </c>
+      <c r="AV81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY81" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="AZ81" t="n">
+        <v>75000000</v>
+      </c>
+      <c r="BA81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB81" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -34907,6 +37121,33 @@
       <c r="AS82" t="n">
         <v>0</v>
       </c>
+      <c r="AT82" t="n">
+        <v>349</v>
+      </c>
+      <c r="AU82" t="n">
+        <v>3569505</v>
+      </c>
+      <c r="AV82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY82" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="AZ82" t="n">
+        <v>75000000</v>
+      </c>
+      <c r="BA82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB82" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -35070,6 +37311,33 @@
       <c r="AS83" t="n">
         <v>0</v>
       </c>
+      <c r="AT83" t="n">
+        <v>46</v>
+      </c>
+      <c r="AU83" t="n">
+        <v>1218565</v>
+      </c>
+      <c r="AV83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY83" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="AZ83" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="BA83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB83" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -35233,6 +37501,33 @@
       <c r="AS84" t="n">
         <v>0</v>
       </c>
+      <c r="AT84" t="n">
+        <v>77</v>
+      </c>
+      <c r="AU84" t="n">
+        <v>2030942</v>
+      </c>
+      <c r="AV84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY84" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="AZ84" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="BA84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB84" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -35396,6 +37691,33 @@
       <c r="AS85" t="n">
         <v>0</v>
       </c>
+      <c r="AT85" t="n">
+        <v>108</v>
+      </c>
+      <c r="AU85" t="n">
+        <v>2843318</v>
+      </c>
+      <c r="AV85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY85" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="AZ85" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="BA85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB85" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -35559,6 +37881,33 @@
       <c r="AS86" t="n">
         <v>0</v>
       </c>
+      <c r="AT86" t="n">
+        <v>315</v>
+      </c>
+      <c r="AU86" t="n">
+        <v>1820190</v>
+      </c>
+      <c r="AV86" t="n">
+        <v>43000000</v>
+      </c>
+      <c r="AW86" t="n">
+        <v>43000000</v>
+      </c>
+      <c r="AX86" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="AY86" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="AZ86" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="BA86" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="BB86" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -35722,6 +38071,33 @@
       <c r="AS87" t="n">
         <v>0</v>
       </c>
+      <c r="AT87" t="n">
+        <v>525</v>
+      </c>
+      <c r="AU87" t="n">
+        <v>3033650</v>
+      </c>
+      <c r="AV87" t="n">
+        <v>43000000</v>
+      </c>
+      <c r="AW87" t="n">
+        <v>43000000</v>
+      </c>
+      <c r="AX87" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="AY87" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="AZ87" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="BA87" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="BB87" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -35885,6 +38261,33 @@
       <c r="AS88" t="n">
         <v>0</v>
       </c>
+      <c r="AT88" t="n">
+        <v>735</v>
+      </c>
+      <c r="AU88" t="n">
+        <v>4247110</v>
+      </c>
+      <c r="AV88" t="n">
+        <v>43000000</v>
+      </c>
+      <c r="AW88" t="n">
+        <v>43000000</v>
+      </c>
+      <c r="AX88" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="AY88" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="AZ88" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="BA88" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="BB88" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -36043,6 +38446,33 @@
       <c r="AS89" t="n">
         <v>0</v>
       </c>
+      <c r="AT89" t="n">
+        <v>301</v>
+      </c>
+      <c r="AU89" t="n">
+        <v>1094351</v>
+      </c>
+      <c r="AV89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX89" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="AY89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB89" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -36201,6 +38631,33 @@
       <c r="AS90" t="n">
         <v>0</v>
       </c>
+      <c r="AT90" t="n">
+        <v>501</v>
+      </c>
+      <c r="AU90" t="n">
+        <v>1823918</v>
+      </c>
+      <c r="AV90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX90" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="AY90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB90" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -36359,6 +38816,33 @@
       <c r="AS91" t="n">
         <v>0</v>
       </c>
+      <c r="AT91" t="n">
+        <v>701</v>
+      </c>
+      <c r="AU91" t="n">
+        <v>2553486</v>
+      </c>
+      <c r="AV91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX91" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="AY91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB91" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -36517,6 +39001,33 @@
       <c r="AS92" t="n">
         <v>10957170</v>
       </c>
+      <c r="AT92" t="n">
+        <v>514</v>
+      </c>
+      <c r="AU92" t="n">
+        <v>18032371</v>
+      </c>
+      <c r="AV92" t="n">
+        <v>10957170</v>
+      </c>
+      <c r="AW92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ92" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="BA92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB92" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -36675,6 +39186,33 @@
       <c r="AS93" t="n">
         <v>18261950</v>
       </c>
+      <c r="AT93" t="n">
+        <v>857</v>
+      </c>
+      <c r="AU93" t="n">
+        <v>30053952</v>
+      </c>
+      <c r="AV93" t="n">
+        <v>18261950</v>
+      </c>
+      <c r="AW93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ93" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="BA93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB93" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -36833,6 +39371,33 @@
       <c r="AS94" t="n">
         <v>25566730</v>
       </c>
+      <c r="AT94" t="n">
+        <v>1199</v>
+      </c>
+      <c r="AU94" t="n">
+        <v>42075533</v>
+      </c>
+      <c r="AV94" t="n">
+        <v>25566730</v>
+      </c>
+      <c r="AW94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ94" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="BA94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB94" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -36996,6 +39561,33 @@
       <c r="AS95" t="n">
         <v>0</v>
       </c>
+      <c r="AT95" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU95" t="n">
+        <v>34250</v>
+      </c>
+      <c r="AV95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA95" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="BB95" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -37159,6 +39751,33 @@
       <c r="AS96" t="n">
         <v>0</v>
       </c>
+      <c r="AT96" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU96" t="n">
+        <v>57084</v>
+      </c>
+      <c r="AV96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA96" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="BB96" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -37322,6 +39941,33 @@
       <c r="AS97" t="n">
         <v>0</v>
       </c>
+      <c r="AT97" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU97" t="n">
+        <v>79918</v>
+      </c>
+      <c r="AV97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA97" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="BB97" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -37482,6 +40128,33 @@
       <c r="AS98" t="n">
         <v>0</v>
       </c>
+      <c r="AT98" t="n">
+        <v>512</v>
+      </c>
+      <c r="AU98" t="n">
+        <v>16276678</v>
+      </c>
+      <c r="AV98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB98" t="n">
+        <v>9565436</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -37642,6 +40315,33 @@
       <c r="AS99" t="n">
         <v>0</v>
       </c>
+      <c r="AT99" t="n">
+        <v>853</v>
+      </c>
+      <c r="AU99" t="n">
+        <v>27127797</v>
+      </c>
+      <c r="AV99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB99" t="n">
+        <v>15942394</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -37802,6 +40502,33 @@
       <c r="AS100" t="n">
         <v>0</v>
       </c>
+      <c r="AT100" t="n">
+        <v>1195</v>
+      </c>
+      <c r="AU100" t="n">
+        <v>37978916</v>
+      </c>
+      <c r="AV100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB100" t="n">
+        <v>22319352</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -37954,6 +40681,33 @@
       <c r="AS101" t="n">
         <v>0</v>
       </c>
+      <c r="AT101" t="n">
+        <v>27</v>
+      </c>
+      <c r="AU101" t="n">
+        <v>1001722</v>
+      </c>
+      <c r="AV101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB101" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -38106,6 +40860,33 @@
       <c r="AS102" t="n">
         <v>0</v>
       </c>
+      <c r="AT102" t="n">
+        <v>45</v>
+      </c>
+      <c r="AU102" t="n">
+        <v>1669536</v>
+      </c>
+      <c r="AV102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB102" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -38258,6 +41039,33 @@
       <c r="AS103" t="n">
         <v>0</v>
       </c>
+      <c r="AT103" t="n">
+        <v>63</v>
+      </c>
+      <c r="AU103" t="n">
+        <v>2337350</v>
+      </c>
+      <c r="AV103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB103" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -38410,6 +41218,33 @@
       <c r="AS104" t="n">
         <v>0</v>
       </c>
+      <c r="AT104" t="n">
+        <v>38</v>
+      </c>
+      <c r="AU104" t="n">
+        <v>936447</v>
+      </c>
+      <c r="AV104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB104" t="n">
+        <v>4216867</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -38562,6 +41397,33 @@
       <c r="AS105" t="n">
         <v>0</v>
       </c>
+      <c r="AT105" t="n">
+        <v>63</v>
+      </c>
+      <c r="AU105" t="n">
+        <v>1560746</v>
+      </c>
+      <c r="AV105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB105" t="n">
+        <v>7028111</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -38713,6 +41575,33 @@
       </c>
       <c r="AS106" t="n">
         <v>0</v>
+      </c>
+      <c r="AT106" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU106" t="n">
+        <v>2185044</v>
+      </c>
+      <c r="AV106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB106" t="n">
+        <v>9839355</v>
       </c>
     </row>
   </sheetData>

--- a/data_input/04_preeval.xlsx
+++ b/data_input/04_preeval.xlsx
@@ -68377,7 +68377,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = AOV nền 282.333 · u khách sẵn có = +0%</t>
+          <t>giá trị hoá đơn = AOV nền 282.333 · u khách sẵn có = +0%</t>
         </is>
       </c>
     </row>
@@ -68439,7 +68439,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = AOV nền 298.981 · u khách sẵn có = +0%</t>
+          <t>giá trị hoá đơn = AOV nền 298.981 · u khách sẵn có = +0%</t>
         </is>
       </c>
     </row>
@@ -68501,7 +68501,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = AOV nền 298.981 · u khách sẵn có = +0%</t>
+          <t>giá trị hoá đơn = AOV nền 298.981 · u khách sẵn có = +0%</t>
         </is>
       </c>
     </row>
@@ -68563,7 +68563,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = AOV nền 291.227 · u khách sẵn có = +0%</t>
+          <t>giá trị hoá đơn = AOV nền 291.227 · u khách sẵn có = +0%</t>
         </is>
       </c>
     </row>
@@ -68625,7 +68625,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = max(AOV nền; ngưỡng × hệ số) 360.000 · u khách sẵn có = +0%</t>
+          <t>giá trị hoá đơn = max(AOV nền; ngưỡng × hệ số) 360.000 · u khách sẵn có = +0%</t>
         </is>
       </c>
     </row>
@@ -68687,7 +68687,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = giá bộ món chương trình 89.000 · u khách sẵn có = +0%</t>
+          <t>giá trị hoá đơn = giá bộ món chương trình 89.000 · u khách sẵn có = +0%</t>
         </is>
       </c>
     </row>
@@ -68749,7 +68749,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = AOV nền 291.227 · u khách sẵn có = +0%</t>
+          <t>giá trị hoá đơn = AOV nền 291.227 · u khách sẵn có = +0%</t>
         </is>
       </c>
     </row>
@@ -68811,7 +68811,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = max(AOV nền; ngưỡng × hệ số) 600.000 · u khách sẵn có = +0%</t>
+          <t>giá trị hoá đơn = max(AOV nền; ngưỡng × hệ số) 600.000 · u khách sẵn có = +0%</t>
         </is>
       </c>
     </row>
@@ -68873,7 +68873,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = AOV nền 291.227 · u khách sẵn có = +0%</t>
+          <t>giá trị hoá đơn = AOV nền 291.227 · u khách sẵn có = +0%</t>
         </is>
       </c>
     </row>
@@ -68935,7 +68935,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = giá bộ món chương trình 89.000 · u khách sẵn có = +0%</t>
+          <t>giá trị hoá đơn = giá bộ món chương trình 89.000 · u khách sẵn có = +0%</t>
         </is>
       </c>
     </row>
@@ -68991,7 +68991,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = TA nền × số khách tối thiểu 295.126 · u khách sẵn có = +0%</t>
+          <t>giá trị hoá đơn = TA nền × số khách tối thiểu 295.126 · u khách sẵn có = +0%</t>
         </is>
       </c>
     </row>
@@ -69053,7 +69053,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = AOV nền 279.942 · u khách sẵn có = +0%</t>
+          <t>giá trị hoá đơn = AOV nền 279.942 · u khách sẵn có = +0%</t>
         </is>
       </c>
     </row>
@@ -69115,7 +69115,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = nhập ở sổ 199.000 · u khách sẵn có = -49%</t>
+          <t>giá trị hoá đơn = nhập ở sổ 199.000 · u khách sẵn có = -49%</t>
         </is>
       </c>
     </row>
@@ -69177,7 +69177,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = nhập ở sổ 222.700 · u khách sẵn có = -33%</t>
+          <t>giá trị hoá đơn = nhập ở sổ 222.700 · u khách sẵn có = -33%</t>
         </is>
       </c>
     </row>
@@ -69239,7 +69239,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = nhập ở sổ 1.888.998 · u khách sẵn có = +0%</t>
+          <t>giá trị hoá đơn = nhập ở sổ 1.888.998 · u khách sẵn có = +0%</t>
         </is>
       </c>
     </row>
@@ -69301,7 +69301,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = nhập ở sổ 168.114 · u khách sẵn có = +0%</t>
+          <t>giá trị hoá đơn = nhập ở sổ 168.114 · u khách sẵn có = +0%</t>
         </is>
       </c>
     </row>
@@ -69363,7 +69363,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = nhập ở sổ 560.861 · u khách sẵn có = +0%</t>
+          <t>giá trị hoá đơn = nhập ở sổ 560.861 · u khách sẵn có = +0%</t>
         </is>
       </c>
     </row>
@@ -69425,7 +69425,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = TA nền × số khách tối thiểu 846.229 · u khách sẵn có = +0%</t>
+          <t>giá trị hoá đơn = TA nền × số khách tối thiểu 846.229 · u khách sẵn có = +0%</t>
         </is>
       </c>
     </row>
@@ -69487,7 +69487,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = AOV nền 650.223 · u khách sẵn có = +0%</t>
+          <t>giá trị hoá đơn = AOV nền 650.223 · u khách sẵn có = +0%</t>
         </is>
       </c>
     </row>
@@ -69549,7 +69549,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = giá bộ món chương trình 150.000 · u khách sẵn có = +0%</t>
+          <t>giá trị hoá đơn = giá bộ món chương trình 150.000 · u khách sẵn có = +0%</t>
         </is>
       </c>
     </row>
@@ -69611,7 +69611,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = AOV nền 650.223 · u khách sẵn có = +0%</t>
+          <t>giá trị hoá đơn = AOV nền 650.223 · u khách sẵn có = +0%</t>
         </is>
       </c>
     </row>
@@ -69673,7 +69673,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = AOV nền 650.223 · u khách sẵn có = +0%</t>
+          <t>giá trị hoá đơn = AOV nền 650.223 · u khách sẵn có = +0%</t>
         </is>
       </c>
     </row>
@@ -69735,7 +69735,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = max(AOV nền; ngưỡng × hệ số) 960.000 · u khách sẵn có = +0%</t>
+          <t>giá trị hoá đơn = max(AOV nền; ngưỡng × hệ số) 960.000 · u khách sẵn có = +0%</t>
         </is>
       </c>
     </row>
@@ -69797,7 +69797,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = nhập ở sổ 690.000 · u khách sẵn có = +56%</t>
+          <t>giá trị hoá đơn = nhập ở sổ 690.000 · u khách sẵn có = +56%</t>
         </is>
       </c>
     </row>
@@ -69859,7 +69859,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = AOV nền 1.661.976 · u khách sẵn có = +0%</t>
+          <t>giá trị hoá đơn = AOV nền 1.661.976 · u khách sẵn có = +0%</t>
         </is>
       </c>
     </row>
@@ -69921,7 +69921,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = nhập ở sổ 776.787 · u khách sẵn có = +0%</t>
+          <t>giá trị hoá đơn = nhập ở sổ 776.787 · u khách sẵn có = +0%</t>
         </is>
       </c>
     </row>
@@ -69983,7 +69983,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = AOV nền 1.812.419 · u khách sẵn có = +0%</t>
+          <t>giá trị hoá đơn = AOV nền 1.812.419 · u khách sẵn có = +0%</t>
         </is>
       </c>
     </row>
@@ -70045,7 +70045,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = TA nền × số khách tối thiểu 2.077.950 · u khách sẵn có = +0%</t>
+          <t>giá trị hoá đơn = TA nền × số khách tối thiểu 2.077.950 · u khách sẵn có = +0%</t>
         </is>
       </c>
     </row>
@@ -70107,7 +70107,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = AOV nền 1.812.419 · u khách sẵn có = +0%</t>
+          <t>giá trị hoá đơn = AOV nền 1.812.419 · u khách sẵn có = +0%</t>
         </is>
       </c>
     </row>
@@ -70169,7 +70169,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = nhập ở sổ 1.828.147 · u khách sẵn có = +0%</t>
+          <t>giá trị hoá đơn = nhập ở sổ 1.828.147 · u khách sẵn có = +0%</t>
         </is>
       </c>
     </row>
@@ -70231,7 +70231,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = nhập ở sổ 900.000 · u khách sẵn có = +0%</t>
+          <t>giá trị hoá đơn = nhập ở sổ 900.000 · u khách sẵn có = +0%</t>
         </is>
       </c>
     </row>
@@ -70293,7 +70293,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = nhập ở sổ 1.280.000 · u khách sẵn có = +0%</t>
+          <t>giá trị hoá đơn = nhập ở sổ 1.280.000 · u khách sẵn có = +0%</t>
         </is>
       </c>
     </row>
@@ -70355,7 +70355,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = AOV nền 1.761.101 · u khách sẵn có = +0%</t>
+          <t>giá trị hoá đơn = AOV nền 1.761.101 · u khách sẵn có = +0%</t>
         </is>
       </c>
     </row>
@@ -70417,7 +70417,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = max(AOV nền; ngưỡng × hệ số) 1.761.101 · u khách sẵn có = +0%</t>
+          <t>giá trị hoá đơn = max(AOV nền; ngưỡng × hệ số) 1.761.101 · u khách sẵn có = +0%</t>
         </is>
       </c>
     </row>
@@ -70479,7 +70479,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = AOV nền 1.761.101 · u khách sẵn có = +0%</t>
+          <t>giá trị hoá đơn = AOV nền 1.761.101 · u khách sẵn có = +0%</t>
         </is>
       </c>
     </row>
@@ -70541,7 +70541,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = nhập ở sổ 1.499.000 · u khách sẵn có = +7%</t>
+          <t>giá trị hoá đơn = nhập ở sổ 1.499.000 · u khách sẵn có = +7%</t>
         </is>
       </c>
     </row>
@@ -70603,7 +70603,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = nhập ở sổ 2.190.000 · u khách sẵn có = -27%</t>
+          <t>giá trị hoá đơn = nhập ở sổ 2.190.000 · u khách sẵn có = -27%</t>
         </is>
       </c>
     </row>
@@ -70665,7 +70665,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = nhập ở sổ 900.000 · u khách sẵn có = +0%</t>
+          <t>giá trị hoá đơn = nhập ở sổ 900.000 · u khách sẵn có = +0%</t>
         </is>
       </c>
     </row>
@@ -70727,7 +70727,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = TA nền × số khách tối thiểu 2.780.841 · u khách sẵn có = +0%</t>
+          <t>giá trị hoá đơn = TA nền × số khách tối thiểu 2.780.841 · u khách sẵn có = +0%</t>
         </is>
       </c>
     </row>
@@ -70789,7 +70789,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>file Final · giá trị hoá đơn = nhập ở sổ 900.000 · u khách sẵn có = +0%</t>
+          <t>giá trị hoá đơn = nhập ở sổ 900.000 · u khách sẵn có = +0%</t>
         </is>
       </c>
     </row>

--- a/data_input/04_preeval.xlsx
+++ b/data_input/04_preeval.xlsx
@@ -24453,10 +24453,10 @@
         <v>1619304</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3768346470330426</v>
+        <v>0.3768346470327184</v>
       </c>
       <c r="Y8" t="n">
-        <v>12.05278723164535</v>
+        <v>12.05278723150992</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -24640,10 +24640,10 @@
         <v>2698841</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3768346470330409</v>
+        <v>0.3768346470327164</v>
       </c>
       <c r="Y9" t="n">
-        <v>12.05278723164529</v>
+        <v>12.05278723150986</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
@@ -24827,10 +24827,10 @@
         <v>3778377</v>
       </c>
       <c r="X10" t="n">
-        <v>0.376834647033041</v>
+        <v>0.3768346470327163</v>
       </c>
       <c r="Y10" t="n">
-        <v>12.0527872316453</v>
+        <v>12.05278723150986</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -44544,7 +44544,7 @@
         <v>1126986</v>
       </c>
       <c r="K42" t="n">
-        <v>0.02443344692735244</v>
+        <v>0.02443344692738264</v>
       </c>
     </row>
     <row r="43">
@@ -44584,7 +44584,7 @@
         <v>1880999</v>
       </c>
       <c r="K43" t="n">
-        <v>0.02008601939794941</v>
+        <v>0.02008601939793445</v>
       </c>
     </row>
     <row r="44">
@@ -44790,7 +44790,7 @@
         <v>1878310</v>
       </c>
       <c r="K48" t="n">
-        <v>0.04072241154558744</v>
+        <v>0.04072241154563784</v>
       </c>
     </row>
     <row r="49">
@@ -44830,7 +44830,7 @@
         <v>3134998</v>
       </c>
       <c r="K49" t="n">
-        <v>0.03347669899658209</v>
+        <v>0.03347669899655726</v>
       </c>
     </row>
     <row r="50">
@@ -45036,7 +45036,7 @@
         <v>2629634</v>
       </c>
       <c r="K54" t="n">
-        <v>0.05701137616382229</v>
+        <v>0.05701137616389288</v>
       </c>
     </row>
     <row r="55">
@@ -45076,7 +45076,7 @@
         <v>4388998</v>
       </c>
       <c r="K55" t="n">
-        <v>0.04686737859521492</v>
+        <v>0.04686737859518007</v>
       </c>
     </row>
     <row r="56">
@@ -68302,10 +68302,10 @@
         <v>202531</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3612653529669584</v>
+        <v>0.3612653529672828</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6387346470330415</v>
+        <v>0.6387346470327171</v>
       </c>
       <c r="N5" t="n">
         <v>17528</v>
